--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1982,6 +1982,42 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="B44" t="n">
+        <v>6439.31982421875</v>
+      </c>
+      <c r="C44" t="n">
+        <v>6466.89013671875</v>
+      </c>
+      <c r="D44" t="n">
+        <v>6438.06005859375</v>
+      </c>
+      <c r="E44" t="n">
+        <v>6457.669921875</v>
+      </c>
+      <c r="F44" t="n">
+        <v>4059070000</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-0.0042663855480634</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>inventhelp inventor develop new thermal capacitor water heater tl council asked to help expand eye on the street program gray medium to produce and air tomorrow new orleans saint preseason game in endtoend native hdr via nextgen tv hidden google search feature that make you a power user jerome powell signal fed may cut rate soon even a inflation risk remain elon musk must face lawsuit for duping trump supporter in million giveaway give your teeth the care they deserve with off an aquasonic ultra whitening toothbrush u supreme court allows nih to cut billion in research grant nature ninepoint partner announces estimated august cash distribution for ninepoint cash management fund etf series clean smarter not harder the best electric spin scrubber make cleaning a breeze federal workforce to lose employee this year trump official say in canada billboard woman in music open nomination for honoree cracker barrel crackup how the culture war are upending corporate branding powell signal fed may cut rate soon even a inflation risk remain canada will match u tariff exemption under usmca trade pact prime minister carney say whats needed to unlock the power and promise of imec new rv provides opioid recovery medical care to underserved minneapolis neighborhood powell signal fed may cut rate soon even a inflation risk remain onlyfans stats that show how massive the platform ha become green space are key to combating record heat in marginalized community familyfriendly workplace gov order budget cut for all state agency except school why xrp is soaring today are you even ready to grow lesson every owneroperator need before adding a truck gen z career catfishing rise ai recruiter a ethical solution trump say canada will drop usmcacompliant retaliatory tariff capital solution hire former caci exec a chief operating officer sunflower elect new board leader director king island tease return of beloved phantom theater ride top evercore analyst boost nvidia nvda stock price target ahead of q earnings tipranks bank lobby for national standard to limit state regulation shareholder alert levi korsinsky llp notifies investor it ha filed a complaint to recover loss suffered by purchaser of cai inc security and set a lead plaintiff deadline of october rosen national investor counsel encourages lockheed martin corporation investor to secure counsel before important deadline in security class action lmt elite express holding inc announces closing of million initial public offering ross benefit from value shopper but tariff challenge continue cvcc board set to review tax implication of new career center best ai writing tool for researcher zumpano patricios welcome sebastian jaramillo a income partner strengthening real estate practice zumpano patricios welcome sebastian jaramillo a income partner strengthening real estate practice canada to ease most retaliatory tariff against united state extrump cfo weisselberg may keep severance pay appellate court rule ethylene buyer could be ruined for their cartel example of unpaid work deal dispatch muskaltman drama ashton kutcher soho house play and we pose question to private equity pro fiserv push embedded payment for health care canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal canada removing tariff on u good compliant with free trade deal netskope file for u ipo with m revenue yoy growth walmart q revenue surge to b raise fullyear outlook delta airline offering new direct flight from austin airport why intuit stock intu is sinking today blue bell ice cream recalled due to packaging error trump say hell be very good to canada a it prime minister drop some tariff trump say we want to be very good to canada a it leader drop some tariff canada remove some of it retaliatory tariff on the u canada remove some of it retaliatory tariff on the u canada remove some of it retaliatory tariff on the u npr trump say we want to be very good to canada a it leader drop some tariff canada remove some of it retaliatory tariff on the u weekly commodity wrapup why lucid group stock died today then got better tinley park chamber cancel this year oktoberfest due to cost how market reacted after powell signaled potential rate cut eastgroup property announces dividend increase how nvidias chip became central to the uschina trade war how nvidias chip became central to the uschina trade war how nvidias chip became central to the uschina trade war how nvidias chip became central to the uschina trade war branded legacy inc form strategic partnership with stanford university dr eran bendavid to advance addiction solution stock market surge after jerome powell indicates rate cut may be coming canada remove countertariffs on some u good canada to drop countertariffs on some u good one day after call with trump bitcoin and crypto stock surge a powell ratecut hint revives risk appetite walmart hike discount for shopper amid tariff uncertainty this is what whale are betting on okta starbucks car toy close on broadway in denver coffee giant closing all non drivethrus snap investor with loss in excess of k have opportunity to lead snap inc security lawsuit kirby mcinerney llp announces investigation against avita medical inc on behalf of investor bear alley marketing position itself a a leader in performance marketing for home service trump say hell keep extending tiktok shutdown deadline let talk indianola school business official brian bartz what is credit card forbearance and who qualifies for it this september bet bonus code nypbet bet get in bonus bet win or lose for yankee v red sox on friday sima monthly investment fund statistic july pi down from ath icp volume tank meanwhile blockdags b token sold point to the next x dsw offer discount on brook revel running shoe this week degree capital announces result of special meeting of shareholder to approve the proposed business combination with mount logan capital inc brattleboro parking zone to be relabeled high roller announces nyse acceptance of plan to regain listing compliance degree capital announces result of special meeting of shareholder to approve the proposed business combination with mount logan capital inc canada to remove many retaliatory tariff on u good allegro stock recovery elliott wave structure support fundamental case labubu blind box restocking aug aug here what to know trump say intel ha agreed to give the u a equity stake bloomberg rich lowry trump is wrong about mailin voting cheap drug high stake america risky bet on china trump again give putin a couple of week with no sign of ukraine peace talk underway cnn trump suggests chicago is next for federal crime crackdown followed by new york city cbs news president donald trump plan crime crackdown in chicago similar to dc national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital national guard troop will soon carry weapon in u capital court ruling clear the way for hundred of cdc staff to be laid off jury selection taking time in randolph csc trial mayor trump president fixates on local crime asphalt and lamppost latest news on fbi searching john boltons home office george mason illegally used race in hiring department of education find george mason illegally used race in hiring department of education find a judge ha ordered alligator alcatraz in florida to wind down operation what happens now world cup draw will be held at washington kennedy center trump say kamala harris will take her day book tour to los angeles california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk newsoms profile soar with trump redistricting fight california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk california gov gavin newsoms national profile soar with latest trump fight but there are risk lake lynn answer ferc question raise possibility of entry fee at cheat lake park people officially became u citizen at the new york state fair funeral home owner who stashed nearly decaying body set to be sentenced new york city to get federal police for crime crackdown after dc chicago trump trump praise missouri republican for considering redistricting bolton investigated over classified document not politics vp vance tell nbc community patrol confronts ice officer at city height elementary school parking lot stitt take aim at tulsa mayor decision to prosecute crime in tribal court trump tariff will reduce deficit by trillion over next decade say cbo report ask rusty how do i apply for s and receive my payment trump say hell keep extending tiktok shutdown deadline trump say hell keep extending tiktok shutdown deadline trump say hell keep extending tiktok shutdown deadline trump say hell keep extending tiktok shutdown deadline uk diplomat receives warning over illegal fishing with jd vance mit global collapse warning revisited humanity enters makeorbreak decade chicago is up next for the national guard theyre screaming for u say trump san carlos and the lastminute commissioner item henderson accepting application for addition to veteran memorial wall trump reacts to canada reversing retaliatory tariff take question at white house erik and lyle menendez can still walk free from prison even if both brother have parole denied a family fight back desantis fire back after dem decries florida move to ditch lgbt rainbow color from crosswalk in orlando hegseth authorizes national guard to carry gun in washington dc ap technology summarybrief at pm edt trump is astonishingly deluded about putin trump official demand apology from george mason president over diversity the new york time the u air force just underwent a massive stress test of how it would fight a highend war in the pacific uk top diplomat get a warning for illegal fishing with u vice president national guard troop in washington will be armed hegseth matt fleming how assembly democrat came to embrace gerrymandering passing the baton in europe could donald trump really win the nobel peace prize asking eric am i wrong for wanting to back out of mexican vacation now that friend included her son beware of the skeeters and malary asking eric am i wrong for backing out of a trip because a friend son is going an energy transition at the crossroad south korea journey toward resilience the u navy drone effort arent going wellbut neither are china pa budget stall again what will it take to break the cycle of delay carney say he will travel to germany next week to deepen tie canada go learn some english customer berates georgian nyc cafe owner now everyones coming to her defense teaching just the fact is not an answer to indoctrination gavin newsoms redistricting gambit a presidential audition not a policy plan fifa world cup draw to take place at kennedy center trump announces tension flare a texas house panel hears a bathroom bill for first time in eight year trump message to dc criminal democrat dont mess with me how some apps are working to solve the epidemic of loneliness what to expect from the ussouth korea summit planned parenthood sue south carolina over medicaid ban certain local voice oppose gov newsoms redistricting campaign cracker barrel new logo sucksand not because of wokeness you idiot ct governor directs flag to halfstaff saturday for state employee fatally injured on job trump say hell ask congress for b for dc improvement letter taxpayer against genocide trump say putin may attend north america world cup it so on after heated back and forth with chris rufo on conservatism jonah goldberg agrees to debate homeowner oppose plan for fencing dune on hollywood beach here why trump say putin may attend north america world cup california ab stall in senate amid parental right opposition trump say putin may attend north america world cup trump say putin may attend north america world cup california governor signed a redistricting plan what happens next trump show off photo putin mailed him from alaska summit but president warns i better be very happy with peace talk after russia ukraine attack policy review committee recap august james jim mcgregor trump say chicago is next for dcstyle federal law enforcement operation a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now a judge ha ordered alligator alcatraz in florida to wind down operation what happens now shiba inu shib is taking longer than expected to reach new high in pepe coin pepe and this coin to outperform it investing in ozak ai ethereumbased ai token during it under presale could lead to millionaire status by a btc and eth hit ath cadence bank ha million stock holding in texas instrument incorporated txn jpmorgan chase co jpm share sold by rbo co llc hoka ha shoe on sale for a low a right now including bondi and clifton trump administration halt construction of revolution wind farm off mass citing national security new brewery tap into corydons dora ordinance excitement british columbia investment management corp sell share of alphabet inc goog british columbia investment management corp raise holding in broadcom inc avgo air canada say more passenger eligible for reimbursement if flight were cancelled canada grab these safe djia dividend bargain after index hit alltime high nextgen pick best cryptos to buy today a arctic pablos cex listing driving maximum gain potential twothirds of river trash is plastic research fastfood chain lock in meal to fight inflation in newsguild see organizing surge a medium worker fuel grassroots militancy tech ceo urge dignity for billion shift worker amid automation lowes target pro with total home strategy amid sale dip and inflation european postal service halt u shipment over trump tariff china stock surge defies weak economy raising fear of another bust analyst waste management inc nysewm announces quarterly dividend evans city council approves ballot language for permanent road tax bet bonus code orl bonus for seahawks v packer raider v cardinal solana whale rotate capital into layer brett analyst say it could deliver x gain by next year whale are choosing this meme coin a the best crypto to buy in instead of dogecoin doge and shiba sol strengthens on institutional demand xrp jump after whale action and blockdags forecast draw buyer in phoenix wealth advisor sell share of air product and chemical inc apd btc climbed to of global money before fed chair signaled rate cut cointelegraph heritage wealth partner llc buy share of meta platform inc meta palantir technology nasdaqpltr insider ryan taylor sell share palantir technology nasdaqpltr insider ryan taylor sell share of stock promising retail stock to keep an eye on august th jpmorgan chase co jpm is biondo investment advisor llcs th largest position immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say trump appeal in fraud case likely despite his total victory trump appeal in fraud case likely despite his total victory baby boomer turned meme stock trading into a thrilling hobby calling it absolutely gambling trump appeal in fraud case likely despite his total victory this weatherproof storage shed is only during wayfairs labor day blowout sale bank of america nysebac hit new month high whats next invesco qqq qqq share purchased by haverford trust co cardano price prediction ada eye new high yet this lowcap coin ha x more upside beltway buzz august apg asset management nv acquires share of intuitive surgical inc isrg pfizer inc pfe share sold by apg asset management nv what to know about visa for foreign trucker and the politics of a deadly florida crash the best amazon deal to shop right now save up to trump halt work on new england offshore wind project thats nearly complete trump halt work on new england offshore wind project thats nearly complete bitcoin btc price could retrace before a run toward kk but ripple xrp and this coin are aiming high in cryptos next top altcoin why this crypto could shine a xrp fall below best gift for digital artist in trump halt work on nearly complete new england offshore wind project waste management inc wm share acquired by groupe la francaise union pacific corporation unp share purchased by kestra advisory service llc haverford trust co sell share of unitedhealth group incorporated unh waste management inc wm share sold by van hulzen asset management llc groupe la francaise purchase share of walmart inc wmt phoenix wealth advisor trim position in cisco system inc csco bahl gaynor inc increase stake in taiwan semiconductor manufacturing company ltd tsm best of the best bahl gaynor inc sell share of mcdonalds corporation mcd chicago a mess trump vow national guard crackdown layer brett dubbed pepe after early momentum outpaces early doge and shib launch hooter bankruptcy prompt rebrand to tacky familyfriendly are home depot cheapest tool set worth buying here what user say trump halt work on new england offshore wind project thats nearly complete douglas winthrop advisor llc sell share of pepsico inc pep caitlin john llc ha holding in invesco qqq qqq british columbia investment management corp buy share of procter gamble company the pg penticton council willing to work with art gallery after layoff announced penticton get your own steam locomotive how family can save money this backtoschool season northwest minnesota foundation issue over million in grant loan during th quarter why the iea reinstated it business a usual scenario business accelerator academy start in september how u of a help build worldclass entrepreneur dogecoin price target in september but analyst say x gain belong to new lowcaps can solana reach by or is there a better crypto to buy now blockdags m presale and referral reward shift focus from xrp rally and eth market issue trump halt work on new england offshore wind project thats nearly complete yahoocom trump halt work on new england offshore wind project thats nearly complete trump halt work on new england offshore wind project thats nearly complete ai bubble fear spark tech stock slide crash warning rise how and where to bet mlb player prop pick odds for aug garrett crochet among best bet smartleaf asset management llc ha million stock holding in mastercard incorporated ma walmart nysewmt issue fy earnings guidance biondo investment advisor llc ha million stake in unitedhealth group incorporated unh cadence bank sell share of american express company axp forest avenue capital management lp boost holding in vistra corp vst european post suspend u delivery over trumpera tariff biondo investment advisor llc acquires share of amgen inc amgn svb wealth llc lower stock position in blackrock blk svb wealth llc sell share of air product and chemical inc apd air product and chemical inc apd share sold by british columbia investment management corp svb wealth llc sell share of air product and chemical inc apd lionshead wealth management llc ha holding in illinois tool work inc itw biondo investment advisor llc increase stock holding in duke energy corporation duk kruse out a dia director in latest pentagon shakeup cringe watch zohran mamdani plan nyc scavenger hunt is there a prize if youre mugged on the subway cu colorado spring campus thought it could avoid trump education crackdown here what happened cu colorado spring campus thought it could avoid trump education crackdown here what happened cu colorado spring campus thought it could avoid trump education crackdown here what happened u justice department release transcript of interview with ghislaine maxwell kilmar abrego garcia is freed from tennessee jail so he can rejoin family in maryland to await trial greene issue scathing rebuke of condition in gaza i will not be silent about it israel vow to open gate of hell on gaza in chilling warning a famine grip the region u seek to deport kilmar abrego garcia to uganda after he refused plea offer in his smuggling case u seek to deport kilmar abrego garcia to uganda after he refused plea offer in his smuggling case kevin oleary sound alarm on rich kid upbringing they become lost in a sea of mediocrity it a disaster for them former dhs official signal he could be next after bolton fbi raid we expect it the lioness at the center of a city hall battered by scandal dnc vote on israel arm embargo may set democratic party course on palestine trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it trump ran on a promise of revenge he making good on it u seek to deport abrego garcia to uganda hampton county law enforcement to ramp up duo patrol trump administration considering deporting kilmar abrego garcia to uganda his lawyer say secretariat jockey mourned in maine a well a canada dunkin customer warns to check receipt after spotting wellness fee national guard roll out in state not linked to trump crime crackdown wh say the redistricting war between texas and california is about to jolt the midterm politico asking eric were no longer invited to shared family holiday meal what should we do about upcoming wedding redistricting war poised to explode a california and texas make their move la consequential karen bass earns epic ratio over claim city recovery is fastest in state history the redistricting war between texas and california is about to jolt the midterm texas abbott promise quick signature of redistricting plan following overnight senate vote ghislaine maxwell absolves trump and everyone else in doj interview conservative activist slam cracker barrel a company left reeling after logo redesign south korea japan agree to boost tie a challenge mount kilmar abrego garcia released from ice custody after return from el salvador truck driver in crash at center of trump administration feud with newsom is denied bond when trying to explain low dem party polling look no further than awesome duo of newsom and swalwell immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say immigration boosted europe economy after pandemic ecbs lagarde say u seek to deport kilmar abrego garcia to uganda after he refused plea offer in his smuggling case trump look to chicago next in federal crackdown the wall street journal giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell giuffre family outraged over doj interview with ghislaine maxwell university of oregon concludes law review discriminated based on perceived national origin against israeli author trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress trump hail new texas electoral map aimed at keeping grip on congress how redistricting is done and why it could give party an edge in election how redistricting is done and why it could give party an edge in election democrat mock jd vance for having cardboard charisma a he push unpopular budget bill opinion it time for mayo pete buttigieg to find some seasoning what happened to ambition for bay restoration guest commentary kilmar abrego garcia threatened with deportation to uganda larimer county restaurant inspection made aug kilmar abrego garcia threatened with deportation to uganda kilmar abrego garcia threatened with deportation to uganda judge block trump from cutting funding from city and county including denver over sanctuary policy internet tax freedom act preempt new york imposition of tax fbi target john boltons home and office trump he not a smart guy but he could be a very unpatriotic guy inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal rachel bitecofer warns that bolton is just the start and trump will go after the rest of u inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal what we know about china and russia new strategic bomber inside the facility where ice is training recruit to take on trump deportation goal inside the facility where ice is training recruit to take on trump deportation goal zelenskyy say security guarantee for ukraine to be ready soon bill maher applauds gavin newsom for mocking donald trump i think it very funny floridarun alligator alcatraz violates u law aclu say russia announces support for venezuela to defend sovereignty amid growing military tension with the united state gianno caldwell mull senate bid a chicagoans are begging for change on crime woe trump threatens chicago with next national guard invasion cnn analyst pinpoint the weirdest part of ghislaine maxwell simply bizarre doj interview cnn analyst pinpoint the weirdest part of ghislaine maxwell simply bizarre doj interview the owl eye liberty and memory from epstein suicide to trump and clinton takeaway from ghislaine maxwell transcript how can israel engineer a famine in gaza in the st century what we learned from the ghislaine maxwell doj interview texas gov abbott say hell swiftly sign redistricting map after lawmaker approve them jeff bezos said he would have felt icky had he taken any more share of amazon i just didnt feel good smart money strategy what the pro buy when the crypto market crash radioactive shrimp update walmart store brand and other brand recalled european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff european postal service suspend shipment of package to u over tariff a winning powerball ticket ha been sold in western new york the sp hasnt yielded this little since the dotcom bubble here what investor can do the motley fool just ranked the biggest financial stock here why the no pick could be your best investment mezcal producer preserve traditional method a demand for liquor grows minute european postal service suspend shipment of package to u over tariff kpop demon hunter give netflix it first boxoffice win curry join the bank holiday sale bonanza with it epic deal event here are the best offer id buy self driving taxi may be coming to nyc a waymo win first av testing permit mashable rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important rosen a leading law firm encourages fiserv inc investor to secure counsel before important deadline in security class action fi ice cream sold at walmarts across state recalled due to undeclared allergen here how a gamestop purchase turned into a bitcoin jackpot ice cream sold at walmarts across state recalled due to undeclared allergen fox business prediction lucid group sale will soar over the next year if this happens solar executive warn that trump attack on renewables will lead to power crunch that spike electricity price pueblo county home listing asked for less money in july see the current median price here prediction these trilliondollar artificial intelligence ai stock could strike a megadeal that wall street isnt ready for cold wallet cashback utility and presale pricing create a upside case while chainlink and shiba inu struggle maintenance compliance burden viability of hopi water treatment system ethereum in trouble xrp might breakout buyer turn to blockdag to earn referral reward acting a the executor of a will can be a very lucrative job the last word national guard troop to be force multiplier for ice homan little pepe crypto price prediction is lilpepe a good investment for longterm holder here how much you should aim to invest in the invesco qqq etf to get to million or more by retirement state audit question m in federal spending by moses lake school district blockchain stock worth watching august th owner scale back golden mile shopping center redevelopment rosen global investor counsel encourages easterly rocmuni high income municipal bond fund comerica bank lower stake in alphabet inc goog trump tap airbnb cofounder a st government design head to lead huge web overhaul trump tap airbnb cofounder a st government design head to lead huge web overhaul fox business offgrid living next new real estate trend a application for rural mortgage skyrocket rosen global investor counsel encourages altimmune inc investor to secure counsel before rosen global investor counsel encourages altimmune inc investor to secure counsel before rosen global investor counsel encourages altimmune inc investor to secure counsel before epstein accuser virginia giuffre wrote a memoir month after her death it coming out powell warning signal unemployment claim jump to highest in year cardano price outlook can ada reach trumprelated defi platform world liberty financial debut wlfi token on ethereum mainnet rosen global investor counsel encourages altimmune inc investor to secure counsel before important deadline in security class action alt the best meme coin presale stampede is loading whitelist labubull now or watch it moon without you backtoschool deal tellos unlimited plan get you cell service for per month your first month nexus gold cvenxs stock price up whats next mason resource cvellg stock price up here why mason resource cvellg trading up here what happened national guard troop to be force multiplier for ice homan freedom investment management inc purchase share of procter gamble company the pg ascent group llc raise stock holding in ameri</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>inventhelp inventor develop new thermal capacitor water heater tl council help expand eye street program gray medium produce air tomorrow new orleans saint preseason game endtoend native hdr via nextgen tv hidden google search feature power user jerome powell signal fed cut rate soon inflation risk elon musk must face lawsuit duping trump supporter million giveaway give teeth care deserve aquasonic ultra whitening toothbrush supreme court allows nih cut billion research grant nature ninepoint partner announces estimated august cash distribution ninepoint cash management fund etf series clean smarter harder best electric spin scrubber cleaning breeze federal workforce lose employee year trump canada billboard woman music open nomination honoree cracker barrel crackup culture war upending corporate branding powell signal fed cut rate soon inflation risk canada match tariff exemption usmca trade pact prime minister carney whats needed unlock power promise imec new rv provides opioid recovery medical care underserved minneapolis neighborhood powell signal fed cut rate soon inflation risk onlyfans stats massive platform become green space combating record heat marginalized community familyfriendly workplace gov order budget cut agency except school xrp soaring today ready grow lesson owneroperator adding truck gen z career catfishing rise ai recruiter ethical solution trump canada drop usmcacompliant retaliatory tariff capital solution hire caci exec chief operating officer sunflower elect new board director king island tease beloved phantom theater ride evercore analyst boost nvidia nvda stock price target ahead q earnings tipranks bank lobby national limit regulation shareholder alert levi korsinsky llp notifies investor filed complaint recover loss suffered purchaser cai security set lead plaintiff deadline october rosen national investor counsel encourages lockheed martin corporation investor secure counsel important deadline security class action lmt elite express holding announces closing million initial public offering ross benefit value shopper tariff challenge continue cvcc board set review tax implication new career center best ai writing tool researcher zumpano patricios welcome sebastian jaramillo income partner strengthening real estate practice zumpano patricios welcome sebastian jaramillo income partner strengthening real estate practice canada ease retaliatory tariff united extrump cfo weisselberg severance pay appellate court rule ethylene buyer ruined cartel example unpaid work deal dispatch muskaltman drama ashton kutcher soho house play pose private equity pro fiserv push embedded payment health care canada removing tariff good compliant free trade deal canada removing tariff good compliant free trade deal canada removing tariff good compliant free trade deal canada removing tariff good compliant free trade deal canada removing tariff good compliant free trade deal canada removing tariff good compliant free trade deal canada removing tariff good compliant free trade deal canada removing tariff good compliant free trade deal netskope file ipo revenue yoy growth walmart q revenue surge b raise fullyear outlook delta airline offering new direct flight austin airport intuit stock intu sinking today blue bell cream recalled due packaging error trump hell good canada prime minister drop tariff trump good canada drop tariff canada remove retaliatory tariff canada remove retaliatory tariff canada remove retaliatory tariff npr trump good canada drop tariff canada remove retaliatory tariff weekly commodity wrapup lucid stock died today got better tinley park chamber cancel year oktoberfest due cost market reacted powell signaled potential rate cut eastgroup property announces dividend increase nvidias chip became central uschina trade war nvidias chip became central uschina trade war nvidias chip became central uschina trade war nvidias chip became central uschina trade war branded legacy form strategic partnership stanford university dr eran bendavid advance addiction solution stock market surge jerome powell indicates rate cut coming canada remove countertariffs good canada drop countertariffs good day call trump bitcoin crypto stock surge powell ratecut hint revives risk appetite walmart hike discount shopper amid tariff uncertainty whale betting okta starbucks car toy close broadway denver coffee giant closing non drivethrus snap investor loss excess k opportunity lead snap security lawsuit kirby mcinerney llp announces investigation avita medical behalf investor bear alley marketing performance marketing service trump hell extending tiktok shutdown deadline indianola school business brian bartz credit card forbearance qualifies september bet bonus code nypbet bet bonus bet lose yankee v red sox friday sima monthly investment fund statistic july pi ath icp volume tank meanwhile blockdags b token sold next x dsw offer discount brook revel running shoe degree capital announces special meeting shareholder approve proposed business combination mount logan capital brattleboro parking zone relabeled high roller announces nyse acceptance plan regain listing compliance degree capital announces special meeting shareholder approve proposed business combination mount logan capital canada remove retaliatory tariff good allegro stock recovery elliott wave structure support fundamental case labubu blind box restocking aug aug trump intel agreed give equity stake bloomberg rich lowry trump mailin voting cheap drug high stake america risky bet china trump give putin couple sign ukraine peace underway cnn trump suggests chicago next federal crime crackdown followed new york cbs news president donald trump plan crime crackdown chicago similar dc national guard troop soon carry weapon capital national guard troop soon carry weapon capital national guard troop soon carry weapon capital national guard troop soon carry weapon capital national guard troop soon carry weapon capital national guard troop soon carry weapon capital national guard troop soon carry weapon capital national guard troop soon carry weapon capital court ruling cdc staff laid jury selection taking randolph csc trial mayor trump president fixates local crime asphalt lamppost latest news fbi searching john boltons office george mason illegally used race hiring department education find george mason illegally used race hiring department education find judge ordered alligator alcatraz florida wind operation happens world cup draw washington kennedy center trump kamala harris take day book tour los angeles california gov gavin newsoms national profile soar latest trump fight risk california gov gavin newsoms national profile soar latest trump fight risk california gov gavin newsoms national profile soar latest trump fight risk newsoms profile soar trump redistricting fight california gov gavin newsoms national profile soar latest trump fight risk california gov gavin newsoms national profile soar latest trump fight risk california gov gavin newsoms national profile soar latest trump fight risk lake lynn answer ferc raise possibility entry fee cheat lake park people officially became citizen new york fair funeral owner stashed nearly decaying body set sentenced new york federal police crime crackdown dc chicago trump trump praise missouri republican considering redistricting bolton investigated classified document politics vp vance nbc community patrol confronts officer height elementary school parking lot stitt take aim tulsa mayor decision prosecute crime tribal court trump tariff reduce deficit trillion next decade cbo report rusty apply receive payment trump hell extending tiktok shutdown deadline trump hell extending tiktok shutdown deadline trump hell extending tiktok shutdown deadline trump hell extending tiktok shutdown deadline uk diplomat receives warning illegal fishing jd vance mit global collapse warning revisited humanity enters makeorbreak decade chicago next national guard theyre screaming trump san carlos lastminute commissioner item henderson accepting application addition veteran memorial wall trump reacts canada reversing retaliatory tariff take white house erik lyle menendez walk free prison brother parole denied family fight desantis fire dem decries florida move ditch lgbt rainbow color crosswalk orlando hegseth authorizes national guard carry gun washington dc technology summarybrief pm trump astonishingly deluded putin trump demand apology george mason president diversity new york air force underwent massive stress test fight highend war pacific uk diplomat warning illegal fishing vice president national guard troop washington armed hegseth matt fleming assembly democrat came embrace gerrymandering passing baton europe donald trump nobel peace prize asking eric wanting mexican vacation friend included son beware skeeters malary asking eric backing trip friend son energy transition crossroad south korea journey resilience navy drone effort arent wellbut neither china pa budget stall take break cycle delay carney travel germany next deepen tie canada learn english customer berates georgian nyc cafe owner everyones coming defense teaching fact answer indoctrination gavin newsoms redistricting gambit presidential audition policy plan fifa world cup draw take place kennedy center trump announces tension flare texas house panel hears bathroom bill year trump message dc criminal democrat dont mess apps working solve epidemic loneliness expect ussouth korea summit planned parenthood sue south carolina medicaid ban certain local voice oppose gov newsoms redistricting campaign cracker barrel new logo sucksand wokeness idiot ct governor directs flag halfstaff saturday employee fatally injured job trump hell congress b dc improvement letter taxpayer genocide trump putin attend north america world cup heated forth chris rufo conservatism jonah goldberg agrees debate homeowner oppose plan fencing dune hollywood beach trump putin attend north america world cup california ab stall senate amid parental opposition trump putin attend north america world cup trump putin attend north america world cup california governor signed redistricting plan happens next trump photo putin mailed alaska summit president warns better happy peace russia ukraine attack policy review committee recap august james jim mcgregor trump chicago next dcstyle federal law enforcement operation judge ordered alligator alcatraz florida wind operation happens judge ordered alligator alcatraz florida wind operation happens judge ordered alligator alcatraz florida wind operation happens judge ordered alligator alcatraz florida wind operation happens judge ordered alligator alcatraz florida wind operation happens judge ordered alligator alcatraz florida wind operation happens shiba inu shib taking longer expected reach new high pepe coin pepe coin outperform investing ozak ai ethereumbased ai token presale lead millionaire status btc eth hit ath cadence bank million stock holding texas instrument incorporated txn jpmorgan chase co jpm share sold rbo co llc hoka shoe sale low bondi clifton trump administration halt construction revolution wind mass citing national security new brewery tap corydons dora ordinance excitement british columbia investment management corp sell share alphabet goog british columbia investment management corp raise holding broadcom avgo air canada passenger eligible reimbursement flight cancelled canada grab safe djia dividend bargain index hit alltime high nextgen pick best cryptos buy today arctic pablos cex listing driving maximum gain potential twothirds river trash plastic research fastfood chain lock meal fight inflation newsguild organizing surge medium worker fuel grassroots militancy tech ceo urge dignity billion shift worker amid automation lowes target pro total strategy amid sale dip inflation european postal service halt shipment trump tariff china stock surge defies weak economy raising fear another bust analyst waste management nysewm announces quarterly dividend evans council approves ballot language permanent road tax bet bonus code orl bonus seahawks v packer raider v cardinal solana whale rotate capital layer brett analyst deliver x gain next year whale choosing meme coin best crypto buy instead dogecoin doge shiba sol strengthens institutional demand xrp jump whale action blockdags forecast draw buyer phoenix wealth advisor sell share air product chemical apd btc climbed global money fed chair signaled rate cut cointelegraph heritage wealth partner llc buy share meta platform meta palantir technology nasdaqpltr insider ryan taylor sell share palantir technology nasdaqpltr insider ryan taylor sell share stock promising retail stock eye august jpmorgan chase co jpm biondo investment advisor llcs largest immigration boosted europe economy pandemic ecbs lagarde immigration boosted europe economy pandemic ecbs lagarde immigration boosted europe economy pandemic ecbs lagarde trump appeal fraud case likely total victory trump appeal fraud case likely total victory baby boomer turned meme stock trading thrilling hobby calling absolutely gambling trump appeal fraud case likely total victory weatherproof storage shed wayfairs labor day blowout sale bank america nysebac hit new month high whats next invesco qqq qqq share purchased haverford trust co cardano price prediction ada eye new high yet lowcap coin x upside beltway buzz august apg asset management nv acquires share intuitive surgical isrg pfizer pfe share sold apg asset management nv visa foreign trucker politics deadly florida crash best amazon deal shop save trump halt work new england offshore wind project thats nearly complete trump halt work new england offshore wind project thats nearly complete bitcoin btc price retrace run kk ripple xrp coin aiming high cryptos next altcoin crypto shine xrp fall best gift digital artist trump halt work nearly complete new england offshore wind project waste management wm share acquired groupe la francaise union pacific corporation unp share purchased kestra advisory service llc haverford trust co sell share unitedhealth incorporated unh waste management wm share sold van hulzen asset management llc groupe la francaise purchase share walmart wmt phoenix wealth advisor trim cisco system csco bahl gaynor increase stake taiwan semiconductor manufacturing company tsm best best bahl gaynor sell share mcdonalds corporation mcd chicago mess trump vow national guard crackdown layer brett dubbed pepe early momentum outpaces early doge shib launch hooter bankruptcy prompt rebrand tacky familyfriendly depot cheapest tool set worth buying user trump halt work new england offshore wind project thats nearly complete douglas winthrop advisor llc sell share pepsico pep caitlin john llc holding invesco qqq qqq british columbia investment management corp buy share procter gamble company pg penticton council willing work art gallery layoff announced penticton steam locomotive family save money backtoschool season northwest minnesota foundation issue million grant loan quarter iea reinstated business usual scenario business accelerator academy start september help build worldclass entrepreneur dogecoin price target september analyst x gain belong new lowcaps solana reach better crypto buy blockdags presale referral reward shift focus xrp rally eth market issue trump halt work new england offshore wind project thats nearly complete yahoocom trump halt work new england offshore wind project thats nearly complete trump halt work new england offshore wind project thats nearly complete ai bubble fear spark tech stock slide crash warning rise bet mlb player prop pick odds aug garrett crochet among best bet smartleaf asset management llc million stock holding mastercard incorporated walmart nysewmt issue fy earnings guidance biondo investment advisor llc million stake unitedhealth incorporated unh cadence bank sell share american express company axp forest avenue capital management lp boost holding vistra corp vst european post suspend delivery trumpera tariff biondo investment advisor llc acquires share amgen amgn svb wealth llc lower stock blackrock blk svb wealth llc sell share air product chemical apd air product chemical apd share sold british columbia investment management corp svb wealth llc sell share air product chemical apd lionshead wealth management llc holding illinois tool work itw biondo investment advisor llc increase stock holding duke energy corporation duk kruse dia director latest pentagon shakeup cringe watch zohran mamdani plan nyc scavenger hunt prize youre mugged subway cu colorado spring campus thought avoid trump education crackdown happened cu colorado spring campus thought avoid trump education crackdown happened cu colorado spring campus thought avoid trump education crackdown happened justice department release transcript interview ghislaine maxwell kilmar abrego garcia freed tennessee jail rejoin family maryland await trial greene issue scathing rebuke condition gaza silent israel vow open gate hell gaza chilling warning famine grip region seek deport kilmar abrego garcia uganda refused plea offer smuggling case seek deport kilmar abrego garcia uganda refused plea offer smuggling case kevin oleary sound alarm rich kid upbringing become sea mediocrity disaster dhs signal next bolton fbi raid expect lioness center hall battered scandal dnc vote israel arm embargo set democratic party course palestine trump ran promise revenge making good trump ran promise revenge making good trump ran promise revenge making good trump ran promise revenge making good trump ran promise revenge making good trump ran promise revenge making good trump ran promise revenge making good seek deport abrego garcia uganda hampton county law enforcement ramp duo patrol trump administration considering deporting kilmar abrego garcia uganda lawyer secretariat jockey mourned maine canada dunkin customer warns receipt spotting wellness fee national guard roll linked trump crime crackdown wh redistricting war texas california jolt midterm politico asking eric longer invited shared family holiday meal upcoming wedding redistricting war poised explode california texas move la consequential karen bass earns epic ratio claim recovery fastest history redistricting war texas california jolt midterm texas abbott promise quick signature redistricting plan following overnight senate vote ghislaine maxwell absolves trump everyone else doj interview conservative activist slam cracker barrel company left reeling logo redesign south korea japan agree boost tie challenge mount kilmar abrego garcia released custody el salvador truck driver crash center trump administration feud newsom denied bond explain low dem party polling look awesome duo newsom swalwell immigration boosted europe economy pandemic ecbs lagarde immigration boosted europe economy pandemic ecbs lagarde immigration boosted europe economy pandemic ecbs lagarde immigration boosted europe economy pandemic ecbs lagarde immigration boosted europe economy pandemic ecbs lagarde seek deport kilmar abrego garcia uganda refused plea offer smuggling case trump look chicago next federal crackdown wall street journal giuffre family outraged doj interview ghislaine maxwell giuffre family outraged doj interview ghislaine maxwell giuffre family outraged doj interview ghislaine maxwell giuffre family outraged doj interview ghislaine maxwell giuffre family outraged doj interview ghislaine maxwell giuffre family outraged doj interview ghislaine maxwell giuffre family outraged doj interview ghislaine maxwell university oregon concludes law review discriminated perceived national origin israeli author trump hail new texas electoral map aimed keeping grip congress trump hail new texas electoral map aimed keeping grip congress trump hail new texas electoral map aimed keeping grip congress trump hail new texas electoral map aimed keeping grip congress trump hail new texas electoral map aimed keeping grip congress trump hail new texas electoral map aimed keeping grip congress trump hail new texas electoral map aimed keeping grip congress trump hail new texas electoral map aimed keeping grip congress trump hail new texas electoral map aimed keeping grip congress trump hail new texas electoral map aimed keeping grip congress redistricting give party edge election redistricting give party edge election democrat mock jd vance cardboard charisma push unpopular budget bill opinion mayo pete buttigieg find seasoning happened ambition bay restoration guest commentary kilmar abrego garcia threatened deportation uganda larimer county restaurant inspection aug kilmar abrego garcia threatened deportation uganda kilmar abrego garcia threatened deportation uganda judge block trump cutting funding county denver sanctuary policy internet tax freedom act preempt new york imposition tax fbi target john boltons office trump smart guy unpatriotic guy inside facility training recruit take trump deportation goal inside facility training recruit take trump deportation goal inside facility training recruit take trump deportation goal inside facility training recruit take trump deportation goal rachel bitecofer warns bolton start trump rest inside facility training recruit take trump deportation goal inside facility training recruit take trump deportation goal inside facility training recruit take trump deportation goal china russia new strategic bomber inside facility training recruit take trump deportation goal inside facility training recruit take trump deportation goal zelenskyy security guarantee ukraine ready soon bill maher applauds gavin newsom mocking donald trump funny floridarun alligator alcatraz violates law aclu russia announces support venezuela defend sovereignty amid growing military tension united gianno caldwell mull senate bid chicagoans begging change crime woe trump threatens chicago next national guard invasion cnn analyst pinpoint weirdest part ghislaine maxwell simply bizarre doj interview cnn analyst pinpoint weirdest part ghislaine maxwell simply bizarre doj interview owl eye liberty memory epstein suicide trump clinton takeaway ghislaine maxwell transcript israel engineer famine gaza st century learned ghislaine maxwell doj interview texas gov abbott hell swiftly sign redistricting map lawmaker approve jeff bezos felt icky taken share amazon didnt feel good smart money strategy pro buy crypto market crash radioactive shrimp update walmart store brand brand recalled european postal service suspend shipment package tariff european postal service suspend shipment package tariff european postal service suspend shipment package tariff european postal service suspend shipment package tariff european postal service suspend shipment package tariff european postal service suspend shipment package tariff winning powerball ticket sold western new york sp hasnt yielded little since dotcom bubble investor motley fool ranked biggest financial stock pick best investment mezcal producer preserve traditional method demand liquor grows european postal service suspend shipment package tariff kpop demon hunter give netflix boxoffice curry join bank holiday sale bonanza epic deal event best offer id buy self driving taxi coming nyc waymo av testing permit mashable rosen leading law firm encourages fiserv investor secure counsel important rosen leading law firm encourages fiserv investor secure counsel important rosen leading law firm encourages fiserv investor secure counsel important rosen leading law firm encourages fiserv investor secure counsel important rosen leading law firm encourages fiserv investor secure counsel important deadline security class action fi cream sold walmarts across recalled due undeclared allergen gamestop purchase turned bitcoin jackpot cream sold walmarts across recalled due undeclared allergen fox business prediction lucid sale soar next year happens solar executive warn trump attack renewables lead power crunch spike electricity price pueblo county listing less money july median price prediction trilliondollar artificial intelligence ai stock strike megadeal wall street isnt ready cold wallet cashback utility presale pricing create upside case chainlink shiba inu struggle maintenance compliance burden viability hopi water treatment system ethereum trouble xrp breakout buyer turn blockdag earn referral reward acting executor lucrative job word national guard troop force multiplier homan little pepe crypto price prediction lilpepe good investment longterm holder aim invest invesco qqq etf million retirement audit federal spending moses lake school district blockchain stock worth watching august owner scale golden mile shopping center redevelopment rosen global investor counsel encourages easterly rocmuni high income municipal bond fund comerica bank lower stake alphabet goog trump tap airbnb cofounder st government design head lead web overhaul trump tap airbnb cofounder st government design head lead web overhaul fox business offgrid living next new real estate trend application rural mortgage skyrocket rosen global investor counsel encourages altimmune investor secure counsel rosen global investor counsel encourages altimmune investor secure counsel rosen global investor counsel encourages altimmune investor secure counsel epstein accuser virginia giuffre wrote memoir month death coming powell warning signal unemployment claim jump highest year cardano price outlook ada reach trumprelated defi platform world liberty financial debut wlfi token ethereum mainnet rosen global investor counsel encourages altimmune investor secure counsel important deadline security class action alt best meme coin presale stampede loading whitelist labubull watch moon without backtoschool deal tellos unlimited plan cell service per month month nexus gold cvenxs stock price whats next mason resource cvellg stock price mason resource cvellg trading happened national guard troop force multiplier homan freedom investment management purchase share procter gamble company pg ascent llc raise stock holding ameri</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2018,6 +2018,42 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="B45" t="n">
+        <v>6465.93994140625</v>
+      </c>
+      <c r="C45" t="n">
+        <v>6468.3701171875</v>
+      </c>
+      <c r="D45" t="n">
+        <v>6429.2099609375</v>
+      </c>
+      <c r="E45" t="n">
+        <v>6435.490234375</v>
+      </c>
+      <c r="F45" t="n">
+        <v>4867680000</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.0041339951911349</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>top altcoins to buy now analyst pick with x potential in the next bull run south bay lawmaker new push to keep california highspeed rail project on track blackrock canada announces final august cash distribution for the ishares premium money market etf integral metal announces closing of private placement offering david gardner on rule breaker investing ibd live qa stock list for monday aug elon musk accuses apple and openai of stifling ai competition in antitrust lawsuit elon musk accuses apple and openai of stifling ai competition in antitrust lawsuit elon musk accuses apple and openai of stifling ai competition in antitrust lawsuit modern farmhouse in henderson neighborhood listed for m dust off your keyboard this fall get a powerful canless duster for off can in nuscale power stock turn into by ap sport summarybrief at pm edt top u city for job growth in and why it matter for homebuyers top u city for job growth in and why it matter for homebuyers top u city for job growth in and why it matter for homebuyers top u city for job growth in and why it matter for homebuyers smart altcoin investment for august with huge price prediction upside american natural gas demand poised for historic high in if youd invested in oklo stock last year here how much money youd have today medium advisory infrastructure announcement in surrey roches u subsidiary genentech break ground on stateoftheart manufacturing facility in north carolina usa transamerica welcome jason frain a head of retirement solution dogecoin news today doge face critical support at whats next best opensource datasets for your next project canadian u official are to meet after canada remove some tariff protecting main street money strengthening mississippi bank sentencing set for man who admitted swapping illegal chinese cargo through port of la long beach sentencing set for man who admitted swapping illegal chinese cargo through port of la long beach misuta chow to close after year top venture capital crms to elevate your investment strategy in new tec open new worthington showroom clark county resident with bad credit on the rise joint development district could generate income for perrysburg township ohio millionaire politician a stunning wealth gap between u and our representative bank and sole proprietor three bill would protect california worker from ai management but will cost stand in the way sevenyear car loan are becoming normal a car price stay high white castle charge diner jawdropping for combo a store make annoying drivethru change bunch of jerk research show how brand can benefit from reclaiming insult where you are and where youve been food industry lobby for tariff exemption on seafood fresh produce a it warns price could spike tariff bingo is tough texas manufacturer sweat trump tariff high interest rate cbo say tariff could raise trillion over next decade raise price cbo say tariff could raise trillion over next decade raise price cbo say tariff could raise trillion over next decade raise price watch cracker barrel face backlash over rebranding car are so expensive that buyer need year loan court denies beverage company preliminary injunction in trade secret case citing conflicting evidence tesla could fall tomorrow and i wouldnt buy a share say top fund manager blizzard cofounder game startup dreamhaven struggle amid industry glut july newhome sale top expectation emini sp rally test gann and fibonacci resistance into august cycle crest southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat southwest airline will require larger passenger to purchase an extra seat levi korsinsky reminds shareholder of a lead plaintiff deadline of september in lineage inc lawsuit line intel say trump plan for u stake in company pose business risk the washington post best gaming mouse with side button to buy in kaldvik a kldvk q webcast result august at cet why zeroclick search is forcing business to pivot how to implement your oem maintenance schedule into your eld so you never miss a critical interval netflixs kpop demon hunter top box office despite fewer screen shorter run rep thomas h kean jr liberty broadband corporation nasdaqlbrdk share rep ritchie torres sell equity lifestyle property inc nyseels share arista network nyseanet stock acquired sen angus s king jr bank of america nysebac share acquired sen angus s king jr pepsico nasdaqpep share unloaded rep ritchie torres equity residential nyseeqr stock unloaded rep ritchie torres rep ritchie torres sell are management corporation nyseares stock sen angus s king jr purchase share of on holding ag nyseonon rep ritchie torres sell colgatepalmolive company nysecl share eaton nyseetn stock unloaded rep ritchie torres sen angus s king jr purchase share of lowes company inc nyselow life without most of the fcpa six month in gas price back up gas pice back up european carrier pause some shipment to u a they prepare for end of de minimis exemption city of charlotte to give out free air conditioning unit we now know which crime are aok with beloved socialist candidate zohran mamdani for now wild video show mountain lion walking right through family front door in california stock waver on wall street after last week rally stock waver on wall street after last week rally stock waver on wall street after last week rally stock waver on wall street after last week rally los angeles area unemployment claim surged following january wildfire report walmart fire vp over kickback lay off hb worker little pepe lilpepe shine a best meme coin for attracting dogecoin doge holder with prospect this quest diagnostics analyst is no longer bullish here are top downgrade for monday tech ipo darling give up some gain tharimmune thar stock is surging monday whats going on usdchf hit new high a usd strengthens eye further gain ahead eurusd reach target tezos is leveling the playing field giving everyone access to uranium the commodity powering the energy of the future tokenized equity in the crosshairs of global stock exchange what happened elon musk xai drop public benefit status echoing openai shift trump want to prosecute flag burner the supreme court ha already said thats illegal dont mourn the death of palestinian journalist talkin bout a revolution greenwood cemetery commemorates the battle of brooklyn fema worker warn agency at risk of hurricane katrinatype failure cnn politics trump say he could rename department of defense to department of war soon trump say he could rename department of defense to department of war soon trump want to meet north korea kim this year he tell south korea trump get a ridiculous badge for turning dc into a police state the alliance of authoritarianism and oligarchy show it hand in dc flower the tiresome tale of amanda knox campaigner want to change the world map to show africa is bigger campaigner want to change the world map to show africa is bigger campaigner want to change the world map to show africa is bigger university of florida pick an interim president after last choice wa rejected university of florida pick an interim president after last choice wa rejected trump hegseth float renaming defense department to department of war trump hegseth float renaming defense department to department of war military time kilmar abrego garcia detained by ice in baltimore face deportation effort kilmar abrego garcia detained by ice in baltimore face deportation effort kilmar abrego garcia detained by ice in baltimore face deportation effort intels role in the uschina chip war analysis trump tortured history of legally targeting his foe cnn politics alleged retaliation by high school coach against athlete lead to first amendment claim house republican seek review of dc crime data dems issue threat of maryland governor redrawing congressional map yeah about that trump executive order prohibiting flag burning is unconstitutional trump predicts conclusive ending to gaza war within three week prior lake teacher lawsuit claim district violated her free speech right over deportation social post venezuela release political prisoner a u ramp up pressure with naval armada theyre going to be brought down trump vow to go after bidens adviser theyre going to be brought down trump vow to go after bidens adviser israel express regret after outcry over hospital strike city pass controversial ordinance targeting homeless activity equity research analyst price target change for august th abo ahh amgn apld avgo bj bke cbre cogt coty editorial jail commissary fund in the spotlight trump say nbc abc should lose license over news coverage richard grenell politely make katie couric look like the intolerant hag she really is and it glorious trump threatens nbc and abc here why he cant revoke their license trump meet south korean president industrial leader in washington sen angus s king jr buy alphabet inc nasdaqgoogl stock rep ritchie torres sell are management corporation nyseares stock sen angus s king jr sell thermo fisher scientific inc nysetmo stock kinder morgan nysekmi share unloaded rep ritchie torres rep ritchie torres sell off share of cocacola company the nyseko rep ritchie torres sell qualcomm incorporated nasdaqqcom stock eaton nyseetn stock unloaded rep ritchie torres sen angus s king jr purchase share of blackstone inc nysebx denton isds communication of student stabbing criticized by parent exmaga rep dish out advice on crybaby trump after social medium rant south park escalates it war against trump in a brutal episode donna brazile dismisses gavin newsoms trump trolling on social medium say these are serious time the hidden crisis of black land loss in the wake of slavery the excerpt west virginia national guard troop in dc now authorized to carry weapon trump say he would like to have another meeting with kim jong un trump sign order cracking down on cashless bail slapping federal charge on dc suspect philadelphia mass transit cut foreshadow possible similar move by other agency across u the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit the latest trump host south korea new leader lee jae myung for a trade summit ohio sued over proofofcitizenship rule for voter registration robert f kennedy jr back morrisey on west virginia school vaccine exemption who cashing in on trump immigration crackdown it not the american people nor the federal or state government democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james democratic ag decry political retaliation against james trump battle with u senate judiciary grassley over homestate pick for judge a federal grant termination grow award recipient should be proactive but also preserve their right trump sign executive order directing doj to prosecute flag burning julio cesar chavez jr released from mexican maximumsecurity prison ahead of trial for alleged cartel tie face the nation no threat to the public situation on catawba river in belmont end peacefully epstein accuser to release unsparing memoir with disturbing detail axios trump dc takeover is a modern day rebirth of a nation hundred from across pa protest in philipsburg against the moshannon valley processing center gillette senator accuses city council of violating the public trust on nuclear issue trump sign order aimed at ending cashless bail policy opening date announced for controversial overnight homeless shelter in portland pearl district bridge cost historical marker on agenda for rome common council chief of war episode recap sled dead redemption asking eric i meant no harm by the compliment i paid a friend california new housing tax will further our housing crisis california new housing tax will further our housing crisis california new housing tax will further our housing crisis california new housing tax will further our housing crisis trump threatens lawsuit over centuryold senate tradition delaying his nominee hispanic tiktoker arrested by ice in los angeles during live stream democratic national committee kick off summer meeting kansa house speaker want to slash million from state budget target medicaid for cut some fema staff call out trump cut in public letter of dissent some fema staff call out trump cut in public letter of dissent some fema staff call out trump cut in public letter of dissent some fema staff call out trump cut in public letter of dissent let meet salvadoran man in trump immigration row to be deported to uganda official salvadoran man in trump immigration row to be deported to uganda official</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>altcoins buy analyst pick x potential next bull run south bay lawmaker new push california highspeed rail project track blackrock canada announces final august cash distribution ishares premium money market etf integral metal announces closing private placement offering david gardner rule breaker investing ibd qa stock list monday aug elon musk accuses apple openai stifling ai competition antitrust lawsuit elon musk accuses apple openai stifling ai competition antitrust lawsuit elon musk accuses apple openai stifling ai competition antitrust lawsuit modern farmhouse henderson neighborhood listed dust keyboard fall powerful canless duster nuscale power stock turn sport summarybrief pm job growth matter homebuyers job growth matter homebuyers job growth matter homebuyers job growth matter homebuyers smart altcoin investment august price prediction upside american natural gas demand poised historic high youd invested oklo stock year money youd today medium advisory infrastructure announcement surrey roches subsidiary genentech break ground stateoftheart manufacturing facility north carolina usa transamerica welcome jason frain head retirement solution dogecoin news today doge face critical support whats next best opensource datasets next project canadian meet canada remove tariff protecting main street money strengthening mississippi bank sentencing set man admitted swapping illegal chinese cargo port la beach sentencing set man admitted swapping illegal chinese cargo port la beach misuta chow close year venture capital crms elevate investment strategy new tec open new worthington showroom clark county resident bad credit rise joint development district generate income perrysburg township ohio millionaire politician stunning wealth gap representative bank sole proprietor bill protect california worker ai management cost stand sevenyear car loan becoming normal car price stay high white castle charge diner jawdropping combo store annoying drivethru change bunch jerk research brand benefit reclaiming insult youve food industry lobby tariff exemption seafood fresh produce warns price spike tariff bingo tough texas manufacturer sweat trump tariff high interest rate cbo tariff raise trillion next decade raise price cbo tariff raise trillion next decade raise price cbo tariff raise trillion next decade raise price watch cracker barrel face backlash rebranding car expensive buyer year loan court denies beverage company preliminary injunction trade secret case citing conflicting evidence tesla fall tomorrow wouldnt buy share fund manager blizzard cofounder game startup dreamhaven struggle amid industry glut july newhome sale expectation emini sp rally test gann fibonacci resistance august cycle crest southwest airline require larger passenger purchase extra seat southwest airline require larger passenger purchase extra seat southwest airline require larger passenger purchase extra seat southwest airline require larger passenger purchase extra seat southwest airline require larger passenger purchase extra seat southwest airline require larger passenger purchase extra seat southwest airline require larger passenger purchase extra seat southwest airline require larger passenger purchase extra seat levi korsinsky reminds shareholder lead plaintiff deadline september lineage lawsuit line intel trump plan stake company pose business risk washington post best gaming mouse button buy kaldvik kldvk q webcast august cet zeroclick search forcing business pivot implement oem maintenance schedule eld never miss critical interval netflixs kpop demon hunter box office fewer screen shorter run rep thomas h kean jr liberty broadband corporation nasdaqlbrdk share rep ritchie torres sell equity lifestyle property nyseels share arista network nyseanet stock acquired sen angus king jr bank america nysebac share acquired sen angus king jr pepsico nasdaqpep share unloaded rep ritchie torres equity residential nyseeqr stock unloaded rep ritchie torres rep ritchie torres sell management corporation nyseares stock sen angus king jr purchase share holding ag nyseonon rep ritchie torres sell colgatepalmolive company nysecl share eaton nyseetn stock unloaded rep ritchie torres sen angus king jr purchase share lowes company nyselow life without fcpa month gas price gas pice european carrier pause shipment prepare end de minimis exemption charlotte give free air conditioning unit crime aok beloved socialist candidate zohran mamdani wild video mountain lion walking family front door california stock waver wall street rally stock waver wall street rally stock waver wall street rally stock waver wall street rally los angeles area unemployment claim surged following january wildfire report walmart fire vp kickback lay hb worker little pepe lilpepe shine best meme coin attracting dogecoin doge holder prospect quest diagnostics analyst longer bullish downgrade monday tech ipo darling give gain tharimmune thar stock surging monday whats usdchf hit new high usd strengthens eye gain ahead eurusd reach target tezos leveling playing field giving everyone access uranium commodity powering energy future tokenized equity crosshairs global stock exchange happened elon musk xai drop public benefit status echoing openai shift trump prosecute flag burner supreme court thats illegal dont mourn death palestinian journalist talkin bout revolution greenwood cemetery commemorates battle brooklyn fema worker warn agency risk hurricane katrinatype failure cnn politics trump rename department defense department war soon trump rename department defense department war soon trump meet north korea kim year south korea trump ridiculous badge turning dc police alliance authoritarianism oligarchy dc flower tiresome tale amanda knox campaigner change world map africa bigger campaigner change world map africa bigger campaigner change world map africa bigger university florida pick interim president choice rejected university florida pick interim president choice rejected trump hegseth float renaming defense department department war trump hegseth float renaming defense department department war military kilmar abrego garcia detained baltimore face deportation effort kilmar abrego garcia detained baltimore face deportation effort kilmar abrego garcia detained baltimore face deportation effort intels role uschina chip war analysis trump tortured history legally targeting foe cnn politics alleged retaliation high school coach athlete lead amendment claim house republican seek review dc crime data dems issue threat maryland governor redrawing congressional map yeah trump executive order prohibiting flag burning unconstitutional trump predicts conclusive ending gaza war prior lake teacher lawsuit claim district violated free speech deportation social post venezuela release political prisoner ramp pressure naval armada theyre brought trump vow bidens adviser theyre brought trump vow bidens adviser israel express regret outcry hospital strike pas controversial ordinance targeting homeless activity equity research analyst price target change august abo ahh amgn apld avgo bj bke cbre cogt coty editorial jail commissary fund spotlight trump nbc abc lose license news coverage richard grenell politely katie couric look intolerant hag glorious trump threatens nbc abc cant revoke license trump meet south korean president industrial washington sen angus king jr buy alphabet nasdaqgoogl stock rep ritchie torres sell management corporation nyseares stock sen angus king jr sell thermo fisher scientific nysetmo stock kinder morgan nysekmi share unloaded rep ritchie torres rep ritchie torres sell share cocacola company nyseko rep ritchie torres sell qualcomm incorporated nasdaqqcom stock eaton nyseetn stock unloaded rep ritchie torres sen angus king jr purchase share blackstone nysebx denton isds communication student stabbing criticized parent exmaga rep dish advice crybaby trump social medium rant south park escalates war trump brutal episode donna brazile dismisses gavin newsoms trump trolling social medium serious hidden crisis black land loss wake slavery excerpt west virginia national guard troop dc authorized carry weapon trump another meeting kim jong un trump sign order cracking cashless bail slapping federal charge dc suspect philadelphia mass transit cut foreshadow possible similar move agency across latest trump host south korea new lee jae myung trade summit latest trump host south korea new lee jae myung trade summit latest trump host south korea new lee jae myung trade summit latest trump host south korea new lee jae myung trade summit latest trump host south korea new lee jae myung trade summit ohio sued proofofcitizenship rule voter registration robert f kennedy jr morrisey west virginia school vaccine exemption cashing trump immigration crackdown american people federal government democratic ag decry political retaliation james democratic ag decry political retaliation james democratic ag decry political retaliation james democratic ag decry political retaliation james democratic ag decry political retaliation james democratic ag decry political retaliation james trump battle senate judiciary grassley homestate pick judge federal grant termination grow award recipient proactive preserve trump sign executive order directing doj prosecute flag burning julio cesar chavez jr released mexican maximumsecurity prison ahead trial alleged cartel tie face nation threat public situation catawba river belmont end peacefully epstein accuser release unsparing memoir disturbing detail axios trump dc takeover modern day rebirth nation across pa protest philipsburg moshannon valley processing center gillette senator accuses council violating public trust nuclear issue trump sign order aimed ending cashless bail policy opening date announced controversial overnight homeless shelter portland pearl district bridge cost historical marker agenda rome common council chief war episode recap sled dead redemption asking eric meant harm compliment paid friend california new housing tax housing crisis california new housing tax housing crisis california new housing tax housing crisis california new housing tax housing crisis trump threatens lawsuit centuryold senate tradition delaying nominee hispanic tiktoker arrested los angeles stream democratic national committee kick summer meeting kansa house speaker slash million budget target medicaid cut fema staff call trump cut public letter dissent fema staff call trump cut public letter dissent fema staff call trump cut public letter dissent fema staff call trump cut public letter dissent meet salvadoran man trump immigration row deported uganda salvadoran man trump immigration row deported uganda</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2054,6 +2054,42 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45896</v>
+      </c>
+      <c r="B46" t="n">
+        <v>6481.39990234375</v>
+      </c>
+      <c r="C46" t="n">
+        <v>6487.06005859375</v>
+      </c>
+      <c r="D46" t="n">
+        <v>6457.83984375</v>
+      </c>
+      <c r="E46" t="n">
+        <v>6462.259765625</v>
+      </c>
+      <c r="F46" t="n">
+        <v>4143680000</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.0023909843081744</v>
+      </c>
+      <c r="H46" t="n">
+        <v>1</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>british american tobacco cfo step down abruptly hostess ding dong pulled over mold concern trump cant fire jerome powell so he going after the rest of the fed poverty in mass it about race and place the republican editorial democrat demand trump resume a nearly completed major wind project near rhode island democrat demand trump resume a nearly completed major wind project near rhode island democrat demand trump resume a nearly completed major wind project near rhode island democrat demand trump resume a nearly completed major wind project near rhode island portland mercury owner buy the chicago reader new era unlocked taylor swift and travis kelce announce engagement how brand have shifted digital spend in how brand have shifted digital spend in how brand have shifted digital spend in how brand have shifted digital spend in how brand have shifted digital spend in extended comment period for benson aluminum recycling plant xrp news today xrp face resistance a whale activity and xrp card boost sentiment zenith netzero gain scc accreditation a iso validation and verification body public hearing slated on draft ny energy plan daniel luries family zoning plan is anything but crypto investor eye lyno ai for s biggest roi opportunity meme coin that will turn into faster than dogecoin doge can soar x and shiba inu shib x saudi arabia and india top the list of russia fuel oil buyer alibaba debut avatar update to it video ai model why the u government is not the savior intel need ethereum price uniswap latest news aave staking option remittix announces major cex listing keanetech maple bitflow why maple bitflow trading platform is being touted a a gamechanger by industry insider read canada trading report justice alito report no gift trip and an active stock portfolio st louis man sentenced to year for seconddegree murder at dutchtown gas station new report these are the most popular potato chip brand in each state courtney panik redefines hr for corporate transformation ai race redefines productivity palantir may squeeze short study say ai chatbots need to fix suicide response a family sue over chatgpt role in boy death study say ai chatbots need to fix suicide response a family sue over chatgpt role in boy death study say ai chatbots need to fix suicide response a family sue over chatgpt role in boy death icu urge cm to update ceus reimbursement citing clinical benefit for patient and healthcare system jack smith legal team fire back against ethic complaint the new york time official opening of phase iii of villa forestville more social and affordable housing unit for senior in forestville peter friedlander departing netflix jinny howe upped to head of u canada scripted series economist warns agi in year could drive wage to zero push ubi trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule trump administration threatens some funding for state for not enforcing trucker english rule how corporate gifting can enhance every employee milestone mortgage fraud claim give trump weapon against lisa cook and others edward jones begin layoff including at it headquarters stock market today dow waver after trump move to oust fed governor cook live update the wall street journal donald trump say he want to rebrand his big beautiful bill nbc news vra investor news if you have suffered loss in vera bradley inc nasdaq vra you are embattled fed gov lisa cook say shell sue trump to keep her job new gallup poll show point swing in trump approval rating man arrested after car chase end in crash into wake forest reservoir beam global score major win a u government extends procurement contract kroger shuts door on location for good with more closure on the chopping block after ceo reveals chain future u challenge foreign digital tax with tariff on tech giant dow jones payment giant american express tesla stock in or near buy zone budget cut will hurt west virginia powerball jackpot reach m seventh largest prize in game history stream realty partner triple miami footprint amid rapid florida growth rosen a leading law firm encourages xplr infrastructure lp fka nextera energy partner lp investor to secure counsel before important deadline in security class action xifr nep crypto news today robinhood microstrategy miss sp kraken meet sec trump medium land b deal ion grove rosen a leading law firm encourages snap inc investor to secure counsel before important residential real estate expert nicole curcio share why home are selling fast in hellonation slqt investor have opportunity to lead selectquote inc security fraud lawsuit rosen a leading law firm encourages snap inc investor to secure counsel before important deadline in security class action snap magnolia isd approves m balanced budget including teacher pay raise marketing a lastminute concern a cvcc bond vote loom agristo potato processing project progress in grand fork where american earn six figure without a degree study numerai secures up to m commitment from jpmorgan asset management biggest layoff of are we expecting more huntington beloved restaurant is closing after year on september eli lilly lly prepares for weight loss pill approval after latestage clinical trial tipranks cd v highyield saving account which earns more interest now slqt investor have opportunity to lead selectquote inc security fraud lawsuit bmo unveils plan to invest in it u branch technology a u tariff exemption for small order end friday it a big deal to some shopper and business how to regretproof your home purchase messer partner with u titanium producer to support aerospace growth trk enterprise inc expands market reach with acquisition of summit laydown service inc katy isd adopts b budget despite projected m shortfall for fy niagara tourism spending soar to billion in boosting local economy fed barkin his forecast is for a modest cut in interest rate trump is out to end the fed autonomy here how he trying to get his way arvore declares it july distribution annualized trump tell cracker barrel to ditch it new logo after maga meltdown furniture seller could face additional white house tariff inspirit iot japanese power plant turn saltwater into electricityand it a glimpse into the future walmart slashed off this blackstone burner griddle and itll still deliver before labor day zillow and berkshire hathaway homeservices team up to empower agent supercharge listing using showcase fcp acquires unit district west gable apartment in west miami fl how democrat plan to use federal medicaid cut in midterm messaging why lululemons global expansion could outweigh north america slowdown wichita city council approves budget with first property tax rate cut in decade trump attempted firing of fed governor threatens central bank independence and that isnt good news for sound economic stewardship or battling inflation white house accuses pritzker illinois dems of whining while chicago crime rage embattled fed gov lisa cook say shell sue trump to keep her job business why the advancement of religion a a charitable purpose must be preserved in canada thursday is next opportunity to meet with santa fe mayor haros charged with murder of son monthold emmanuel in riverside county la could see more border patrol agent soon sector chief say conrad black to hold canada together ottawa need a daring strategy milwaukee judge must face charge after motion to dismiss denied israeli protester demand hostage deal a cabinet meet israeli protester demand hostage deal a cabinet meet israeli protester demand hostage deal a cabinet meet hakeem jeffries ripped for noting lisa cook race while slamming trump for trying to fire her who give a flying fruitcake what color she is trump dc crime crackdown could revive death penalty for convicted murderer jack smith legal team fire back against ethic complaint the new york time butler county sheriff within legal right to hold ice detainee civilly ohio ag opinion say yearold democrat make way for rising farleft star after republican got their way with redistricting opinion celeb chef blast confused trump for restaurant claim embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job embattled fed gov lisa cook say shell sue trump to keep her job trump call for death penalty for anyone charged with killing someone in washington dc cook firing take the fed into the unknown democratic party scrap resolution on israel and gaza after fraught debate democratic party scrap resolution on israel and gaza after fraught debate the new york time orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin orthodox archbishop apologizes to anyone pained by his meeting with putin dr congo m rebel resume talk in qatar after renewed violence in east court toss trump lawsuit against maryland judge over u deportation ukrainian woman who fled war stabbed to death at charlotte light rail station democrat latest move on the gaza war spark backlash and backtracking democrat latest move on the gaza war spark backlash and backtracking north myrtle beach election filing period is open here who filed so far cracker barrel cave old country store to bring back old logo after blowback what to know about lisa cook the fed governor who trump say he firing trump team floated energy incentive with russia in sideline ukraine peace talk report five question and expert answer about where the ussouth korea alliance go from here trump asks ntd white house correspondent to share her dc mugging story at cabinet meeting west hartford state legislator join the crowd looking to replace rep john larson taiwan deports japanese man after filming prochina video in taipei the foreigner working for doge politico the foreigner working for doge u envoy israel counterproposal to lebanon disarmament plan coming arizona department of education apologizes to esa parent after some personally identifiable information wa given to local medium including news trump announces name change for department of defense too defensive trump dot threatens to withhold fund from state that dont enforce english requirement for truck driver nbc news bc green party candidate stopping in armstrong for meet and greet trump appointee call out trump administration effort to smear judge court reject trump doj lawsuit against maryland judge detroit school urge judge to halt chickfila construction next door u envoy tell arab journalist in lebanon to be civilised utah ordered to redraw congressional map opening up possible democratic seat video kilmar abrego garcia take word shot at the united state a he escorted through ice facility utah ordered to redraw congressional map opening up possible democratic seat utah ordered to redraw congressional map seat for democrat possible cbs news adam sandler questioned over snl song calling out antisemitic musician trump push to fire fed governor threatens central bank independence and that isnt good news for sound economic stewardship or battling inflation trump attempted firing of fed governor threatens central bank independence and that isnt good news for sound economic stewardship or battling inflation utah judge strike down republican congressional map in gerrymandering case house oversight committee subpoena epstein estate seeking alleged trump note is trump doing a better or worse job than biden here what a new poll found whistleblower say trump official copied million of social security number hhs asks state and territory to remove gender ideology content from sex ed material social security refusing to make payment change after inconvenient law and issue wont be fixed for month exclusive gop chairman think his party ha what it take to beat the purple out of georgia duffy threatens state that dont enforce english language requirement for truck driver duffy threatens state that dont enforce english language requirement for truck driver let talk knoxville back to school police chief aaron fuller he wa shot and killed by a border patrol agent year ago his family still demand justice roadway crack sealing work scheduled to begin wednesday with book and kid in tow this boyle height mom is fighting for her community library she pushed to overturn trump loss in the election now shell help oversee u election security propublica the bb lancer just finished another btf mission can gavin newsoms bold move save the democrat and win in robert f wrobel wisconsin democrat propose new funding for knowlesnelson stewardship grand fork district republican party ready for day window to select state house replacement pa top court official facebook post subject to same righttoknow standard a other record she pushed to overturn trump loss in the election now shell help oversee u election security john bolton mock trump nobel peace obsession in first comment since fbi raid meta to spend ten of million on proai super pac indigenous youth make historic ride down the klamath river lula denounces u decision to revoke visa from brazilian justice minister</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>british american tobacco cfo step abruptly hostess ding dong pulled mold concern trump cant fire jerome powell rest fed poverty mass race place republican editorial democrat demand trump resume nearly completed major wind project rhode island democrat demand trump resume nearly completed major wind project rhode island democrat demand trump resume nearly completed major wind project rhode island democrat demand trump resume nearly completed major wind project rhode island portland mercury owner buy chicago reader new era unlocked taylor swift travis kelce announce engagement brand shifted digital spend brand shifted digital spend brand shifted digital spend brand shifted digital spend brand shifted digital spend extended period benson aluminum recycling plant xrp news today xrp face resistance whale activity xrp card boost sentiment zenith netzero gain scc accreditation iso validation verification body public hearing slated draft ny energy plan daniel luries family zoning plan anything crypto investor eye lyno ai biggest roi opportunity meme coin turn faster dogecoin doge soar x shiba inu shib x saudi arabia india list russia fuel oil buyer alibaba debut avatar update video ai model government savior intel ethereum price uniswap latest news aave staking option remittix announces major cex listing keanetech maple bitflow maple bitflow trading platform touted gamechanger industry insider canada trading report justice alito report gift trip active stock portfolio st louis man sentenced year seconddegree murder dutchtown gas station new report popular potato chip brand courtney panik redefines hr corporate transformation ai race redefines productivity palantir squeeze short study ai chatbots fix suicide response family sue chatgpt role boy death study ai chatbots fix suicide response family sue chatgpt role boy death study ai chatbots fix suicide response family sue chatgpt role boy death icu urge cm update ceus reimbursement citing clinical benefit patient healthcare system jack smith legal team fire ethic complaint new york opening phase iii villa forestville social affordable housing unit senior forestville peter friedlander departing netflix jinny howe upped head canada scripted series economist warns agi year drive wage push ubi trump administration threatens funding enforcing trucker english rule trump administration threatens funding enforcing trucker english rule trump administration threatens funding enforcing trucker english rule trump administration threatens funding enforcing trucker english rule trump administration threatens funding enforcing trucker english rule corporate gifting enhance employee milestone mortgage fraud claim give trump weapon lisa cook others edward jones begin layoff stock market today dow waver trump move oust fed governor cook update wall street journal donald trump rebrand big bill nbc news vra investor news suffered loss vera bradley nasdaq vra embattled fed gov lisa cook shell sue trump job new gallup poll swing trump approval rating man arrested car chase end crash wake forest reservoir beam global score major government extends procurement contract kroger shuts door location good closure chopping block ceo reveals chain future challenge foreign digital tax tariff tech giant dow jones payment giant american express tesla stock buy zone budget cut hurt west virginia powerball jackpot reach seventh largest prize game history stream realty partner triple miami footprint amid rapid florida growth rosen leading law firm encourages xplr infrastructure lp fka nextera energy partner lp investor secure counsel important deadline security class action xifr nep crypto news today robinhood microstrategy miss sp kraken meet sec trump medium land b deal ion grove rosen leading law firm encourages snap investor secure counsel important residential real estate expert nicole curcio share selling fast hellonation slqt investor opportunity lead selectquote security fraud lawsuit rosen leading law firm encourages snap investor secure counsel important deadline security class action snap magnolia isd approves balanced budget teacher pay raise marketing lastminute concern cvcc bond vote loom agristo potato processing project progress grand fork american earn figure without degree study numerai secures commitment jpmorgan asset management biggest layoff expecting huntington beloved restaurant closing year september eli lilly lly prepares weight loss pill approval latestage clinical trial tipranks cd v highyield saving account earns interest slqt investor opportunity lead selectquote security fraud lawsuit bmo unveils plan invest branch technology tariff exemption small order end friday big deal shopper business regretproof purchase messer partner titanium producer support aerospace growth trk enterprise expands market reach acquisition summit laydown service katy isd adopts b budget projected shortfall fy niagara tourism spending soar billion boosting local economy fed barkin forecast modest cut interest rate trump end fed autonomy arvore declares july distribution annualized trump cracker barrel ditch new logo maga meltdown furniture seller face additional white house tariff inspirit iot japanese power plant turn saltwater electricityand glimpse future walmart slashed blackstone burner griddle itll deliver labor day zillow berkshire hathaway homeservices team empower agent supercharge listing showcase fcp acquires unit district west gable apartment west miami fl democrat plan federal medicaid cut midterm messaging lululemons global expansion outweigh north america slowdown wichita council approves budget property tax rate cut decade trump attempted firing fed governor threatens central bank independence isnt good news sound economic stewardship battling inflation white house accuses pritzker illinois dems whining chicago crime rage embattled fed gov lisa cook shell sue trump job business advancement religion charitable purpose must preserved canada thursday next opportunity meet santa fe mayor haros charged murder son monthold emmanuel riverside county la border patrol agent soon sector chief conrad black canada together ottawa daring strategy milwaukee judge must face charge motion dismiss denied israeli protester demand hostage deal cabinet meet israeli protester demand hostage deal cabinet meet israeli protester demand hostage deal cabinet meet hakeem jeffries ripped noting lisa cook race slamming trump fire give flying fruitcake color trump dc crime crackdown revive death penalty convicted murderer jack smith legal team fire ethic complaint new york butler county sheriff legal detainee civilly ohio ag opinion yearold democrat rising farleft star republican got redistricting opinion celeb chef blast confused trump restaurant claim embattled fed gov lisa cook shell sue trump job embattled fed gov lisa cook shell sue trump job embattled fed gov lisa cook shell sue trump job embattled fed gov lisa cook shell sue trump job embattled fed gov lisa cook shell sue trump job trump call death penalty anyone charged killing someone washington dc cook firing take fed unknown democratic party scrap resolution israel gaza fraught debate democratic party scrap resolution israel gaza fraught debate new york orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin orthodox archbishop apologizes anyone pained meeting putin dr congo rebel resume qatar renewed violence east court toss trump lawsuit maryland judge deportation ukrainian woman fled war stabbed death charlotte light rail station democrat latest move gaza war spark backlash backtracking democrat latest move gaza war spark backlash backtracking north myrtle beach election filing period open filed far cracker barrel cave old country store old logo blowback lisa cook fed governor trump firing trump team floated energy incentive russia sideline ukraine peace report expert answer ussouth korea alliance trump asks ntd white house correspondent share dc mugging story cabinet meeting west hartford legislator join crowd replace rep john larson taiwan deports japanese man filming prochina video taipei foreigner working doge politico foreigner working doge envoy israel counterproposal lebanon disarmament plan coming arizona department education apologizes esa parent personally identifiable information local medium news trump announces name change department defense defensive trump dot threatens withhold fund dont enforce english requirement truck driver nbc news bc green party candidate stopping armstrong meet greet trump appointee call trump administration effort smear judge court reject trump doj lawsuit maryland judge detroit school urge judge halt chickfila construction next door envoy arab journalist lebanon civilised utah ordered redraw congressional map opening possible democratic seat video kilmar abrego garcia take word shot united escorted facility utah ordered redraw congressional map opening possible democratic seat utah ordered redraw congressional map seat democrat possible cbs news adam sandler questioned snl song calling antisemitic musician trump push fire fed governor threatens central bank independence isnt good news sound economic stewardship battling inflation trump attempted firing fed governor threatens central bank independence isnt good news sound economic stewardship battling inflation utah judge strike republican congressional map gerrymandering case house oversight committee subpoena epstein estate seeking alleged trump note trump better worse job biden new poll found whistleblower trump copied million social security hhs asks territory remove gender ideology content sex ed material social security refusing payment change inconvenient law issue wont fixed month exclusive gop chairman party take beat purple georgia duffy threatens dont enforce english language requirement truck driver duffy threatens dont enforce english language requirement truck driver knoxville school police chief aaron fuller shot killed border patrol agent year ago family demand justice roadway crack sealing work scheduled begin wednesday book kid tow boyle height mom fighting community library pushed overturn trump loss election shell help oversee election security propublica bb lancer finished another btf mission gavin newsoms bold move save democrat robert f wrobel wisconsin democrat propose new funding knowlesnelson stewardship grand fork district republican party ready day window select house replacement pa court facebook post subject righttoknow record pushed overturn trump loss election shell help oversee election security john bolton mock trump nobel peace obsession since fbi raid meta spend million proai super pac indigenous youth historic ride klamath river lula denounces decision revoke visa brazilian justice minister</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J46"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2090,6 +2090,42 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45897</v>
+      </c>
+      <c r="B47" t="n">
+        <v>6501.85986328125</v>
+      </c>
+      <c r="C47" t="n">
+        <v>6508.22998046875</v>
+      </c>
+      <c r="D47" t="n">
+        <v>6466.9599609375</v>
+      </c>
+      <c r="E47" t="n">
+        <v>6483.83984375</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4283760000</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.0031567194195349</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>silver stabilizes above a mean reversion structure hold ford recall more than pickup truck over instrument display failure on the dashboard ford recall more than pickup truck over instrument display failure on the dashboard ford recall more than pickup truck over instrument display failure on the dashboard fashion model reckon with ai model and digital clone after controversial ad appears in vogue ai profit window is wide open here how to time it from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience from swag to strategy why business are replacing cheap merch with thoughtful luxury gifting experience are workplace relationship the key to finding meaning on the job the ethical life podcast are workplace relationship the key to finding meaning on the job the ethical life podcast safer foundation to host open house at new employment service location in rock island are workplace relationship the key to finding meaning on the job the ethical life podcast the next x crypto to invest in a cardano ada and ripple xrp holder seek stronger bull run play are workplace relationship the key to finding meaning on the job the ethical life podcast xrp news today why investor are choosing this defi utility token over ripple clear creek isd trustee approve over k in capital project are workplace relationship the key to finding meaning on the job the ethical life podcast are workplace relationship the key to finding meaning on the job the ethical life podcast are workplace relationship the key to finding meaning on the job the ethical life podcast america bankruptcy wave ha surpassed the pandemicand it getting worse josh kosnicks five bridge answer whats next when the hustle fails highflying stock set for a pullback sp hit record high a investor await nvidia result reuters these analyst increase their forecast on ncino following betterthanexpected q earnings xrp bitcoin or eth here which coin user predict to perform best until trump critic inside fema put on indefinite leave after blasting cut in dissent letter up fintech share drop after strong q result what you need to know subsea awarded contract offshore turkiye rfk jr make good on promise to end covid vaccine mandate biontech tumble this economic sugar high wont last crfb warns touting analysis predicting longterm stagnation and billion of annual borrowing through the latest trump effort to control u capital expands to union station bytedance target billion valuation a revenue exceed meta sharp technology soar after insider buy and m solana treasury plan water wellness summit offer expert analysis recommendation for waterborne disease prevention the death of reaganomics trump break with longtime gop economic doctrine first commerce credit union donates for student scholarship buffalo diocese abuse settlement increase to million downtown san jose apartment complex land construction loan downtown san jose apartment complex land construction loan bank of montreal analyst boost their forecast after q result fargo agrees to jail rate increase after exhausting discussion building your organization next generation of leader no college degree here are job where can still earn figure no college degree here are job where can still earn figure mdot suspending construction lifting traffic restriction for labor day weekend how coolvu is empowering entrepreneur and protecting small business powell see the light in his final jackson hole talk my husband sold our house behind my back and kept every dime well now it my turn to cut him off uvalde cisd considers new law firm a trust in current agency falter following document issue johnson fistel pllp investigates claim on behalf of alto neuroscience inc longterm shareholder these analyst boost their forecast on echostar delta to pay million to resolve fuel dump lawsuit investigation alert elanco animal health incorporated driven brand holding hasbro and transmedics johnson fistel pllp investigates claim on behalf of investor kelowna councillor wonder if the city should stop density bonusing program kelowna arctic pablo coin raise m in presale one of the top meme coin to invest a dogecoin and shiba inu rally make cracker barrel a winner again trump celebrates logo reversal nprs all thing considered name scott detrow a new fulltime host johnson fistel pllp investigates constellation brand atkore domino pizza and fmc corporation on behalf of longterm shareholder innout primanti bros gone after one year on high street these analyst revise their forecast on okta after upbeat q earnings rbc city national bank is back on front foot ceo say nvidias upstart chinese rival cambricon just showed growth but dont get too excited trump is forcing the economy to bend to his will only one person can stop him the latest trump effort to control u capital expands to union station the latest trump effort to control u capital expands to union station the latest trump effort to control u capital expands to union station the latest trump effort to control u capital expands to union station another power company eyeing northwestern ontario city for solar farm guess investor alert by the former attorney general of louisiana kahn swick foti llc investigates adequacy of price and process in proposed sale of guess inc ge executive order open door to alternative asset in k key consideration for plan fiduciary im rooting for female founder comeback and for the end of branding woman from girlboss to tradwife and all the way down the best walmart labor day deal on kitchen bestseller university of phoenix leadership present at greater phoenix chamber foundation workforce summit university of phoenix leadership present at greater phoenix chamber foundation workforce summit the latest trump effort to control u capital expands to union station mongodb to rally around here are top analyst forecast for wednesday will credit card interest rate finally drop this september cross river and sightline team on gamingfocused debit card tom cotton target tax status of terroristsupporting youth movement vertical aerospace shortinterest collapse signal shifting market sentiment food and chemical unpacked epr you keeping up podcast unpacking the latest option trading trend in carvana decoding bank of america option activity whats the big picture oktas option a look at what the big money is thinking attention cio it is just one week away register now florida csuite executive invited to forecasting the future analyst projection for synopsys crowdstrike likely to report lower q earnings these most accurate analyst revise forecast ahead of earnings call analyst assess lineage cell therapeutic what you need to know analyst expectation for omega healthcare invtss future larkins investigation expands to indianapolis in now offering comprehensive investigative and tscm service what analyst rating have to say about compass let talk indianola mayor steve richardson analyst expectation for eli lillys future texas new proxy advisor disclosure law key detail for shareholder and company ahead of september pe ratio insight for bread finl hldgs analyst expectation for essex property trust future coach tory burch and more designer bag are up to off on amazon save up to on dyson dewalt anker adidas and more during ebays th anniversary sale maga loses it after minneapolis mayor emotional speech on shooting voter lose in redistricting game texas republican are wrong to start this tit for tat fight voter lose in redistricting game texas republican are wrong to start this tit for tat fight trump tell supreme court he shouldnt have to spend foreign aid approved by congress fda rescinds emergency use authorization for covid vaccine rfk jr fda rescinds emergency use authorization for covid vaccine rfk jr federal prosecutor fail to indict sandwich slinger exdoj employee on assault charge report gerrymandering is controversial but the alternative is worse fda rescinds emergency use authorization for covid vaccine rfk jr fda rescinds emergency use authorization for covid vaccine rfk jr attorney for jack smith respond to federal watchdog probe fulton county commissioner risk jail time for not appointing republican to election board dc mayor masked ice agent and outoftown national guard are ineffective axios lehigh valley police department shared driver comical excuse during speed enforcement detail ukraine will allow men to leave country exploring trend how immigration shape our region from cracker barrel to bud light trump weighs in on another corporate controversy un warns gaza famine expanding a aid group decry israeli siege riley push bill for rural hospital funding gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule trouble finding tea global matcha shortage take toll on bay area business white nationalist agenda minority in front line of trump policy target minneapolis mayor jacob frey slammed for mocking prayer after the catholic school shooting gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule gop whip time to change senate confirmation rule johnson fistel pllp investigates claim on behalf of alto neuroscience inc longterm shareholder mixed report of russian force holding ground in dnipropetrovsk ice is suddenly showing up in california hospital worker want more guidance on what to do ice is suddenly showing up in california hospital worker want more guidance on what to do the not so dormant commerce clause watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue congressional candidate in arizona debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue watch congressional candidate debate ice other issue protester to assemble on labor day magic johnson turned down a deal of a lifetime in boy did i make a mistake im still kicking myself offset vow to never get married again warns men against it too mary spencer youre not too young to make an estate plan commentary why is trump going after the smithsonian museum gov tony evers renews appeal for fema help following milwaukeearea flooding a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know a deadly truck crash in florida ha fueled an immigration fight here what to know executive order open door to alternative asset in k key consideration for plan fiduciary abrego garcia cannot be deported before october hearing judge say council in burnaby bc call for israel arm embargo metro vancouver south african politician criticized by trump is found guilty of hate speech u envoy cut lebanon trip short amid protest outrage over press comment trump say liberal donor george soros and son should be criminally charged bolivian court order the release of a prominent rightwing opposition leader fema worker put on leave after signing letter warning of trump overhaul of the agency how wes moore can stand up for the national guard guest commentary bengalmc air cushion catamaran aim to be the navy future ultraadaptable combat ship newton is removing italian flag color from street again russian force break into another region of ukraine with peace effort stuck green destry covington table drinking area vote again native american housing advocate urge congress to renew affordable housing law nyc mayor race eric adam label democratic socialist mamdani a communist echoing a frequent trump attack trump military invasion is cleaning up dcliterally denmark summons u envoy over suspected influence campaign in greenland debate over book page pit cultural concern against free access asking eric im a loyal person but my husband emotional affair ha me unable to trust him republican nominated to replace sen darin smith joseph kibler running for wyoming governor credit union deliver big return for community through cdfis new parkingmeter hour added for el cajon boulevard surrounding area top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show top florida official say alligator alcatraz will likely be empty within day email show majority of voter oppose deploying national guard to dc quinnipiac university national poll find support drop for u military aid to israel a think israel is committing genocide in gaza quinnipiac university poll u federal judge rule wisconsin judge cannot claim immunity in immigration obstruction case jared kushner participates in gaza meeting at the white house source say watch labor leader give trump the business for hurting worker top florida official say alligator alcatraz will likely be empty within day email show morris a a wave of shooting roils minneapolis leave the national guard at home a deadly florida truck crash ha fueled an immigration fight here what to know a deadly florida truck crash ha fueled an immigration fight here what to know</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>silver stabilizes reversion structure ford recall pickup truck instrument display failure dashboard ford recall pickup truck instrument display failure dashboard ford recall pickup truck instrument display failure dashboard fashion model reckon ai model digital clone controversial ad vogue ai profit window wide open swag strategy business replacing cheap merch thoughtful luxury gifting experience swag strategy business replacing cheap merch thoughtful luxury gifting experience swag strategy business replacing cheap merch thoughtful luxury gifting experience swag strategy business replacing cheap merch thoughtful luxury gifting experience workplace relationship finding meaning job ethical life podcast workplace relationship finding meaning job ethical life podcast safer foundation host open house new employment service location rock island workplace relationship finding meaning job ethical life podcast next x crypto invest cardano ada ripple xrp holder seek stronger bull run play workplace relationship finding meaning job ethical life podcast xrp news today investor choosing defi utility token ripple creek isd trustee approve k capital project workplace relationship finding meaning job ethical life podcast workplace relationship finding meaning job ethical life podcast workplace relationship finding meaning job ethical life podcast america bankruptcy wave surpassed pandemicand getting worse josh kosnicks bridge answer whats next hustle fails highflying stock set pullback sp hit record high investor await nvidia reuters analyst increase forecast ncino following betterthanexpected q earnings xrp bitcoin eth coin user predict perform best trump critic inside fema put indefinite blasting cut dissent letter fintech share drop strong q subsea awarded contract offshore turkiye rfk jr good promise end covid vaccine mandate biontech tumble economic sugar high wont crfb warns touting analysis predicting longterm stagnation billion annual borrowing latest trump effort control capital expands union station bytedance target billion valuation revenue exceed meta sharp technology soar insider buy solana treasury plan water wellness summit offer expert analysis recommendation waterborne disease prevention death reaganomics trump break longtime gop economic doctrine commerce credit union donates student scholarship buffalo diocese abuse settlement increase million downtown san jose apartment complex land construction loan downtown san jose apartment complex land construction loan bank montreal analyst boost forecast q fargo agrees jail rate increase exhausting discussion building organization next generation college degree job earn figure college degree job earn figure mdot suspending construction lifting traffic restriction labor day weekend coolvu empowering entrepreneur protecting small business powell light final jackson hole husband sold house behind kept dime turn cut uvalde cisd considers new law firm trust agency falter following document issue johnson fistel pllp investigates claim behalf alto neuroscience longterm shareholder analyst boost forecast echostar delta pay million resolve fuel dump lawsuit investigation alert elanco animal health incorporated driven brand holding hasbro transmedics johnson fistel pllp investigates claim behalf investor kelowna councillor wonder stop density bonusing program kelowna arctic pablo coin raise presale meme coin invest dogecoin shiba inu rally cracker barrel winner trump celebrates logo reversal nprs considered name scott detrow new fulltime host johnson fistel pllp investigates constellation brand atkore domino pizza fmc corporation behalf longterm shareholder innout primanti bros year high street analyst revise forecast okta upbeat q earnings rbc national bank front foot ceo nvidias upstart chinese rival cambricon showed growth dont excited trump forcing economy bend stop latest trump effort control capital expands union station latest trump effort control capital expands union station latest trump effort control capital expands union station latest trump effort control capital expands union station another power company eyeing northwestern ontario solar guess investor alert attorney general louisiana kahn swick foti llc investigates adequacy price process proposed sale guess ge executive order open door alternative asset k consideration plan fiduciary im rooting female founder comeback end branding woman girlboss tradwife best walmart labor day deal kitchen bestseller university phoenix leadership present greater phoenix chamber foundation workforce summit university phoenix leadership present greater phoenix chamber foundation workforce summit latest trump effort control capital expands union station mongodb rally around analyst forecast wednesday credit card interest rate finally drop september cross river sightline team gamingfocused debit card tom cotton target tax status terroristsupporting youth movement vertical aerospace shortinterest collapse signal shifting market sentiment food chemical unpacked epr keeping podcast unpacking latest option trading trend carvana decoding bank america option activity whats big picture oktas option look big money thinking attention cio away register florida csuite executive invited forecasting future analyst projection synopsys crowdstrike likely report lower q earnings accurate analyst revise forecast ahead earnings call analyst assess lineage cell therapeutic analyst expectation omega healthcare invtss future larkins investigation expands indianapolis offering comprehensive investigative tscm service analyst rating compass indianola mayor steve richardson analyst expectation eli lillys future texas new proxy advisor disclosure law detail shareholder company ahead september pe ratio insight bread finl hldgs analyst expectation essex property trust future coach tory burch designer bag amazon save dyson dewalt anker adidas ebays anniversary sale maga loses minneapolis mayor emotional speech shooting voter lose redistricting game texas republican start tit tat fight voter lose redistricting game texas republican start tit tat fight trump supreme court shouldnt spend foreign aid approved congress fda rescinds emergency authorization covid vaccine rfk jr fda rescinds emergency authorization covid vaccine rfk jr federal prosecutor fail indict sandwich slinger exdoj employee assault charge report gerrymandering controversial alternative worse fda rescinds emergency authorization covid vaccine rfk jr fda rescinds emergency authorization covid vaccine rfk jr attorney jack smith respond federal watchdog probe fulton county commissioner risk jail appointing republican election board dc mayor masked agent outoftown national guard ineffective axios lehigh valley police department shared driver comical excuse speed enforcement detail ukraine allow men country exploring trend immigration shape region cracker barrel bud light trump weighs another corporate controversy un warns gaza famine expanding aid decry israeli siege riley push bill rural hospital funding gop whip change senate confirmation rule gop whip change senate confirmation rule trouble finding tea global matcha shortage take toll bay area business white nationalist agenda minority front line trump policy target minneapolis mayor jacob frey slammed mocking prayer catholic school shooting gop whip change senate confirmation rule gop whip change senate confirmation rule gop whip change senate confirmation rule gop whip change senate confirmation rule johnson fistel pllp investigates claim behalf alto neuroscience longterm shareholder mixed report russian force holding ground dnipropetrovsk suddenly showing california hospital worker guidance suddenly showing california hospital worker guidance dormant commerce clause watch congressional candidate debate issue watch congressional candidate debate issue congressional candidate arizona debate issue watch congressional candidate debate issue watch congressional candidate debate issue watch congressional candidate debate issue watch congressional candidate debate issue watch congressional candidate debate issue protester assemble labor day magic johnson turned deal lifetime boy mistake im kicking offset vow never married warns men mary spencer youre young estate plan commentary trump smithsonian museum gov tony evers renews appeal fema help following milwaukeearea flooding deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight deadly truck crash florida fueled immigration fight executive order open door alternative asset k consideration plan fiduciary abrego garcia deported october hearing judge council burnaby bc call israel arm embargo metro vancouver south african politician criticized trump found guilty hate speech envoy cut lebanon trip short amid protest outrage press trump liberal donor george soros son criminally charged bolivian court order release prominent rightwing opposition fema worker put signing letter warning trump overhaul agency wes moore stand national guard guest commentary bengalmc air cushion catamaran aim navy future ultraadaptable combat ship newton removing italian flag color street russian force break another region ukraine peace effort stuck green destry covington table drinking area vote native american housing advocate urge congress renew affordable housing law nyc mayor race eric adam label democratic socialist mamdani communist echoing frequent trump attack trump military invasion cleaning dcliterally denmark summons envoy suspected influence campaign greenland debate book page pit cultural concern free access asking eric im loyal husband emotional affair unable trust republican nominated replace sen darin smith joseph kibler running wyoming governor credit union deliver big community cdfis new parkingmeter hour added el cajon boulevard surrounding area florida alligator alcatraz likely empty day email florida alligator alcatraz likely empty day email florida alligator alcatraz likely empty day email florida alligator alcatraz likely empty day email florida alligator alcatraz likely empty day email florida alligator alcatraz likely empty day email florida alligator alcatraz likely empty day email florida alligator alcatraz likely empty day email florida alligator alcatraz likely empty day email majority voter oppose deploying national guard dc quinnipiac university national poll find support drop military aid israel israel committing genocide gaza quinnipiac university poll federal judge rule wisconsin judge claim immunity immigration obstruction case jared kushner participates gaza meeting white house source watch labor give trump business hurting worker florida alligator alcatraz likely empty day email morris wave shooting roils minneapolis national guard deadly florida truck crash fueled immigration fight deadly florida truck crash fueled immigration fight</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2126,6 +2126,42 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="B48" t="n">
+        <v>6460.259765625</v>
+      </c>
+      <c r="C48" t="n">
+        <v>6491.759765625</v>
+      </c>
+      <c r="D48" t="n">
+        <v>6444.56982421875</v>
+      </c>
+      <c r="E48" t="n">
+        <v>6489.27978515625</v>
+      </c>
+      <c r="F48" t="n">
+        <v>4234840000</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-0.0063981842935716</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>judge block kari lake tasked to dismantle voa from firing it director annunciation mass shooting what we know about the shooter motive stock add a bit to their record on wall street flyw class action reminder flyw investor with large loss should contact robbins llp for information about the lead plaintiff deadline in the flywire corporation class action lawsuit atlas energy report second quarter financial result shareholder notice faruqi faruqi llp investigates claim on behalf of investor of altimmune ehc investor news if you have suffered loss in encompass health corporation nyse ehc you are encouraged to contact the rosen law firm about your right coinbase to monetize bitcointoethereum rotation through trading volume cfo say intel took trump deal to remove uncertainty around chip act billion los gatos property sale twobedroom home sell for million los gatos property sale twobedroom home sell for million raising cane to open more restaurant in september how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained how global ecommerce brand can recover u import tariff duty drawback explained fort smith weighs m in water upgrade a demand grows market expert say ozak ai might outperform ethereum in next bull run food hub planned across treaty territory to combat food insecurity xrp news today analyst warns dont sell xrp yet lawsuit win etf catalyst may lift price california face high pump price a phillips shuts la refinery the federal government is taking over dc union station what doe that mean the federal government is taking over dc union station what doe that mean u put official gdp data on nine blockchains in historic trumpera crypto push is ada price mirroring the breakout pattern a holder look for the next x bet big on remittix missing yearold boy with autism killed by alligator in new orleans police finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service finturf and energuy launch incentive program contractor earn for every financed project using energuy service hormel share face worst day on record a pork and other cost surge gbank financial holding inc is pleased to share the press release of boltbetz nike put finishing touch on a corporate overhaul more layoff ahead taco bell reconsiders voice ai after seeing mixed result tesla sale plunge again in europe a anger at musk keep buyer away for th month in a row yahoo finance northwood plaza owner defends work at former great eastern council want action gbank financial holding inc is pleased to share the press release of boltbetz will a reverse mortgage impact your social security or medicare benefit taiwan prosecutor charge people for allegedly stealing tsmc trade secret consumer watchdog public interest group to legislator dont let newsom sell out real utility rate reform in eleventh hour deal for utilitybacked western grid proposal and wildfire fund retail roundup key winner and loser after q earnings gbank financial holding inc is pleased to share the press release of boltbetz guardian officially release million veteran after disappointing season small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption small parcel in limbo a trump move to end u tariff exemption beef and nut price have surged and thats driving hormels stock to it biggest drop ever fresno council to vote on m plan for west fresno affordable housing jcpenneys closing down sale spread to two more location after shutdown continue major airline add route with low flight cost challenging a top rival meta is racing the clock to launch it newest llama ai model this year business insider reykjavik energy green bond auction result fed cook an unintentional clerical error may have been behind the mortgage dispute ap sport summarybrief at pm edt earthwise advertising investor awareness campaign bluerock total income real estate fund shareholder receive iss and glass lewis recommendation to support key proposal in connection with listing of the fund on the nyse a sea war brew off gambia a desperate local fisherman attack foreign vessel and each other labor day deal alert heydude is offering an extra off top style city pivot after apex rescinds rosecrans airport lease agreement best ai chatbots and key statistic of stockton mark oneyear anniversary of staart app with conference powerball player win in texas where wa the lucky ticket sold florida taxpayer may lose m on empty alligator alcatraz a judge order shutdown florida taxpayer may lose m on empty alligator alcatraz a judge order shutdown florida taxpayer may lose m on empty alligator alcatraz a judge order shutdown the probability machine trump ha fired a democrat on a federal railroad board he the latest to refuse to leave his post politico who are the most valuable nfl team cowboy b top forbes list for instacart offer indie grocer ecommerce tool with mdi partnership naples set tax rate at postal service across the world to suspend u delivery after trump end tariff exemption casco set tax rate at credo stock notch record high ahead of earnings report grocery chain to close maryland location campaign finance board again denies matching fund to mayor adam seager marine acquires rk marina on rushford lake u economy grew percent in q beating prior estimate denim trend boost abercrombie a outlook stock climb treasury secretary bessent capital market are roaring back powerball jackpot nears billion ahead of saturday drawing trump pick for un aviation office ha long history donating to dems nikki haley nyseg rge to upgrade high voltage line substation across ny state how michael polk growth culture drove performance at newell brand and beyond trump look to fire transportation regulator ahead of rail merger a closer look at enphase energy option market dynamic stonepeak buy fort worth logistics property freeland to host history walk and cemetery tour for th anniversary rwanda say deportee arrived from the u in august under agreement with washington ap business summarybrief at pm edt cdc crisis triggered by upcoming vaccine meeting leading to director firing former yankee mark teixeira running for congress a republican apparently anyone can be an immigration judge in trump america white house confirms trump fired cdc director after she refused to resign woman at center of viral rochester video say she moved intends to fight charge sunday voting choice given to county by state board trump renews citizenship requirement waived since noem hit back at fema critic reveals vision for disaster relief agency the federal government is taking over dc union station what doe that mean npr former golden triangle development leader conduct would harm every member of this community xi put axis of u enemy on parade with putin kim in beijing former mlb star mark teixeira announces run for texas congressional seat trump administration asks military base near chicago for support on immigration operation whatever happened to the woman in the no sex for fish group whatever happened to the woman in the no sex for fish group minneapolis mayor we need a statewide and a federal ban on assault weapon cdc director arrives at office to find dead deer with fired carved into it what to know after the u deports more migrant to africa the latest trump administration asks military base near chicago for support on immigration gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap gov jared polis order million in spending cut sweep state cash account to help close budget gap at least migrant detained by ice in san francisco a arrest soar iran is facing a return of un sanction what happens now immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started immigration agent signed up to recruit at a california university then the protest started exclusive gop smell blood in water over defeated dem exsens vulnerability karoline leavitt take jen psaki to task over her attack on prayer following tragic catholic school shooting fresno council to vote on m plan for west fresno affordable housing governor pay tribute to buttearea veteran still serving veteran closure of florida alligator alcatraz immigration detention center can proceed judge say mass sen warren launch probe over shuttering of public corruption unit at justice dept fbi leavitt slam insensitive psaki on prayer comment after minnesota shooting montgomery county ready to combat mosquito with targeted spraying in windlestrae park amid west nile concern opinion gov newsom playing for a tie in national redistricting battle leavitt slam insensitive psaki on prayer comment after minnesota shooting leavitt slam insensitive psaki on prayer comment after minnesota shooting leavitt slam insensitive psaki on prayer comment after minnesota shooting congress probe wikipedia over antiisrael prokremlin content manipulation trump administration asks military base near chicago for support on immigration operation trump administration asks military base near chicago for support on immigration operation trump administration asks military base near chicago for support on immigration operation trump administration asks military base near chicago for support on immigration operation leavitt slam insensitive psaki on prayer comment after minnesota shooting fed lisa cook sue trump over move to fire her is it ever legal to pas a school bus in new jersey u to sell ukraine extendedrange missile resident have a chance to weigh in on city chicken sept texas governor greg abbott revise special legislative session agenda to enhance law enforcement privacy election integrity election commission panel call for a shakeup in how hawaii vote ecuadorian man arrested in maine sue immigration official alleging unlawful detention deadeyed travis kelce nod at bow tie option for cat ring bearer trump ha fired a democrat on a federal railroad board he the latest to refuse to leave his post trump federal takeover of dc could do irreparable damage to policecommunity relation rfk jr say cdc must deliver on trump agenda after white house fire director flagging flag burner again wife of greencard holder detained by ice speaks outlots of tear shenandoah to rework park master plan following resident pushback watchdog group sue for record on spying targeting trump associate michael caputo tong warns of recruitment scam targeting ct job seeker white house is not happy with view cohost for her comment on latino trumpers campaign finance board again denies matching fund to mayor adam ap business summarybrief at pm edt hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness hud secretary pursues paradigm shift in administration approach to homelessness schumer jeffries call on gop leader to meet to avoid government shutdown bondi patel to testify before congress amid epstein fallout bondi patel to testify before congress amid epstein fallout european power hit iran with pre sanction a pressure for nuclear negotiation hoosier gop legislative leader break redistricting silence no business a usual public rally monday at shorey park judge frank caprios death leaf mourner remembering his compassion that drew many online fan montgomery county executive celebrates new affordable housing milestone in montgomery village uno study offer firstever look into labor trafficking in nebraska lt governor david wasinger launch missouri state employee charitable campaign in jefferson city trump unprecedented firing of fed governor lisa cook raise untested question</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>judge block kari lake tasked dismantle voa firing director annunciation mass shooting shooter motive stock add bit record wall street flyw class action reminder flyw investor large loss contact robbins llp information lead plaintiff deadline flywire corporation class action lawsuit atlas energy report quarter financial shareholder notice faruqi faruqi llp investigates claim behalf investor altimmune ehc investor news suffered loss encompass health corporation nyse ehc encouraged contact rosen law firm coinbase monetize bitcointoethereum rotation trading volume cfo intel took trump deal remove uncertainty around chip act billion los gatos property sale twobedroom sell million los gatos property sale twobedroom sell million raising cane open restaurant september global ecommerce brand recover import tariff duty drawback explained global ecommerce brand recover import tariff duty drawback explained global ecommerce brand recover import tariff duty drawback explained global ecommerce brand recover import tariff duty drawback explained global ecommerce brand recover import tariff duty drawback explained global ecommerce brand recover import tariff duty drawback explained global ecommerce brand recover import tariff duty drawback explained global ecommerce brand recover import tariff duty drawback explained global ecommerce brand recover import tariff duty drawback explained global ecommerce brand recover import tariff duty drawback explained fort smith weighs water upgrade demand grows market expert ozak ai outperform ethereum next bull run food hub planned across treaty territory combat food insecurity xrp news today analyst warns dont sell xrp yet lawsuit etf catalyst lift price california face high pump price phillips shuts la refinery federal government taking dc union station doe federal government taking dc union station doe put gdp data blockchains historic trumpera crypto push ada price mirroring breakout pattern holder look next x bet big remittix missing yearold boy autism killed alligator new orleans police finturf energuy launch incentive program contractor earn financed project energuy service finturf energuy launch incentive program contractor earn financed project energuy service finturf energuy launch incentive program contractor earn financed project energuy service finturf energuy launch incentive program contractor earn financed project energuy service finturf energuy launch incentive program contractor earn financed project energuy service finturf energuy launch incentive program contractor earn financed project energuy service finturf energuy launch incentive program contractor earn financed project energuy service finturf energuy launch incentive program contractor earn financed project energuy service finturf energuy launch incentive program contractor earn financed project energuy service hormel share face worst day record pork cost surge gbank financial holding pleased share press release boltbetz nike put finishing touch corporate overhaul layoff ahead taco bell reconsiders voice ai seeing mixed tesla sale plunge europe anger musk buyer away month row yahoo finance northwood plaza owner defends work great eastern council action gbank financial holding pleased share press release boltbetz reverse mortgage impact social security medicare benefit taiwan prosecutor charge people allegedly stealing tsmc trade secret consumer watchdog public interest legislator dont newsom sell real utility rate reform eleventh hour deal utilitybacked western grid proposal wildfire fund retail roundup winner loser q earnings gbank financial holding pleased share press release boltbetz guardian officially release million veteran disappointing season small parcel limbo trump move end tariff exemption small parcel limbo trump move end tariff exemption small parcel limbo trump move end tariff exemption small parcel limbo trump move end tariff exemption small parcel limbo trump move end tariff exemption small parcel limbo trump move end tariff exemption beef nut price surged thats driving hormels stock biggest drop ever fresno council vote plan west fresno affordable housing jcpenneys closing sale spread location shutdown continue major airline add route low flight cost challenging rival meta racing clock launch newest llama ai model year business insider reykjavik energy green bond auction fed cook unintentional clerical error behind mortgage dispute sport summarybrief pm earthwise advertising investor awareness campaign bluerock total income real estate fund shareholder receive iss glass lewis recommendation support proposal connection listing fund nyse sea war brew gambia desperate local fisherman attack foreign vessel labor day deal alert heydude offering extra style pivot apex rescinds rosecrans airport lease agreement best ai chatbots statistic stockton mark oneyear anniversary staart app conference powerball player texas lucky ticket sold florida taxpayer lose empty alligator alcatraz judge order shutdown florida taxpayer lose empty alligator alcatraz judge order shutdown florida taxpayer lose empty alligator alcatraz judge order shutdown probability machine trump fired democrat federal railroad board latest refuse post politico valuable nfl team cowboy b forbes list instacart offer indie grocer ecommerce tool mdi partnership naples set tax rate postal service across world suspend delivery trump end tariff exemption casco set tax rate credo stock notch record high ahead earnings report grocery chain close maryland location campaign finance board denies matching fund mayor adam seager marine acquires rk marina rushford lake economy grew percent q beating prior estimate denim trend boost abercrombie outlook stock climb treasury secretary bessent capital market roaring powerball jackpot nears billion ahead saturday drawing trump pick un aviation office history donating dems nikki haley nyseg rge upgrade high voltage line substation across ny michael polk growth culture drove performance newell brand beyond trump look fire transportation regulator ahead rail merger closer look enphase energy option market dynamic stonepeak buy fort worth logistics property freeland host history walk cemetery tour anniversary rwanda deportee arrived august agreement washington business summarybrief pm cdc crisis triggered upcoming vaccine meeting leading director firing yankee mark teixeira running congress republican apparently anyone immigration judge trump america white house confirms trump fired cdc director refused resign woman center viral rochester video moved intends fight charge sunday voting choice county board trump renews citizenship requirement waived since noem hit fema critic reveals vision disaster relief agency federal government taking dc union station doe npr golden triangle development conduct harm community xi put axis enemy parade putin kim beijing mlb star mark teixeira announces run texas congressional seat trump administration asks military base chicago support immigration operation whatever happened woman sex fish whatever happened woman sex fish minneapolis mayor statewide federal ban assault weapon cdc director arrives office find dead deer fired carved deports migrant africa latest trump administration asks military base chicago support immigration gov jared polis order million spending cut sweep cash account help close budget gap gov jared polis order million spending cut sweep cash account help close budget gap gov jared polis order million spending cut sweep cash account help close budget gap gov jared polis order million spending cut sweep cash account help close budget gap gov jared polis order million spending cut sweep cash account help close budget gap gov jared polis order million spending cut sweep cash account help close budget gap least migrant detained san francisco arrest soar iran facing un sanction happens immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest immigration agent signed recruit california university protest exclusive gop smell blood water defeated dem exsens vulnerability karoline leavitt take jen psaki task attack prayer following tragic catholic school shooting fresno council vote plan west fresno affordable housing governor pay tribute buttearea veteran serving veteran closure florida alligator alcatraz immigration detention center proceed judge mass sen warren launch probe shuttering public corruption unit justice dept fbi leavitt slam insensitive psaki prayer minnesota shooting montgomery county ready combat mosquito targeted spraying windlestrae park amid west nile concern opinion gov newsom playing tie national redistricting battle leavitt slam insensitive psaki prayer minnesota shooting leavitt slam insensitive psaki prayer minnesota shooting leavitt slam insensitive psaki prayer minnesota shooting congress probe wikipedia antiisrael prokremlin content manipulation trump administration asks military base chicago support immigration operation trump administration asks military base chicago support immigration operation trump administration asks military base chicago support immigration operation trump administration asks military base chicago support immigration operation leavitt slam insensitive psaki prayer minnesota shooting fed lisa cook sue trump move fire ever legal pa school bus new jersey sell ukraine extendedrange missile resident chance weigh chicken sept texas governor greg abbott revise special legislative session agenda enhance law enforcement privacy election integrity election commission panel call shakeup hawaii vote ecuadorian man arrested maine sue immigration alleging unlawful detention deadeyed travis kelce nod bow tie option cat ring bearer trump fired democrat federal railroad board latest refuse post trump federal takeover dc irreparable damage policecommunity relation rfk jr cdc must deliver trump agenda white house fire director flagging flag burner wife greencard holder detained speaks outlots tear shenandoah rework park master plan following resident pushback watchdog sue record spying targeting trump associate michael caputo tong warns recruitment scam targeting ct job seeker white house happy view cohost latino trumpers campaign finance board denies matching fund mayor adam business summarybrief pm hud secretary pursues paradigm shift administration approach homelessness hud secretary pursues paradigm shift administration approach homelessness hud secretary pursues paradigm shift administration approach homelessness hud secretary pursues paradigm shift administration approach homelessness hud secretary pursues paradigm shift administration approach homelessness hud secretary pursues paradigm shift administration approach homelessness hud secretary pursues paradigm shift administration approach homelessness schumer jeffries call gop meet avoid government shutdown bondi patel testify congress amid epstein fallout bondi patel testify congress amid epstein fallout european power hit iran pre sanction pressure nuclear negotiation hoosier gop legislative break redistricting silence business usual public rally monday shorey park judge frank caprios death leaf mourner remembering compassion drew online fan montgomery county executive celebrates new affordable housing milestone montgomery village uno study offer firstever look labor trafficking nebraska lt governor david wasinger launch missouri employee charitable campaign jefferson trump unprecedented firing fed governor lisa cook raise untested</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2162,6 +2162,42 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="B49" t="n">
+        <v>6415.5400390625</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6416.5400390625</v>
+      </c>
+      <c r="D49" t="n">
+        <v>6360.580078125</v>
+      </c>
+      <c r="E49" t="n">
+        <v>6401.509765625</v>
+      </c>
+      <c r="F49" t="n">
+        <v>4784000000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-0.0069222799368615</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>hows the market doe ownership go past the topsoil fresh stock on jim cramers radar juneteenth organizer get funding to repair modernize building panda express owns other restaurant chain do you know which one fed rate cut still on track no firework after nvidia earnings federal government post billion deficit from april to june canada whats going on with broadcom stock friday oakland unified school district looking to shed nearly million from budget is it a bot or not ticketings next big legal fight could reshape the resale industry a model for understanding with edward kaplan smlr investor have opportunity to lead semler scientific inc security fraud lawsuit first filed by the rosen law firm rock tech lithium announces offering of up to million the persistent pitfall of taxpayer funded campaign berkshire hillsbrookline merger nears completion retailer warn trump tariff will trigger consumer price explosion who will he blame boing boing nvidia ceo say ai will actually make u busier in the future gizmodo is amazon falling behind in the cloud computing battle brutally honest way to finance your startup dmv may owe you s and have no obligation to let you know wa being held in just a single case qgold announces financing to complete acquisition of quartz mountain gold project in oregon usa and advance mine centre camp in ontario canada qgold announces financing to complete acquisition of quartz mountain gold project in oregon usa and advance mine centre camp in ontario canada should the federal reserve cut rate next month should the federal reserve cut rate next month hope gas responds to criticism in it pipeline program ratehike case raising cane to open ann arbor location september th the company second in metro detroit trump administration kill wasteful funding for humboldt bay offshore wind project sunblock charcoal and powerball holiday weekend lottery drawing worth billion sunblock charcoal and powerball holiday weekend lottery drawing worth billion sunblock charcoal and powerball holiday weekend lottery drawing worth billion sunblock charcoal and powerball holiday weekend lottery drawing worth billion ardot seeking public comment on proposed disadvantaged business enterprise goal for why you should think twice before buying private equity in your k nasb financial inc declares cash dividend on common stock sunblock charcoal and powerball holiday weekend lottery drawing worth billion ap news ulta beauty delivers strong quarter investor brush off the glow thought i wa going to die tunisian singer detained for week fight deportation while trying to finish music small business joint venture win coast guard cyber contract dupont to sell kevlar business for billion the manufacturer life insurance company grows position in tesla inc tsla stock market news today market slide a chip stock weigh spsp complete index seeking alpha layoff hit international paper jb hunt hormel and more the orange peel first year put asheville on the map now staffer hope to buy it cv walgreens now require prescription for covid vaccine in colorado the denver post in hong kong eric trump lauds growing influence of crypto the new york time forecasting the future analyst projection for oneok what the option market tell u about mastercard lazr investor have opportunity to lead luminar technology inc security fraud lawsuit sword group availability of the h financial report sword group h report of the liquidity agreement contracted with oddo bhf procter gamble unusual option activity forecasting the future analyst projection for dt midstream dows option frenzy what you need to know pce inflation flat but core sticky implication for fed september meeting analyst expectation for targa resourcess future breaking down karooooo analyst share their view segg medium unveils nextgeneration corporate website showcasing completion of turnaround and launch of growth phase a glimpse into the expert outlook on cheniere energy through analyst is rivian automotive gaining or losing market support peering into extreme networkss recent short interest let talk indianola kwik star ribbon cutting expert outlook snapon through the eye of analyst is flex gaining or losing market support pe ratio insight for bank of nova scotia let talk knoxville planning and zoning administrator nathan parch part two segg medium unveils nextgeneration corporate website showcasing completion of turnaround and launch of growth phase u government publishes gdp data on bitcoin ethereum blockchains home price in okanagan and kamloops area may be levelling housewise chainlink link price movement face hurdle litecoin target rally while cold wallet hold roi edge major discount on outdoor furniture costway dining set off at target bytedance hit b valuation a q revenue surge to b energy exchange electronx earns cftc designated market and clearing approval how senior can borrow home equity without refinancing now crypto news today coinshares profit jump avalanche transaction rise gumi add xrp here why serve robotics surged this week savvy shopper save over k in year by extreme couponing she scored k of jcpenney cookware for just backtoschool sale tax holiday the edmund fitzgerald and a state microbe theyre among state bill in august should you buy lucid stock ahead of it for reverse stock split bitcoin drop below a xrp slide below and eth dogecoin wobble shopping labor day furniture sale tip to bargain for the best price ollies bargain earnings suggest analyst underestimate longterm potential no ruling friday on trump attempt to fire fed official the credit race closing the perception gap to win welcome to the new made in china era and it look a lot different dell struggle to protect margin a supply chain cost mount cracker barrel ditched it new logo but it also got rid of something else labubu doll and affordable latte why chinese brand are betting big on the u business insider mycarrier portal and carrier assure integrate to make carrier vetting easier cracker barrel is still deep in dei despite the return of uncle herschel former trans mountain ceo to head major project office canada cracker barrel did more than just ditch it logo after maga meltdown the daily beast cracker barrel new logo wa pitiful one of chain original executive say anthony brown maryland legal victory show prudent use of resource reader commentary atlanta becomes largest u metro without a printed daily newspaper a journalconstitution go digital techstock skid sends nasdaq sharply lower live stockmarket update understanding the benefit and risk of ai agent university of northern iowa to open finance and real estate analytics lab for business eli lilly is proof that wall street star dont have to be tech titan trump fire democratic member from transportation board just before it considers the largest railroad merger in history marvell sink a weak data center outlook stokes custom ai chip worry reuters mount logan capital inc shareholder approve previously announced business combination with degree capital corp court block trump effort to end protected status for venezuelan mamdani team with sharpton to threaten wall street upcoming upgrade to holocaust museum exhibit spark some staff concern source trump planning immigration crackdown in chicago next week dhs source say gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber gov gretchen whitmer call special election for state senate seat that could split michigan chamber migrant defer their american dream to seek asylum in mexico bonus editorial cartoon for aug alabama town first black mayor reelected after being locked out of office lawyer who led karen read defense one step closer to joining team for civil suit trump move to cut bn in foreign aid already approved by congress rubio revoke visa for palestinian official denying address at un meeting alabama town first black mayor reelected year after he say white resident locked him out of office cbs news can tv help prepare for invasion jd vance say there thing dems should learn from trump and critic cant believe he serious jd vance say there thing dems should learn from trump and critic cant believe he serious abrego garcia asks for gag order on bondi noem meet bill pulte the trump housing official at the center of the latest fed controversy abrego garcia asks for gag order on bondi noem judge weighs request to block trump firing of fed governor lisa cook abrego garcia asks for gag order on bondi noem contract talk fail between alberta government and teacher possible strike loom alberta republican joni ernst will not seek reelection source say abrego garcia asks for gag order on bondi noem trump yank kamala harris bidenextended taxpayerfunded secret service protection before book tour susan estrich the epitome of dumbness judge hears argument on lisa cook attempted firing by trump administration psc answer preston county commission objection to marl project corruption allegation impact argentina president mileis popularity trump block b in foreign aid congress okd using maneuver last seen nearly year ago trump block b in foreign aid congress okd using maneuver last seen nearly year ago mackinac island police chief to resign citing ongoing friction with city council a lament for the shrinking middle class reader commentary dear annie unfaithful fiancee tell me to stop living in the past appeal court block trump administration from ending legal protection for venezuelan appeal court block trump administration from ending legal protection for venezuelan appeal court block trump administration from ending legal protection for venezuelan a trumpbrokered peace deal in the south caucasus is hopeful but incomplete many state employeefriendly labor law take effect a nlrb remains quorumless benton county to display in god we trust in all public building by oct everyone on x point and laugh at dingus gungrabber who share pic of bullet scattered on his street democrat some republican cry outrage over trump use of rare tactic to withhold approved foreign aid funding lori falce year of thought and prayer appeal court say uk asylumseekers can stay at hotel dc federal judge to weigh order blocking fed gov lisa cook firing ahead of interest rate meeting let talk knoxville planning and zoning administrator nathan parch part two donald trump war on culture is not a sideshow japan india to deepen security economic tie amid u tariff ai is ummasking ice officer can washington do anything about it politico public trust in election increase with clear fact sen ernst of iowa is expected to announce next month that she wont run for reelection in u revoke visa of palestinian official ahead of un general assembly fox news star call out trump ally over apparent hypocrisy this is the same thing sen ernst of iowa is expected to announce next month that she wont run for reelection in ap news fox news star call out trump ally over apparent hypocrisy this is the same thing free speech unmuted president trump executive order on flag desecration it a joke san jose mayor slam california legislature over lack of prop funding ransomware attack targeting pa attorney general lead to case delay susan collins rip trump unlawful effort to cancel billion in foreign aid susan collins rip trump unlawful effort to cancel billion in foreign aid susan collins rip trump unlawful effort to cancel billion in foreign aid what to know a texas bill let resident sue outofstate abortion pill provider what to know a texas bill let resident sue outofstate abortion pill provider what to know a texas bill let resident sue outofstate abortion pill provider what to know a texas bill let resident sue outofstate abortion pill provider chicago is in the trump administration sight for it next immigration crackdown chicago is in the trump administration sight for it next immigration crackdown trump admin plan immigration enforcement surge in boston politico a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows a trump threatens more guard troop in u city here what the law allows kilmar abrego garcia asks for gag order against pam bondi kristi noem kilmar abrego garcia asks for gag order against pam bondi kristi noem texas gov greg abbott sign new congressional redistricting map president trump requested kimball shinkoskey explain the law talk for trump riviera in gaza persist a israel push deeper into gaza city france germany vow to up pressure on ogre putin bankruptcy for north dakota and western minnesota published aug trump administration to cut plus job at voice of america best business line of credit in flexible small business funding option for growth and emergency adhesive dowel veneer the industrial choice shaping mass timber verizon down how to fix so modeonly issue in phone amid outage hindustan time hindustan time what would the fed do in a tie vote it not clear and the bank of england had to break a deadlock this month can you use milwaukee battery on harbor freight tool ulster county rail trail study to be contracted to new paltzbased consulting firm tim walz admits vp bid might have hurt him with voter in home state judge delay septum rate increase additional service cut gas price go up in killeen area per gallon at one place kari lake lay off hundred at voa parent agency amid legal battle doesnt surprise memark cuban explains why high school senior care more about making money than any generation in year cnc deadline alert rosen a longstanding law firm encourages centene corporation investor to secure counsel before important september deadline in security class action cnc bet bonus code orl bet on oregon v montana state get in bonus bet bemidji chamber ambassador welcome thrivent financial advisor letter illegal dumping and time to support wastetoenergy how the sound of name can bias hiring decision writer bloc a push for change in the u electoral college give u hope for future climate action strengthening italian finance a new era through takeover consolidation u trading partner dazed and confused after tariff court loss delaware ag other state secure americorps funding in winning suit solana etf buzz fade a investor shift to magacoin finance a rising star best soundbars with wireless rear speaker in cryptos under that could make you x richer mirroring pepe coin pepe run best small business loan option in how owner qualify compare program and secure fast funding with rok financial what happens to trump tariff now that a federal appeal court ha knocked them down cracker barrel or waffle house the south most heated food debate return amid logo saga ai cant install an hvac system why gen z is flocking to job in the trade navigating client conundrum california payday loan online same day no credit check bad credit guaranteed approval radcred launch payday loan platform for immediate financial relief for california borrower usa kari lake lay off more than staff at voice of america parent agency the washington post amazon is selling a laptop for thats nice and responsive how to check for a lien on a car before you buy how an appeal court ruling on trump tariff could upend the bond market barrons how an appeal court ruling on trump tariff could upend the bond market how to check for a lien on a car before you buy sameday business loan in fast approval for owner facing urgent cash flow need how to check for a lien on a car before you buy madison county official think wind farm could impact public safety your money way the new tax bill could impact your wallet ultimate plantbased beet burger mowest to reveal library renovation cuba energy crisis deepens a blackout grip the nation best crypto to invest in why blockdag rtx hyper and snort are gaining attention how europe is redrawing it energy map rosen global investor counsel encourages easterly rocmuni high income municipal bond fund cryptos under to accumulate now ozak ai xdc cro trx and vechain carol saline dy journalist with a story to tell about her dying powerball jackpot rise to billion sixthlargest ever sunblock charcoal and powerball holiday weekend lottery jackpot worth billion is up for grab larimer county restaurant inspection made aug china xi offer backing for myanmar sco membership bid wamco deadline notice rosen trusted investor counsel encourages western asset management company llc mutual fund investor with loss in excess of k to secure counsel before important september deadline in security class action merz promise debt relief for municipality ahead of electoral test burlington store nyseburl announces quarterly earnings result beat estimate by eps u trading partner dazed and confused after tariff court loss bloombergcom u trading partner dazed and confused after tariff court loss shopper can get electronics clothes and school supply worth up to taxfree a u state exemption final hour spirit airline bankruptcy tee up painful cut in survival bid do novelty menu like taco bell yk make investor money southwest airline begin flying first plane with secondary cockpit barrier reuters stock retail wa discussing this week and how they performed open bull mdb nvda baba channel rewind growth spark conflict video vault top wireless printer under r in paige thomason caramel pecan turtle brownie recipe dogecoin price prediction doge alternative for x gain this bull cycle billion powerball jackpot is up for grab saturday here how to play austin americanstatesman baird financial group inc acquires share of qualcomm incorporated qcom best water stock to watch now august th walmart inc wmt share purchased by titleist asset management llc deadline approach for under forty nomination eu to work on using frozen russian asset to aid ukraine after war white house to release m in americorps funding after maryland lawsuit white house to release m in americorps funding after maryland lawsuit groundbreaking of home housing cooperative in upper hammonds plain commentary lawmaker could trim electric bill baird financial group inc acquires share of ishares core sp etf ivv kodai capital management lp invests in honeywell international inc hon haberman call tariff ruling a big blow to trump agenda orange county restaurant shut down by health inspector aug costcos controversial policy change officially take effect costcos controversial policy change officially take effect mcdonalds corporation mcd share sold by baird financial group inc warren buffett warns not to invest in terrible industry because it a rewarding a struggling in quicksand micron boeing lead five stock near buy point yearold retail chain closed dozen of store s at risk in order to become the you must do what the other wont billionaire grant cardone say hard work defines success a court ha ruled most of trump tariff illegal here whats next tesla lawyer ask judge to throw out million verdict saying mention of elon musk misled the jury tesla lawyer ask judge to throw out million verdict saying mention of elon musk misled the jury fortune promising value stock to keep an eye on august th adam thielen take pay cut with viking excited to be back home insight wealth partner llc make new investment in palantir technology inc pltr insight wealth partner llc ha holding in jpmorgan chase co jpm deeply affordable halawa rental tower nearly full best altcoins to buy this week ethereum xrp and magacoin finance highlighted after market dip letter charlotte county ha no goodpaying job young american expect to inherit on average a new survey show how much millennials and gen z are banking on family wealth buford pusser famous tennessee sheriff who inspired hollywood in the s may have killed his wife in authority say mayor brandon johnson executive order ban law enforcement from wearing mask amid impending immigration crackdown mayor brandon johnson executive order ban law enforcement from wearing mask amid impending immigration crackdown a look at the race to replace canada rapidly aging fleet of submarine hilarious antivance demonstrator line up to protest his motorcade a last second turn sends them chasing car trenton raise the ukrainian flag at city hall with help from area organization photo college face financial struggle a trump policy send international enrollment plummeting college face financial struggle a trump policy send international enrollment plummeting election ejection chicago mayor and other dems are warning illegal alien ice will be at the poll we are on the street palestinian flee israel assault on gaza city cal thomas flagging flag burner again ny gov hochul now ha a press office account thats trying to outdo the newsom press office account naomi osaka call out jelena ostapenko over controversial remark toward taylor townsend ukraine exparliamentary speaker is shot dead in lviv dave bossie dnc and mamdani expose the coming disaster for democrat monday is labor day whats open whats closed wisconsin conservative supreme justice rebecca bradley wont seek reelection in fate intervenes family avoids execution in holocaust asking eric since my husband wa killed his family want nothing to do with me or my child salmo to get voter approval for new firetruck nelson trump revenge summer heat up with fed ouster bolton raid trump revenge summer heat up with fed ouster bolton raid new yorkers must fight political manipulation be it by the ccp or the united federation of teacher collegian marlboro rhinebeck resident graduate from university of rhode island tania fernandes anderson asks judge to let her dodge prison time for public corruption israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows doj call for tip on employer favoring foreign worker in hiring practice flag campaignwe cant reclaim that which wa never ours school board member say removing protection doe not give reason to bully trump cast doubt on putinzelensky meeting maybe they have to fight a little longer gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg gaza aid flotilla should not have to exist say thunberg thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival thousand protest israeli siege of gaza near venice film festival nh democrat launch town hall series to promote presidential primary chicago mayor to sign executive order directing city to resist trump immigration raid social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post social security whistleblower who claim doge mishandled american sensitive data resigns from post israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows israel soon will halt or slow aid to northern gaza a military offensive grows florida python hunter recount bloody battle with snake she got me son here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza here a look at why it is so hard to end the war in gaza got what it take to be lodis mayor for a day city accepting application from local student border czar say ice ops will ramp up for seattle portland after labor day unofficial election result strike delay start of class in southwest washington school district people are calling this jd vance habit his single most obnoxious characteristic and i have to agree epstein estate to hand over birthday book to lawmaker house dem say saturday morning college face financial struggle a trump policy send international enrollment plummeting letter something to actually feel hopeful about letter far fewer cost with votebymail election dncs summer showdown infighting expose crack in democrat unity narrative against gop agenda law enforcement increasing patrol across new hampshire over labor day weekend when can lawyer be punished for undignified or discourteous criticism of judge kellyanne conway revel in trump insane power grab after cracker barrel fiasco israel soon will halt or slow aid to northern gaza a military offensive grows ice detains somaliamerican activist ramsey county sheriff civilian officer what to know about worker over billionaire protest on labor day axios macron warns world will know by monday if putin played trump again u greenlights million sale of starlink service patriot support to ukraine state top election official balk at doj request for sensitive voter information state top election official balk at doj request for sensitive voter information when did caring for america most vulnerable kid become political opinion assembly bill undermines prop and put public safety at risk chicago plan to maintain peace amid federal deployment bondi fire doj employee over alleged gesture toward guard troop jd vance discusses readiness to be president if god forbid something happens to trump department of defense to conduct training exercise in philly starting sunday summerlins kestrel kestrel common offer unique floor plan whats open whats closed on labor day store hour for walmart costco target publix and more alcom best crypto to buy now magacoin finance gain traction a solana xrp and avax see whale inflow sen rand paul on the national debt let no one say we werent warned magax stage countdown secure your entry before the next wave begin need to save on a new appliance wayfair ha off kitchenaid mixer ninja creami did anyone win the powerball lottery jackpot swell to over billion woodside home open acacia in cadence china xi host modi and putin for summit amid anger over trump tariff daron bland contract cowboy cb agrees to massive extension with hope of returning to pro bowl form surfshark face classaction lawsuit over autorenewal violation final countdown top meme coin to invest before the next x surge hit midhudson people on the move for the week of sept nvidia lean heavily on two undisclosed customer for revenue boom china india pledge partnership ahead of putin joining summit guardian pitcher paid leave extended indefinitely a mlb continues gambling probe rosen top ranked global counsel encourages luminar technology inc investor to secure rosen top ranked global counsel encourages luminar technology inc investor to secure rosen top ranked global counsel encourages luminar technology inc investor to secure grover norquist idea for the next gop reconciliation bill how the fed losing it independence could affect american everyday life social security and medicare cut are coming because the bond market will eventually bring congress to it knee economist say fy energy launch multilevel affiliate program to expand access to cleanpowered crypto infrastructure cardano price support now at a worried holder back altcoins with huge potential like remittix social security and medicare cut are coming because the bond market will force congress economist fortune amazon labor day sale is filled with some surprisingly good deal rosen top ranked global counsel encourages luminar technology inc investor to secure counsel before important deadline in security class action lazr bob on business fort worth ridglea theater look to reel in a buyer nvidia q ai drive growth amid revenue concentration risk lithonias recreation center to get massive renovation and upgrade crypto news ozak ai presale heat up with m raisednext x token tesla unexpectedly end contract at giga texas letting go people tesla unexpectedly end contract at giga texas letting go people electrek gen z shift to aiproof trade like plumbing for job security business brief postal carrier retires after almost year of service intel secures b accelerated chip funding with u equity stake u still working on trade deal despite court ruling ustr say trump tariff spark pricing chaos for u business six month in vintage photo show how the role of woman in the workforce ha evolved in the last year i felt like a dead person former goldman sachs banker said before leaving u to build a startup in seoul which store and restaurant will be open for labor day should you ignore ethereum and buy this surging altcoin instead best samsung phone under r in budget pick that deliver hbar price set for gain in q a one altcoin could make investor over x by november future why trump tariff ruling may not matter for stock investor business daily touted a the teslakiller lucid scramble to stay on the nasdaq kemp jones reaped big money from company with an interest in legislation kemp jones reaped big money from company with an interest in legislation builderais b rise and collapse highlight fragility of ai boom seeking alpha kemp jones reaped big money from company with an interest in legislation final chance to get cash bonus from major u bank putting away a day will secure it for you people still spending on tech despite red flag in july report gizmodo people still spending on tech despite red flag in july report popular weightloss stock make a massive heartsaving claim trump trade counselor peter navarro rebuke politician in black robe over partisan tariff ruling mindanao busine</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>hows market doe ownership past topsoil fresh stock jim cramers radar juneteenth organizer funding repair modernize building panda express owns restaurant chain fed rate cut track firework nvidia earnings federal government post billion deficit april june canada whats broadcom stock friday oakland unified school district shed nearly million budget bot ticketings next big legal fight reshape resale industry model understanding edward kaplan smlr investor opportunity lead semler scientific security fraud lawsuit filed rosen law firm rock tech lithium announces offering million persistent pitfall taxpayer funded campaign berkshire hillsbrookline merger nears completion retailer warn trump tariff trigger consumer price explosion blame boing boing nvidia ceo ai busier future gizmodo amazon falling behind cloud computing battle brutally honest finance startup dmv owe obligation single case qgold announces financing complete acquisition quartz mountain gold project oregon usa advance mine centre camp ontario canada qgold announces financing complete acquisition quartz mountain gold project oregon usa advance mine centre camp ontario canada federal reserve cut rate next month federal reserve cut rate next month gas responds criticism pipeline program ratehike case raising cane open ann arbor location september company metro detroit trump administration kill wasteful funding humboldt bay offshore wind project sunblock charcoal powerball holiday weekend lottery drawing worth billion sunblock charcoal powerball holiday weekend lottery drawing worth billion sunblock charcoal powerball holiday weekend lottery drawing worth billion sunblock charcoal powerball holiday weekend lottery drawing worth billion ardot seeking public proposed disadvantaged business enterprise goal twice buying private equity k nasb financial declares cash dividend common stock sunblock charcoal powerball holiday weekend lottery drawing worth billion news ulta beauty delivers strong quarter investor brush glow thought die tunisian singer detained fight deportation finish music small business joint venture coast guard cyber contract dupont sell kevlar business billion manufacturer life insurance company grows tesla tsla stock market news today market slide chip stock weigh spsp complete index seeking alpha layoff hit international paper jb hunt hormel orange peel year put asheville map staffer buy cv walgreens require prescription covid vaccine colorado denver post hong kong eric trump lauds growing influence crypto new york forecasting future analyst projection oneok option market mastercard lazr investor opportunity lead luminar technology security fraud lawsuit sword availability h financial report sword h report liquidity agreement contracted oddo bhf procter gamble unusual option activity forecasting future analyst projection dt midstream dows option frenzy pce inflation flat core sticky implication fed september meeting analyst expectation targa resourcess future breaking karooooo analyst share view segg medium unveils nextgeneration corporate website showcasing completion turnaround launch growth phase glimpse expert outlook cheniere energy analyst rivian automotive gaining losing market support peering extreme networkss recent short interest indianola kwik star ribbon cutting expert outlook snapon eye analyst flex gaining losing market support pe ratio insight bank nova scotia knoxville planning zoning administrator nathan parch part segg medium unveils nextgeneration corporate website showcasing completion turnaround launch growth phase government publishes gdp data bitcoin ethereum blockchains price okanagan kamloops area levelling housewise chainlink link price movement face hurdle litecoin target rally cold wallet roi edge major discount outdoor furniture costway dining set target bytedance hit b valuation q revenue surge b energy exchange electronx earns cftc designated market clearing approval senior borrow equity without refinancing crypto news today coinshares profit jump avalanche transaction rise gumi add xrp robotics surged savvy shopper save k year extreme couponing scored k jcpenney cookware backtoschool sale tax holiday edmund fitzgerald microbe theyre among bill august buy lucid stock ahead reverse stock split bitcoin drop xrp slide eth dogecoin wobble shopping labor day furniture sale tip bargain best price ollies bargain earnings suggest analyst underestimate longterm potential ruling friday trump attempt fire fed credit race closing perception gap welcome new china era look lot different dell struggle protect margin supply chain cost mount cracker barrel ditched new logo got rid something else labubu doll affordable latte chinese brand betting big business insider mycarrier portal carrier assure integrate carrier vetting easier cracker barrel deep dei uncle herschel trans mountain ceo head major project office canada cracker barrel ditch logo maga meltdown beast cracker barrel new logo pitiful chain original executive anthony brown maryland legal victory prudent resource reader commentary atlanta becomes largest metro without printed newspaper journalconstitution digital techstock skid sends nasdaq sharply lower stockmarket update understanding benefit risk ai agent university northern iowa open finance real estate analytics lab business eli lilly proof wall street star dont tech titan trump fire democratic transportation board considers largest railroad merger history marvell sink weak data center outlook stokes custom ai chip worry reuters mount logan capital shareholder approve previously announced business combination degree capital corp court block trump effort end protected status venezuelan mamdani team sharpton threaten wall street upcoming upgrade holocaust museum exhibit spark staff concern source trump planning immigration crackdown chicago next dhs source gov gretchen whitmer call special election senate seat split michigan chamber gov gretchen whitmer call special election senate seat split michigan chamber gov gretchen whitmer call special election senate seat split michigan chamber gov gretchen whitmer call special election senate seat split michigan chamber gov gretchen whitmer call special election senate seat split michigan chamber gov gretchen whitmer call special election senate seat split michigan chamber migrant defer american dream seek asylum mexico bonus editorial cartoon aug alabama town black mayor reelected locked office lawyer led karen defense step closer joining team civil suit trump move cut bn foreign aid approved congress rubio revoke visa palestinian denying address un meeting alabama town black mayor reelected year white resident locked office cbs news tv help prepare invasion jd vance dems learn trump critic cant believe serious jd vance dems learn trump critic cant believe serious abrego garcia asks gag order bondi noem meet bill pulte trump housing center latest fed controversy abrego garcia asks gag order bondi noem judge weighs request block trump firing fed governor lisa cook abrego garcia asks gag order bondi noem contract fail alberta government teacher possible strike loom alberta republican joni ernst seek reelection source abrego garcia asks gag order bondi noem trump yank kamala harris bidenextended taxpayerfunded secret service protection book tour susan estrich epitome dumbness judge hears argument lisa cook attempted firing trump administration psc answer preston county commission objection marl project corruption allegation impact argentina president mileis popularity trump block b foreign aid congress okd maneuver seen nearly year ago trump block b foreign aid congress okd maneuver seen nearly year ago mackinac island police chief resign citing ongoing friction council lament shrinking middle class reader commentary dear annie unfaithful fiancee stop living past appeal court block trump administration ending legal protection venezuelan appeal court block trump administration ending legal protection venezuelan appeal court block trump administration ending legal protection venezuelan trumpbrokered peace deal south caucasus hopeful incomplete employeefriendly labor law take effect nlrb remains quorumless benton county display god trust public building oct everyone x laugh dingus gungrabber share pic bullet scattered street democrat republican cry outrage trump rare tactic withhold approved foreign aid funding lori falce year thought prayer appeal court uk asylumseekers stay hotel dc federal judge weigh order blocking fed gov lisa cook firing ahead interest rate meeting knoxville planning zoning administrator nathan parch part donald trump war culture sideshow japan india deepen security economic tie amid tariff ai ummasking officer washington anything politico public trust election increase fact sen ernst iowa expected announce next month wont run reelection revoke visa palestinian ahead un general assembly fox news star call trump ally apparent hypocrisy sen ernst iowa expected announce next month wont run reelection news fox news star call trump ally apparent hypocrisy free speech unmuted president trump executive order flag desecration joke san jose mayor slam california legislature lack prop funding ransomware attack targeting pa attorney general lead case delay susan collins rip trump unlawful effort cancel billion foreign aid susan collins rip trump unlawful effort cancel billion foreign aid susan collins rip trump unlawful effort cancel billion foreign aid texas bill resident sue outofstate abortion pill provider texas bill resident sue outofstate abortion pill provider texas bill resident sue outofstate abortion pill provider texas bill resident sue outofstate abortion pill provider chicago trump administration sight next immigration crackdown chicago trump administration sight next immigration crackdown trump admin plan immigration enforcement surge boston politico trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows trump threatens guard troop law allows kilmar abrego garcia asks gag order pam bondi kristi noem kilmar abrego garcia asks gag order pam bondi kristi noem texas gov greg abbott sign new congressional redistricting map president trump requested kimball shinkoskey explain law trump riviera gaza persist israel push deeper gaza france germany vow pressure ogre putin bankruptcy north dakota western minnesota published aug trump administration cut plus job voice america best business line credit flexible small business funding option growth emergency adhesive dowel veneer industrial choice shaping mass timber verizon fix modeonly issue phone amid outage hindustan hindustan fed tie vote bank england break deadlock month milwaukee battery harbor freight tool ulster county rail trail study contracted new paltzbased consulting firm tim walz admits vp bid hurt voter judge delay septum rate increase additional service cut gas price killeen area per gallon place kari lake lay voa parent agency amid legal battle doesnt surprise memark cuban explains high school senior care making money generation year cnc deadline alert rosen longstanding law firm encourages centene corporation investor secure counsel important september deadline security class action cnc bet bonus code orl bet oregon v montana bonus bet bemidji chamber ambassador welcome thrivent financial advisor letter illegal dumping support wastetoenergy sound name bias hiring decision writer bloc push change electoral college give future climate action strengthening italian finance new era takeover consolidation trading partner dazed confused tariff court loss delaware ag secure americorps funding winning suit solana etf buzz fade investor shift magacoin finance rising star best soundbars wireless rear speaker cryptos x richer mirroring pepe coin pepe run best small business loan option owner qualify compare program secure fast funding rok financial happens trump tariff federal appeal court knocked cracker barrel waffle house south heated food debate amid logo saga ai cant install hvac system gen z flocking job trade navigating client conundrum california payday loan online day credit bad credit guaranteed approval radcred launch payday loan platform immediate financial relief california borrower usa kari lake lay staff voice america parent agency washington post amazon selling laptop thats nice responsive lien car buy appeal court ruling trump tariff upend bond market barrons appeal court ruling trump tariff upend bond market lien car buy sameday business loan fast approval owner facing urgent cash flow lien car buy madison county wind impact public safety money new tax bill impact wallet ultimate plantbased beet burger mowest reveal library renovation cuba energy crisis deepens blackout grip nation best crypto invest blockdag rtx hyper snort gaining attention europe redrawing energy map rosen global investor counsel encourages easterly rocmuni high income municipal bond fund cryptos accumulate ozak ai xdc cro trx vechain carol saline dy journalist story dying powerball jackpot rise billion sixthlargest ever sunblock charcoal powerball holiday weekend lottery jackpot worth billion grab larimer county restaurant inspection aug china xi offer backing myanmar sco membership bid wamco deadline notice rosen trusted investor counsel encourages western asset management company llc mutual fund investor loss excess k secure counsel important september deadline security class action merz promise debt relief municipality ahead electoral test burlington store nyseburl announces quarterly earnings beat estimate eps trading partner dazed confused tariff court loss bloombergcom trading partner dazed confused tariff court loss shopper electronics clothes school supply worth taxfree exemption final hour spirit airline bankruptcy tee painful cut survival bid novelty menu taco bell yk investor money southwest airline begin flying plane secondary cockpit barrier reuters stock retail discussing performed open bull mdb nvda baba channel rewind growth spark conflict video vault wireless printer r paige thomason caramel pecan turtle brownie recipe dogecoin price prediction doge alternative x gain bull cycle billion powerball jackpot grab saturday play austin americanstatesman baird financial acquires share qualcomm incorporated qcom best water stock watch august walmart wmt share purchased titleist asset management llc deadline approach nomination eu work frozen russian asset aid ukraine war white house release americorps funding maryland lawsuit white house release americorps funding maryland lawsuit groundbreaking housing cooperative upper hammonds plain commentary lawmaker trim electric bill baird financial acquires share ishares core sp etf ivv kodai capital management lp invests honeywell international hon haberman call tariff ruling big blow trump agenda orange county restaurant shut health inspector aug costcos controversial policy change officially take effect costcos controversial policy change officially take effect mcdonalds corporation mcd share sold baird financial warren buffett warns invest terrible industry rewarding struggling quicksand micron boeing lead stock buy yearold retail chain closed dozen store risk order become must wont billionaire grant cardone hard work defines success court ruled trump tariff illegal whats next tesla lawyer judge throw million verdict saying mention elon musk misled jury tesla lawyer judge throw million verdict saying mention elon musk misled jury fortune promising value stock eye august adam thielen take pay cut viking excited insight wealth partner llc new investment palantir technology pltr insight wealth partner llc holding jpmorgan chase co jpm deeply affordable halawa rental tower nearly full best altcoins buy ethereum xrp magacoin finance highlighted market dip letter charlotte county goodpaying job young american expect inherit average new survey millennials gen z banking family wealth buford pusser famous tennessee sheriff inspired hollywood killed wife authority mayor brandon johnson executive order ban law enforcement wearing mask amid impending immigration crackdown mayor brandon johnson executive order ban law enforcement wearing mask amid impending immigration crackdown look race replace canada rapidly aging fleet submarine hilarious antivance demonstrator line protest motorcade turn sends chasing car trenton raise ukrainian flag hall help area organization photo college face financial struggle trump policy send international enrollment plummeting college face financial struggle trump policy send international enrollment plummeting election ejection chicago mayor dems warning illegal alien poll street palestinian flee israel assault gaza cal thomas flagging flag burner ny gov hochul press office account thats outdo newsom press office account naomi osaka call jelena ostapenko controversial remark taylor townsend ukraine exparliamentary speaker shot dead lviv dave bossie dnc mamdani expose coming disaster democrat monday labor day whats open whats closed wisconsin conservative supreme justice rebecca bradley wont seek reelection fate intervenes family avoids execution holocaust asking eric since husband killed family nothing child salmo voter approval new firetruck nelson trump revenge summer heat fed ouster bolton raid trump revenge summer heat fed ouster bolton raid new yorkers must fight political manipulation ccp united federation teacher collegian marlboro rhinebeck resident graduate university rhode island tania fernandes anderson asks judge dodge prison public corruption israel soon halt slow aid northern gaza military offensive grows israel soon halt slow aid northern gaza military offensive grows israel soon halt slow aid northern gaza military offensive grows doj call tip employer favoring foreign worker hiring practice flag campaignwe cant reclaim never school board removing protection doe give bully trump cast doubt putinzelensky meeting maybe fight little longer gaza aid flotilla exist thunberg gaza aid flotilla exist thunberg gaza aid flotilla exist thunberg gaza aid flotilla exist thunberg gaza aid flotilla exist thunberg gaza aid flotilla exist thunberg gaza aid flotilla exist thunberg gaza aid flotilla exist thunberg thousand protest israeli siege gaza venice film festival thousand protest israeli siege gaza venice film festival thousand protest israeli siege gaza venice film festival thousand protest israeli siege gaza venice film festival thousand protest israeli siege gaza venice film festival thousand protest israeli siege gaza venice film festival thousand protest israeli siege gaza venice film festival thousand protest israeli siege gaza venice film festival thousand protest israeli siege gaza venice film festival thousand protest israeli siege gaza venice film festival thousand protest israeli siege gaza venice film festival nh democrat launch town hall series promote presidential primary chicago mayor sign executive order directing resist trump immigration raid social security whistleblower claim doge mishandled american sensitive data resigns post social security whistleblower claim doge mishandled american sensitive data resigns post social security whistleblower claim doge mishandled american sensitive data resigns post social security whistleblower claim doge mishandled american sensitive data resigns post social security whistleblower claim doge mishandled american sensitive data resigns post social security whistleblower claim doge mishandled american sensitive data resigns post social security whistleblower claim doge mishandled american sensitive data resigns post social security whistleblower claim doge mishandled american sensitive data resigns post israel soon halt slow aid northern gaza military offensive grows israel soon halt slow aid northern gaza military offensive grows israel soon halt slow aid northern gaza military offensive grows florida python hunter recount bloody battle snake got son look hard end war gaza look hard end war gaza look hard end war gaza look hard end war gaza look hard end war gaza look hard end war gaza look hard end war gaza look hard end war gaza look hard end war gaza got take lodis mayor day accepting application local student border czar ops ramp seattle portland labor day unofficial election strike delay start class southwest washington school district people calling jd vance habit single obnoxious characteristic agree epstein estate birthday book lawmaker house dem saturday morning college face financial struggle trump policy send international enrollment plummeting letter something feel hopeful letter far fewer cost votebymail election dncs summer showdown infighting expose crack democrat unity narrative gop agenda law enforcement increasing patrol across new hampshire labor day weekend lawyer punished undignified discourteous criticism judge kellyanne conway revel trump insane power grab cracker barrel fiasco israel soon halt slow aid northern gaza military offensive grows detains somaliamerican activist ramsey county sheriff civilian officer worker billionaire protest labor day axios macron warns world monday putin played trump greenlights million sale starlink service patriot support ukraine election balk doj request sensitive voter information election balk doj request sensitive voter information caring america vulnerable kid become political opinion assembly bill undermines prop put public safety risk chicago plan maintain peace amid federal deployment bondi fire doj employee alleged gesture guard troop jd vance discusses readiness president god forbid something happens trump department defense conduct training exercise philly starting sunday summerlins kestrel kestrel common offer unique floor plan whats open whats closed labor day store hour walmart costco target publix alcom best crypto buy magacoin finance gain traction solana xrp avax whale inflow sen rand paul national debt werent warned magax stage countdown secure entry next wave begin save new appliance wayfair kitchenaid mixer ninja creami anyone powerball lottery jackpot swell billion woodside open acacia cadence china xi host modi putin summit amid anger trump tariff daron bland contract cowboy cb agrees massive extension returning pro bowl form surfshark face classaction lawsuit autorenewal violation final countdown meme coin invest next x surge hit midhudson people move sept nvidia lean heavily undisclosed customer revenue boom china india pledge partnership ahead putin joining summit guardian pitcher paid extended indefinitely mlb continues gambling probe rosen ranked global counsel encourages luminar technology investor secure rosen ranked global counsel encourages luminar technology investor secure rosen ranked global counsel encourages luminar technology investor secure grover norquist idea next gop reconciliation bill fed losing independence affect american everyday life social security medicare cut coming bond market eventually congress knee economist fy energy launch multilevel affiliate program expand access cleanpowered crypto infrastructure cardano price support worried holder altcoins potential remittix social security medicare cut coming bond market force congress economist fortune amazon labor day sale filled surprisingly good deal rosen ranked global counsel encourages luminar technology investor secure counsel important deadline security class action lazr bob business fort worth ridglea theater look reel buyer nvidia q ai drive growth amid revenue concentration risk lithonias recreation center massive renovation upgrade crypto news ozak ai presale heat raisednext x token tesla unexpectedly end contract giga texas letting people tesla unexpectedly end contract giga texas letting people electrek gen z shift aiproof trade plumbing job security business brief postal carrier retires almost year service intel secures b accelerated chip funding equity stake working trade deal court ruling ustr trump tariff spark pricing chaos business month vintage photo role woman workforce evolved year felt dead goldman sachs banker leaving build startup seoul store restaurant open labor day ignore ethereum buy surging altcoin instead best samsung phone r budget pick deliver hbar price set gain q altcoin investor x november future trump tariff ruling matter stock investor business touted teslakiller lucid scramble stay nasdaq kemp jones reaped big money company interest legislation kemp jones reaped big money company interest legislation builderais b rise collapse highlight fragility ai boom seeking alpha kemp jones reaped big money company interest legislation final chance cash bonus major bank putting away day secure people spending tech red flag july report gizmodo people spending tech red flag july report popular weightloss stock massive heartsaving claim trump trade counselor peter navarro rebuke politician black robe partisan tariff ruling mindanao busine</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2198,6 +2198,42 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45903</v>
+      </c>
+      <c r="B50" t="n">
+        <v>6448.259765625</v>
+      </c>
+      <c r="C50" t="n">
+        <v>6453.669921875</v>
+      </c>
+      <c r="D50" t="n">
+        <v>6416.169921875</v>
+      </c>
+      <c r="E50" t="n">
+        <v>6445.81982421875</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4465360000</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.0051000736279842</v>
+      </c>
+      <c r="H50" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>the winklevoss twin are eyeing billion crypto ipo trump cant use national guard military in california to enforce law judge breyer rule family of max crash victim push to appoint a special prosecutor saying boeing is trying to buy everyone off gold smash record a ratecut bet policy turmoil fuel haven rush coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war palantir stock struggle a valuation criticism and ceo sale weigh on investor coming price cut at mcdonalds could signal a broader fast food price war coming price cut at mcdonalds could signal a broader fast food price war turkiyes huge summer of transfer explained how galatasaray and fenerbahce can outspend europe big club anthropic nearly triple valuation to b with massive new funding disney to pay million over alleged violation of childrens online privacy army pick startup to fasttrack selfdriving squad vehicle ai chatbots for doctor are hot but there plenty of value down the stack too argues corti ceo genesee county architecture firm selects yearold batavia house for new hq hundred of economist defend lisa cook fed independence in open letter against trump effort coming price cut at mcdonalds may signal a broader fast food price war a trump tariff struggle in the court there a simple solution he could consider top trending topic of august the less independent the fed is the more the yield curve will steepen national alliance brenner sap to invest billion in europe sovereign cloud anna wintour tap chloe malle a vogue successor but shes still in charge marcus where you are and where youve been stock are experiencing a healthy reset say citis drew pettit ubs give america a recession checkup and see a probability from the hard data with a soggy economy ahead fortune mcdonalds will launch new value meal on monday sept mcdonalds will launch new value meal on monday sept amazon end a program that let prime member share free shipping perk with user outside household amazon end a program that let prime member share free shipping perk with user outside household general assembly looking to reinvigorate staterun venture capital fund fi deadline rosen leading investor counsel encourages fiserv inc investor with loss in excess of k to secure counsel before important deadline in security class action fi trifork group reporting of transaction made by person discharging managerial responsibility clean any screen or lens with the infinitely reuseable waterbear screen cleaner exbudget staffer weigh in against trump pocket rescission offstrip casino team up with new bookmaker proposed budget for west aurora school district show million surplus save big on top gaming gear from walmart now score headset laptop desktop more company kick off ipo roadshow market rally still ha room to run where to invest what are analytical insight wet strength resin market to reach u million by astute analytica blue apron pivot amid our subscription fatigue coreweave stock crwv sink a insider sell at an alarming pace tipranks kraft heinz to separate into two publicly traded company predoc raise million for aipowered health information management system space stock tracker trump move space command rocket lab open launch complex crocs appoints nike alum to cfo chair coreweave tumble a top shareholder magnetar dial down position put on huge collar trade sherwood news bitcoin buck stock market downtrend but lag gold rally congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process solana early investor who bought at and exited at ath belief only new crypto can repeat sol rise congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process congress return but trump pocket rescission snarl govt funding process openai and meta say theyre fixing ai chatbots to better respond to teen in distress openai and meta say theyre fixing ai chatbots to better respond to teen in distress costco told to review footage after store manager blatantly accused shopper of ignoring strict store policy nestle dismisses ceo over undisclosed relationship with subordinate nestle dismisses ceo over undisclosed relationship with subordinate egg milk bread all rising a summer close royce microcap trust nyse rmt a of jul how low will mortgage rate fall with a september fed rate cut here what to know trump and son stake in crypto firm worth bn the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way the rule for cash how to manage your money the smart way tesla trillion secret musk say robot could be of it value coming price cut at mcdonalds may signal a broader fast food price war stafford co mull zoning regulation government shutdown on oct seen a increasingly likely exclusive disney will pay m to settle childrens privacy lawsuit with ftc axios ace hardware crave cooky among new business in sugar landmissouri city bet bonus code njcom unlock a guaranteed bonus for mlb u open today syndeo medical announces multiyear exclusive distribution agreement for bearpacs passiotm pump drainage system irbt deadline rosen recognized investor counsel encourages irobot corporation investor with loss in excess of k to secure counsel before important september deadline in security class action irbt the white house premium how washington is creating ai stock rocket openai shuffle executive role acquires statsig for billion openai shuffle executive role acquires statsig for billion the verge salesforce advantage over hubspot and mondaycom highlight relative valuation an expanded version of the dol opinion letter program return what do retail employer need to know jefferies david katz bullish call for cruise maryland man collect his second big lottery prize in two month elliott management look to put fizz back into pepsi with b stake a it press for a turnaround amazon prime signups reportedly lagged in u leading up to annual sale event pennsylvania democrat attract some buzz in the party bid to take back u house turn out trump cant turn activeduty troop into police officer after losing two antiviolence worker to gunfire chicago nonprofit persists we have to be strong why is bangladesh saying it can no longer host rohingya school shouldnt wait for legislature to ban cellphone use the republican editorial pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge why are our church no longer safe annunciation school shooting raise alarming question letter to the editor sen joni ernst will not run for reelection in live now gop hold press conference on federal authority over dc a trump tariff struggle in the court there a simple solution he could consider trump tariff decision an emergency will appeal a soon a wednesday axios what america should know about wes moore guest commentary gov healey slam republic service over stalled trash strike talk kim jong un daughter and possible heir make rare foreign appearance poll what should be the new massachusetts flag the judge who defied trump now face brazil biggest case what is the posse comitatus act yearold law governs military role in local law enforcement voter registration trend unchanged at traditional summer end cimg inc completes the previously announced sale of million of it common stock for bitcoin pentagon authorizes military lawyer to serve a temporary immigration judge pentagon authorizes military lawyer to serve a temporary immigration judge pentagon authorizes military lawyer to serve a temporary immigration judge tim walz appears to tell supporter all is not lost because trump will die soon watch profane rashida tlaib rant target israel backer in wild unhinged tirade how much ha your devon county councillor spent in their community so far british wife of trump voter face deportation after year in u amid immigration crackdown saga education launch tutoring partnership with brooklyn lab to accelerate math learning a life lived herman lyon carried the horror of war with strength and courage harford council district f incumbent jacob bennett run for reelection harford council district f incumbent jacob bennett run for reelection tv writer graham linehans arrest over transgender post spark free speech outcry in the uk tv writer graham linehans arrest over transgender post spark free speech outcry in the uk gop rep thomas massie take first step to force a vote on releasing the epstein file texas dei ban expands to public school face federal lawsuit u drone strike cartel drug boat trump post video for world to see beware uk comedy writer graham linehan arrested over social medium post criticizing trans activist gavin newsom brutally taunt trump after major legal victory trump face new epstein headache a congress return from recess israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive airbnb cofounder share when he lost faith in dem party switched to gop israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive springfield garden could be banned from owning managing property in mass ag campbell say what is a pardon and who is eligible wichita criminal defense lawyer who will replace jerry nadler who will retire in after year in congress repping manhattan looking back on japan surrender in wwii year later trump expected to speak shortly a majority of nevada legislation aimed at government transparency failed during the session in the martian author david baron explores mar mania of the th century israel continues to intensify offensive in gaza city rep jerry nadler announces retirement citing bidens oneterm presidency politico ussfcu win dual honor at broadcom customer achievement award trial of greensboro native accused of attempting to assassinate trump set for sept court annuls istanbul congress of turkey main opposition party dismisses leadership court annuls istanbul congress of turkey main opposition party dismisses leadership ernst wont seek reelection giving democrat opening in battle for senate israel start calling up reservist a it push into initial stage of gaza city offensive israel start calling up reservist a it push into initial stage of gaza city offensive pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge madness in minneapolis court allows trump admin close in on yanking back bidens gold bar pentagon authorizes up to military lawyer to serve a temporary immigration judge pentagon authorizes up to military lawyer to serve a temporary immigration judge delray beach argues to keep it rainbow intersection at hearing in orlando delray beach argues to keep it rainbow intersection at hearing in orlando judge dismisses lawsuit springfield joined over terminated m epa grant labor day protester across the country demand worker right decry ice labor day protester across the country demand worker right decry ice</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>winklevoss twin eyeing billion crypto ipo trump cant national guard military california enforce law judge breyer rule family max crash victim push appoint special prosecutor saying boeing buy everyone gold smash record ratecut bet policy turmoil fuel rush coming price cut mcdonalds signal broader fast food price war coming price cut mcdonalds signal broader fast food price war coming price cut mcdonalds signal broader fast food price war coming price cut mcdonalds signal broader fast food price war coming price cut mcdonalds signal broader fast food price war coming price cut mcdonalds signal broader fast food price war coming price cut mcdonalds signal broader fast food price war palantir stock struggle valuation criticism ceo sale weigh investor coming price cut mcdonalds signal broader fast food price war coming price cut mcdonalds signal broader fast food price war turkiyes summer transfer explained galatasaray fenerbahce outspend europe big club anthropic nearly triple valuation b massive new funding disney pay million alleged violation childrens online privacy army pick startup fasttrack selfdriving squad vehicle ai chatbots doctor hot plenty value stack argues corti ceo genesee county architecture firm selects yearold batavia house new hq economist defend lisa cook fed independence open letter trump effort coming price cut mcdonalds signal broader fast food price war trump tariff struggle court simple solution consider trending topic august less independent fed yield curve steepen national alliance brenner sap invest billion europe sovereign cloud anna wintour tap chloe malle vogue successor shes charge marcus youve stock experiencing healthy reset citis drew pettit ubs give america recession checkup probability hard data soggy economy ahead fortune mcdonalds launch new value meal monday sept mcdonalds launch new value meal monday sept amazon end program prime share free shipping perk user outside household amazon end program prime share free shipping perk user outside household general assembly reinvigorate staterun venture capital fund fi deadline rosen leading investor counsel encourages fiserv investor loss excess k secure counsel important deadline security class action fi trifork reporting transaction discharging managerial responsibility clean screen lens infinitely reuseable waterbear screen cleaner exbudget staffer weigh trump pocket rescission offstrip casino team new bookmaker proposed budget west aurora school district million surplus save big gaming gear walmart score headset laptop desktop company kick ipo roadshow market rally room run invest analytical insight wet strength resin market reach million astute analytica blue apron pivot amid subscription fatigue coreweave stock crwv sink insider sell alarming pace tipranks kraft heinz separate publicly traded company predoc raise million aipowered health information management system space stock tracker trump move space command rocket lab open launch complex crocs appoints nike alum cfo chair coreweave tumble shareholder magnetar dial put collar trade sherwood news bitcoin buck stock market downtrend lag gold rally congress trump pocket rescission snarl govt funding process congress trump pocket rescission snarl govt funding process congress trump pocket rescission snarl govt funding process congress trump pocket rescission snarl govt funding process solana early investor bought exited ath belief new crypto repeat sol rise congress trump pocket rescission snarl govt funding process congress trump pocket rescission snarl govt funding process congress trump pocket rescission snarl govt funding process congress trump pocket rescission snarl govt funding process openai meta theyre fixing ai chatbots better respond teen distress openai meta theyre fixing ai chatbots better respond teen distress costco review footage store manager blatantly accused shopper ignoring strict store policy nestle dismisses ceo undisclosed relationship subordinate nestle dismisses ceo undisclosed relationship subordinate egg milk bread rising summer close royce microcap trust nyse rmt jul low mortgage rate fall september fed rate cut trump son stake crypto firm worth bn rule cash manage money smart rule cash manage money smart rule cash manage money smart rule cash manage money smart rule cash manage money smart rule cash manage money smart rule cash manage money smart rule cash manage money smart rule cash manage money smart rule cash manage money smart tesla trillion secret musk robot value coming price cut mcdonalds signal broader fast food price war stafford co mull zoning regulation government shutdown oct seen increasingly likely exclusive disney pay settle childrens privacy lawsuit ftc axios ace hardware crave cooky among new business sugar landmissouri bet bonus code njcom unlock guaranteed bonus mlb open today syndeo medical announces multiyear exclusive distribution agreement bearpacs passiotm pump drainage system irbt deadline rosen recognized investor counsel encourages irobot corporation investor loss excess k secure counsel important september deadline security class action irbt white house premium washington creating ai stock rocket openai shuffle executive role acquires statsig billion openai shuffle executive role acquires statsig billion verge salesforce advantage hubspot mondaycom highlight relative valuation expanded version dol opinion letter program retail employer jefferies david katz bullish call cruise maryland man collect big lottery prize month elliott management look put fizz pepsi b stake press turnaround amazon prime signups reportedly lagged leading annual sale event pennsylvania democrat attract buzz party bid take house turn trump cant turn activeduty troop police officer losing antiviolence worker gunfire chicago nonprofit persists strong bangladesh saying longer host rohingya school shouldnt wait legislature ban cellphone republican editorial pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge church longer safe annunciation school shooting raise alarming letter editor sen joni ernst run reelection gop press conference federal authority dc trump tariff struggle court simple solution consider trump tariff decision emergency appeal soon wednesday axios america wes moore guest commentary gov healey slam republic service stalled trash strike kim jong un daughter possible heir rare foreign appearance poll new massachusetts flag judge defied trump face brazil biggest case posse comitatus act yearold law governs military role local law enforcement voter registration trend unchanged traditional summer end cimg completes previously announced sale million common stock bitcoin pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge tim walz supporter trump die soon watch profane rashida tlaib rant target israel backer wild unhinged tirade devon county councillor spent community far british wife trump voter face deportation year amid immigration crackdown saga education launch tutoring partnership brooklyn lab accelerate math learning life lived herman lyon carried horror war strength courage harford council district f incumbent jacob bennett run reelection harford council district f incumbent jacob bennett run reelection tv writer graham linehans arrest transgender post spark free speech outcry uk tv writer graham linehans arrest transgender post spark free speech outcry uk gop rep thomas massie take step force vote releasing epstein file texas dei ban expands public school face federal lawsuit drone strike cartel drug boat trump post video world beware uk comedy writer graham linehan arrested social medium post criticizing trans activist gavin newsom brutally taunt trump major legal victory trump face new epstein headache congress recess israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive airbnb cofounder share faith dem party switched gop israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive springfield garden banned owning managing property mass ag campbell pardon eligible wichita criminal defense lawyer replace jerry nadler retire year congress repping manhattan japan surrender wwii year later trump expected speak shortly majority nevada legislation aimed government transparency failed session martian author david baron explores mar mania century israel continues intensify offensive gaza rep jerry nadler announces retirement citing bidens oneterm presidency politico ussfcu dual honor broadcom customer achievement award trial greensboro native accused attempting assassinate trump set sept court annuls istanbul congress turkey main opposition party dismisses leadership court annuls istanbul congress turkey main opposition party dismisses leadership ernst wont seek reelection giving democrat opening battle senate israel start calling reservist push initial stage gaza offensive israel start calling reservist push initial stage gaza offensive pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge madness minneapolis court allows trump admin close yanking bidens gold bar pentagon authorizes military lawyer temporary immigration judge pentagon authorizes military lawyer temporary immigration judge delray beach argues rainbow intersection hearing orlando delray beach argues rainbow intersection hearing orlando judge dismisses lawsuit springfield joined terminated epa grant labor day protester across country demand worker decry labor day protester across country demand worker decry</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2234,6 +2234,42 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45904</v>
+      </c>
+      <c r="B51" t="n">
+        <v>6502.080078125</v>
+      </c>
+      <c r="C51" t="n">
+        <v>6502.5400390625</v>
+      </c>
+      <c r="D51" t="n">
+        <v>6445.97998046875</v>
+      </c>
+      <c r="E51" t="n">
+        <v>6456.60009765625</v>
+      </c>
+      <c r="F51" t="n">
+        <v>4670770000</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.008346486409699301</v>
+      </c>
+      <c r="H51" t="n">
+        <v>1</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>dixons proposed comprehensive plan outline city official goal for increased housing walkability smallcap etf just became the hot new tradethanks to powell dollar general warns of price increase jacksonshaw proudly announces opening of dualbranded la vega symphony park hotel the u housing market where insurance cost are the highest say goodbye to these store in sept amid major wave of retail closure money move to make if you win the billion powerball jackpot tonight or get a similar financial windfall wall street steady with a boost from alphabet conocophillips to slash workforce by up to holiday spending expected to drop this yearled by sharpest decline from gen z xrp news today xrp remains bullish miner earn kday a fed cut expectation boost crypto market amazon is selling comfortable adidas sneaker for just pc commissioner seeking funding for il feed yard support infrastructure trump approval rating unchanged from last week at in latest poll security fraud investigation into avita medical inc rcel continues investor who lost money urged to contact the law office of frank r cruz portland city council approves levying fine on owner of vacant commercial property trumpy news outlet sue fox news for dominating conservative tv rebrand misfire elsmere to resume negotiation for new admin facility communal spa and sauna proposed in fairfax spectrum brand terminates cfo to cut cost u money reserve and mike rowe honor skilled tradespeople with launch of trade of america ultra high relief silver coin should you use ai to negotiate your credit card debt most home for sale in la vega valley are unaffordable for local report say nio stock forecast can china tesla regain it spark clark county council debate percent sale tax increase to raise m for affordable housing tillis say he will not consider lisa cook fed replacement amid legal dispute politico tesla bull move into the driver seat so do robotaxi safety monitor dceda launch workforce nonprofit dekalb work inc how a billion deal will impact this houstonbased company strategy polymarket authorized for u return day after trump jr join a advisor bestselling vacuum cleaner in top pick irobot corporation sued for security law violation contact the dj law group to discus your right irbt select american to get check every month a part of firstofitskind program defining retail new rhode island rule clarify sunday and holiday premium pay calculation scouted writing on this portable tablet feel just like pen on paper polo star nacho figueras buy condo in celebrity chef building in miami hedge fund and insider trading news ken griffin michael burry ray dalio warren buffett jane street huntington ingalls industry inc hii kla corp klac and more u oil giant conocophillips will lay off up to of it work force the new york time the superman sequel man of tomorrow will arrive summer conservative news network newsmax file antitrust lawsuit against fox news beige book most distructs reported little or no change in economic activity water to attend upcoming investor conference in september modot announces major i eastbound lane shift at wentzville parkway a part of improve i project u rail freight narrowly up a key commodity sink marquis who who recognizes spotlight biographees for the third quarter of gold and silver price keep shining is it finally time to sell barrons july real estate brokerage labor cost index july real estate brokerage labor cost index water to attend upcoming investor conference in september water to attend upcoming investor conference in september lavrov praise india for not caving to u tariff pressure fengate break ground on new rental tower in mount dennis neighbourhood american eagle sydney sweeney and travis kelce campaign drove more than new customer evergy say federal change wont affect planned solar project in kansa and missouri evergy say federal change wont affect planned solar project in kansa and missouri evergy say federal change wont affect planned solar project in kansa and missouri cayman chemical and curapath partner to provide wider access to pegfree shielding lipid for lipid nanoparticles timeline key event in the troubled history of the boeing max jetliner timeline key event in the troubled history of the boeing max jetliner timeline key event in the troubled history of the boeing max jetliner timeline key event in the troubled history of the boeing max jetliner cooling strategy green ocean file motion for summary judgment to vacate federal approval for revolution wind green ocean file motion for summary judgment to vacate federal approval for revolution wind green ocean file motion for summary judgment to vacate federal approval for revolution wind green ocean file motion for summary judgment to vacate federal approval for revolution wind green ocean file motion for summary judgment to vacate federal approval for revolution wind the tragedy of a transactional age how t erik conleys lifelong passion for the investment market sparked a mission to empower everyday investor huntington beach council approves deal that subsidizes air show for up to year a trump loss in his tariff court case could mean a billion refund for american businessesheres how they could get their money back subdued decision in google antitrust trial may help keep a monopoly in power subdued decision in google antitrust trial may help keep a monopoly in power subdued decision in google antitrust trial may help keep a monopoly in power subdued decision in google antitrust trial may help keep a monopoly in power subdued decision in google antitrust trial may help keep a monopoly in power subdued decision in google antitrust trial may help keep a monopoly in power subdued decision in google antitrust trial may help keep a monopoly in power subdued decision in google antitrust trial may help keep a monopoly in power subdued decision in google antitrust trial may help keep a monopoly in power subdued decision in google antitrust trial may help keep a monopoly in power subdued decision in google antitrust trial may help keep a monopoly in power u holiday spending to suffer worst plunge since pandemic over tariff fear inflation gsa onegov deal hype billion in saving but should we buy into it subdued decision in google antitrust trial may help keep a monopoly in power a trump court loss on tariff could mean a billion refund for american business fortune cd v highyield saving account here which earns more now apple ha survived trump tariff so far it might raise iphone price anyway breaking boilwater notice announced for gulf cove area west virginia public broadcasting navigates postrescission funding issue west virginia public broadcasting navigates postrecission funding issue best phone of detailed guide on feature pricing and performance in a brawl over rightwing tv newsmax sue fox news in a brawl over rightwing tv newsmax sue fox news in a brawl over rightwing tv newsmax sue fox news npr frontier airline brings back annual flight pas what to know frontier airline brings back annual flight pas what to know we cant take it anymore governor order new office to fight utility rate hike in indiana idme raise million to expand digital identity solution rogue house republican help dems kill a vote to censure lamonica mciver in shock result axios the weeknight cohosts rebuke trump foiled plan to deport guatemalan child brave epstein survivor plead with trump who despicably demeans them a a hoax opinion lightfoot return to blast lawabiding gun store and maker for chicago felonious firearm frenzy can we reframe our past without sliding into selfdeception the ethical life podcast can we reframe our past without sliding into selfdeception the ethical life podcast can we reframe our past without sliding into selfdeception the ethical life podcast can we reframe our past without sliding into selfdeception the ethical life podcast can we reframe our past without sliding into selfdeception the ethical life podcast can we reframe our past without sliding into selfdeception the ethical life podcast can we reframe our past without sliding into selfdeception the ethical life podcast can we reframe our past without sliding into selfdeception the ethical life podcast fanduel partner with septum to restore broad street line service for eagle home opener bid to oust tarrant county district clerk from job dismissed by judge security fraud investigation into avita medical inc rcel continues investor who lost money urged to contact the law office of frank r cruz republican approve measure supporting epstein investigation amid discharge threat republican approve measure supporting epstein investigation amid discharge threat rogue house republican help dems kill a vote to censure lamonica mciver in shock result republican approve measure supporting epstein investigation amid discharge threat morning joe host say dem governor should call trump for reinforcement so they can save life former sen john sununu weighs new hampshire senate run former sen john sununu weighs new hampshire senate run house approves symbolic signal of support for oversight epstein investigation republican approve measure supporting epstein investigation amid discharge threat republican approve measure supporting epstein investigation amid discharge threat republican approve measure supporting epstein investigation amid discharge threat republican approve measure supporting epstein investigation amid discharge threat tariff trigger split between uaw and canada unifor republican approve measure supporting epstein investigation amid discharge threat rubio say u and mexico will strengthen security collaboration rubio say u and mexico will strengthen security collaboration rubio say u and mexico will strengthen security collaboration new november drinking law now carry jail time for driver after family battle for harderhitting punishment redistricting poised to spread ahead of midterm election redistricting poised to spread ahead of midterm election some recognition that were in trouble gop scramble to rebrand trump big beautiful bill boston mayoral candidate josh kraft make change to campaign team nadlers retirement reignites debate over advanced age of many in congress u approves million in assistance to nigeria to help address hunger u approves million in assistance to nigeria to help address hunger u approves million in assistance to nigeria to help address hunger poilievre call on ottawa to end temporary foreign worker program watch bipartisan representative hold news conference with epstein survivor ap news summary at pm edt ap news summary at pm edt marco rubio say trump admin will go on the offense against cartel full might of the u china flex military muscle with drone missile and ai robot wolf at world war victory parade watch epstein accuser speak outside u capitol free speech or vandalism frog bridge chalk draw debate arizona ag kris mayes and coalition of state file amicus brief to support federal worker collective bargaining right against trump order senate get point blueprint to corner rfk jr from excdc official trump say u strike targeting venezuelan gang will cause cartel to think twice epstein survivor implore congress to act a push for disclosure build epstein survivor implore congress to act a push for disclosure build water to attend upcoming investor conference in september the classless left harasses vice president vance a he meet with family of annunciation church victim uae warns against israeli annexation of west bank a strike in gaza kill uae warns against israeli annexation of west bank a strike in gaza kill uae warns against israeli annexation of west bank a strike in gaza kill uae warns against israeli annexation of west bank a strike in gaza kill president trump float deploying national guard troop to new orleans president trump float deploying national guard troop to new orleans npr president trump float deploying national guard troop to new orleans u approves million in assistance to nigeria to help address hunger european leader face tough choice a the uk and france host another meeting on ukraine clover health ceo andrew toy testifies before congress on the transformative role of ai in healthcare highlight how clover is leading the way uae warns against israeli annexation of west bank a strike in gaza kill froma harrop column are we beginning to fix immigration u approves million in assistance to nigeria to help address hunger the value of ceasefires trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump suggests national guard could go into new orleans a blue city in a red state trump targeting new orleans for guard deployment uk and spain sign cooperation deal a they seek to bolster postbrexit tie jamaican vote in tight leadership race guyana president poised for reelection green ocean file motion for summary judgment to vacate federal approval for revolution wind conservative news network newsmax file antitrust lawsuit against fox news</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>dixons proposed comprehensive plan outline goal increased housing walkability smallcap etf became hot new tradethanks powell dollar general warns price increase jacksonshaw proudly announces opening dualbranded la vega symphony park hotel housing market insurance cost highest goodbye store sept amid major wave retail closure money move billion powerball jackpot tonight similar financial windfall wall street steady boost alphabet conocophillips slash workforce holiday spending expected drop yearled sharpest decline gen z xrp news today xrp remains bullish miner earn kday fed cut expectation boost crypto market amazon selling comfortable adidas sneaker pc commissioner seeking funding il feed yard support infrastructure trump approval rating unchanged latest poll security fraud investigation avita medical rcel continues investor money urged contact law office frank r cruz portland council approves levying fine owner vacant commercial property trumpy news outlet sue fox news dominating conservative tv rebrand misfire elsmere resume negotiation new admin facility communal spa sauna proposed fairfax spectrum brand terminates cfo cut cost money reserve mike rowe honor skilled tradespeople launch trade america ultra high relief silver coin ai negotiate credit card debt sale la vega valley unaffordable local report nio stock forecast china tesla regain spark clark county council debate percent sale tax increase raise affordable housing tillis consider lisa cook fed replacement amid legal dispute politico tesla bull move driver seat robotaxi safety monitor dceda launch workforce nonprofit dekalb work billion deal impact houstonbased company strategy polymarket authorized day trump jr join advisor bestselling vacuum cleaner pick irobot corporation sued security law violation contact dj law discus irbt select american month part firstofitskind program defining retail new rhode island rule clarify sunday holiday premium pay calculation scouted writing portable tablet feel pen paper polo star nacho figueras buy condo celebrity chef building miami hedge fund insider trading news ken griffin michael burry ray dalio warren buffett jane street huntington ingalls industry hii kla corp klac oil giant conocophillips lay work force new york superman sequel man tomorrow arrive summer conservative news network newsmax file antitrust lawsuit fox news beige book distructs reported little change economic activity water attend upcoming investor conference september modot announces major eastbound lane shift wentzville parkway part improve project rail freight narrowly commodity sink marquis recognizes spotlight biographees third quarter gold silver price shining finally sell barrons july real estate brokerage labor cost index july real estate brokerage labor cost index water attend upcoming investor conference september water attend upcoming investor conference september lavrov praise india caving tariff pressure fengate break ground new rental tower mount dennis neighbourhood american eagle sydney sweeney travis kelce campaign drove new customer evergy federal change wont affect planned solar project kansa missouri evergy federal change wont affect planned solar project kansa missouri evergy federal change wont affect planned solar project kansa missouri cayman chemical curapath partner provide wider access pegfree shielding lipid lipid nanoparticles timeline event troubled history boeing max jetliner timeline event troubled history boeing max jetliner timeline event troubled history boeing max jetliner timeline event troubled history boeing max jetliner cooling strategy green ocean file motion summary judgment vacate federal approval revolution wind green ocean file motion summary judgment vacate federal approval revolution wind green ocean file motion summary judgment vacate federal approval revolution wind green ocean file motion summary judgment vacate federal approval revolution wind green ocean file motion summary judgment vacate federal approval revolution wind tragedy transactional age erik conleys lifelong passion investment market sparked mission empower everyday investor huntington beach council approves deal subsidizes air year trump loss tariff court case billion refund american businessesheres money subdued decision google antitrust trial help monopoly power subdued decision google antitrust trial help monopoly power subdued decision google antitrust trial help monopoly power subdued decision google antitrust trial help monopoly power subdued decision google antitrust trial help monopoly power subdued decision google antitrust trial help monopoly power subdued decision google antitrust trial help monopoly power subdued decision google antitrust trial help monopoly power subdued decision google antitrust trial help monopoly power subdued decision google antitrust trial help monopoly power subdued decision google antitrust trial help monopoly power holiday spending suffer worst plunge since pandemic tariff fear inflation gsa onegov deal hype billion saving buy subdued decision google antitrust trial help monopoly power trump court loss tariff billion refund american business fortune cd v highyield saving account earns apple survived trump tariff far raise iphone price anyway breaking boilwater notice announced gulf cove area west virginia public broadcasting navigates postrescission funding issue west virginia public broadcasting navigates postrecission funding issue best phone detailed guide feature pricing performance brawl rightwing tv newsmax sue fox news brawl rightwing tv newsmax sue fox news brawl rightwing tv newsmax sue fox news npr frontier airline brings annual flight pa frontier airline brings annual flight pa cant take anymore governor order new office fight utility rate hike indiana idme raise million expand digital identity solution rogue house republican help dems kill vote censure lamonica mciver shock axios weeknight cohosts rebuke trump foiled plan deport guatemalan child brave epstein survivor plead trump despicably demeans hoax opinion lightfoot blast lawabiding gun store maker chicago felonious firearm frenzy reframe past without sliding selfdeception ethical life podcast reframe past without sliding selfdeception ethical life podcast reframe past without sliding selfdeception ethical life podcast reframe past without sliding selfdeception ethical life podcast reframe past without sliding selfdeception ethical life podcast reframe past without sliding selfdeception ethical life podcast reframe past without sliding selfdeception ethical life podcast reframe past without sliding selfdeception ethical life podcast fanduel partner septum restore broad street line service eagle opener bid oust tarrant county district clerk job dismissed judge security fraud investigation avita medical rcel continues investor money urged contact law office frank r cruz republican approve measure supporting epstein investigation amid discharge threat republican approve measure supporting epstein investigation amid discharge threat rogue house republican help dems kill vote censure lamonica mciver shock republican approve measure supporting epstein investigation amid discharge threat morning joe host dem governor call trump reinforcement save life sen john sununu weighs new hampshire senate run sen john sununu weighs new hampshire senate run house approves symbolic signal support oversight epstein investigation republican approve measure supporting epstein investigation amid discharge threat republican approve measure supporting epstein investigation amid discharge threat republican approve measure supporting epstein investigation amid discharge threat republican approve measure supporting epstein investigation amid discharge threat tariff trigger split uaw canada unifor republican approve measure supporting epstein investigation amid discharge threat rubio mexico strengthen security collaboration rubio mexico strengthen security collaboration rubio mexico strengthen security collaboration new november drinking law carry jail driver family battle harderhitting punishment redistricting poised spread ahead midterm election redistricting poised spread ahead midterm election recognition trouble gop scramble rebrand trump big bill boston mayoral candidate josh kraft change campaign team nadlers retirement reignites debate advanced age congress approves million assistance nigeria help address hunger approves million assistance nigeria help address hunger approves million assistance nigeria help address hunger poilievre call ottawa end temporary foreign worker program watch bipartisan representative news conference epstein survivor news summary pm news summary pm marco rubio trump admin offense cartel full china flex military muscle drone missile ai robot wolf world war victory parade watch epstein accuser speak outside capitol free speech vandalism frog bridge chalk draw debate arizona ag kris mayes coalition file amicus brief support federal worker collective bargaining trump order senate blueprint corner rfk jr excdc trump strike targeting venezuelan gang cause cartel twice epstein survivor implore congress act push disclosure build epstein survivor implore congress act push disclosure build water attend upcoming investor conference september classless left harasses vice president vance meet family annunciation church victim uae warns israeli annexation west bank strike gaza kill uae warns israeli annexation west bank strike gaza kill uae warns israeli annexation west bank strike gaza kill uae warns israeli annexation west bank strike gaza kill president trump float deploying national guard troop new orleans president trump float deploying national guard troop new orleans npr president trump float deploying national guard troop new orleans approves million assistance nigeria help address hunger european face tough choice uk france host another meeting ukraine clover health ceo andrew toy testifies congress transformative role ai healthcare highlight clover leading uae warns israeli annexation west bank strike gaza kill froma harrop column beginning fix immigration approves million assistance nigeria help address hunger value ceasefires trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump suggests national guard new orleans blue red trump targeting new orleans guard deployment uk spain sign cooperation deal seek bolster postbrexit tie jamaican vote tight leadership race guyana president poised reelection green ocean file motion summary judgment vacate federal approval revolution wind conservative news network newsmax file antitrust lawsuit fox news</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J51"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2270,6 +2270,42 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="B52" t="n">
+        <v>6481.5</v>
+      </c>
+      <c r="C52" t="n">
+        <v>6532.64990234375</v>
+      </c>
+      <c r="D52" t="n">
+        <v>6443.97998046875</v>
+      </c>
+      <c r="E52" t="n">
+        <v>6529.080078125</v>
+      </c>
+      <c r="F52" t="n">
+        <v>5066120000</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-0.0031651529783888</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>wall street cheer and worker fear a layoff overshadow earnings verizon to speak at goldman sachs communacopia sept exclusive ev maker rivian lay off worker a it prep launch of cheaper suv the wall street journal verizon to speak at goldman sachs communacopia sept fewer discount more spending here what shopper are expecting this holiday season trump administration nominates new federal maritime commissioner amid leadership transition google facing million in damage for nearly a decade of improper smartphone snooping spirit airline to stop flying out of san diego in october google facing million in damage for nearly a decade of improper smartphone snooping google face million in damage for tracking people online activity google facing million in damage for nearly a decade of improper smartphone snooping google facing million in damage for nearly a decade of improper smartphone snooping google facing million in damage for nearly a decade of improper smartphone snooping google facing million in damage for nearly a decade of improper smartphone snooping google facing million in damage for nearly a decade of improper smartphone snooping google facing million in damage for nearly a decade of improper smartphone snooping google facing million in damage for nearly a decade of improper smartphone snooping google facing million in damage for nearly a decade of improper smartphone snooping google facing million in damage for nearly a decade of improper smartphone snooping google facing million in damage for nearly a decade of improper smartphone snooping northwestern university president step down following federal funding freeze s most popular backtoschool product according to shopify data s most popular backtoschool product according to shopify data s most popular backtoschool product according to shopify data zappos is taking up to off top shoe brand crocs birkenstock doc marten and more google facing million in damage for nearly a decade of improper smartphone snooping proposed minnesota power sale to blackrock rous concern proposed minnesota power sale to blackrock rous concern proposed minnesota power sale to blackrock rous concern proposed minnesota power sale to blackrock rous concern proposed minnesota power sale to blackrock rous concern netflix expands moment feature with custom clip option for mobile user proposed minnesota power sale to blackrock rous concern proposed minnesota power sale to blackrock rous concern orsted skyborn sue u over halt to mw revolution wind google facing million in damage for nearly a decade of improper smartphone snooping ap news invent inventor develops automatic flat tire protection mbq polkadot and cardano price face pressure a viral ethereum l token gain in popularity proposed minnesota power sale to blackrock rous concern with court tariff ruling u business could be due refund here is what analyst are saying about kratos defense security solution ktos presque isle look to hide new solar project from public view if trump tariff are thrown out company could be refunded billion surprised stock market are still moving higher say raymond james larry adam crypto company under scary attack by north korean hacker here is what you need to know before investing in astronics corporation atro ny coffee price climb a conab cut it brazil coffee production forecast china dark horse ai startup say it will use domestic chip not nvidias for it latest model what doe that mean for nvda stock stock and etf on sale this month g fuel unveils groundbreaking formula the next innovation in energy rocket lab corporation rklb announces opening of launch complex tariff pressure loom over american eagle outlook despite recent gain tech company bet on aifueled auto repair with east bay expansion tech company bet on aifueled auto repair with east bay expansion lake area writer alliance host annual fall conference oct at maddens with court tariff ruling u business could be due refund bofa security lift elbit system ltd eslts price target to maintains buy rating brilliant nextgen inc secures million in funding to accelerate product innovation and market growth transgender federal employee say they face fear and discrimination under trump if you won the b powerball jackpot how much would be withheld for tax karman holding inc krmn is up nearly since nyse debut in february after jennings contract sweetener who next on er list of business dealing after jennings contract sweetener who next on er list of business dealing after jennings contract sweetener who next on er list of business dealing after jennings contract sweetener who next on er list of business dealing lawsuit over roblox emote of charli xcx apple dance is amicably resolved rapafusyn pharmaceutical close oversubscribed million series a financing to advance it rapafusyn pharmaceutical close oversubscribed million series a financing to advance it mastercontrol reach m arr milestone driven by aipowered quality and manufacturing solution paramount mandate dayaweek return to office ahead of major cost cut major israeli defense contractor selects mobilicom limited mob to support rcws prime healthcare hospital across state earn national recognition from the american heart association maryland rake in million in cannabis tax revenue allocates fund for social equity and public health if you won the b powerball jackpot how much would be withheld for tax paramount staffer expected back at office day a week rapafusyn pharmaceutical close oversubscribed million series a financing to advance it nondegrading molecular glue drug discovery platform trump concerned for month a socialist mamdani surge putting nyc mayor race in upheaval if you won the b powerball jackpot how much would be withheld for tax if you won the b powerball jackpot how much would be withheld for tax sifco industry inc sif ha surged in one month here is why avondale councilmember max white ascends to vice chair of valley metro board spearheading transit improvement in maricopa county xrp news today xrp price recovery stall a tokenization forecast reach trillion doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless ice agent detain at illinois domestic violence courthouse this week advocate warn of chilling effect on victim ice agent detain at illinois domestic violence courthouse this week advocate warn of chilling effect on victim the equality utah ally gala announces theme and guest star tig notoro influential group behind aocs victory seek to oust la democratic congressman influential group behind aocs victory seek to oust la democratic congressman paris talk yield ukraine support plan threat of russia sanction paris talk yield ukraine support plan threat of russia sanction paris talk yield ukraine support plan threat of russia sanction paris talk yield ukraine support plan threat of russia sanction paris talk yield ukraine support plan threat of russia sanction paris talk yield ukraine support plan threat of russia sanction paris talk yield ukraine support plan threat of russia sanction paris talk yield ukraine support plan threat of russia sanction senator tear into rfk jr over vaccine restriction in explosive hearing report in wake of minneapolis school shooting doj deliberating trans gun ban eagle county democrat sponsor september food drive the senate face a reality check on blue slip lawton resident to vote on charter amendment and city council representative in upcoming election something thats worth fighting for jim bank stress need to preserve american dream despite sad reality california county restriction on being a spectator at a car sideshow violates first amendment a applied to reporter bay area resident protest billionaire on labor day jeffries say democrat will fight gop effort to whitewash jan attack on the capitol navy revers demotion of rep ronny jackson trump former white house doctor jeffries say democrat will fight gop effort to whitewash jan attack on the capitol jeffries say democrat will fight gop effort to whitewash jan attack on the capitol former hhs chief i cant imagine what i would do if i were a parent in florida donald trump or great britain is there any doubt who is the bigger threat to free speech jeffries say democrat will fight gop effort to whitewash jan attack on the capitol jeffries say democrat will fight gop effort to whitewash jan attack on the capitol keith ellison son to keep figure minneapolis councilmember salary during fellowship at harvard jeffries say democrat will fight gop effort to whitewash jan attack on the capitol jeffries say democrat will fight gop effort to whitewash jan attack on the capitol robert f kennedy jr vaccine policy endangers america child madison county court denies terry sedlaceks request for transfer from alton mental health center jeffries say democrat will fight gop effort to whitewash jan attack on the capitol heidi stevens forgetting or erasing the past is a sure path to repeating it now more than ever board of correction attorney say he cant represent panel in attorney general lawsuit pritzker urged to avoid playing politics on crime issue by former obama advisor doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless clark county extends deadline for nurse to join public health advisory council federal judge criticize supreme court for overturning ruling and siding with trump allentown investigation find isolated discriminatory conduct dysfunctional hr department but no systemic discrimination philadelphians should record federal troop if trump sends them to the city da krasner say on cnn philadelphians should record federal troop if trump sends them to the city da krasner say on cnn philadelphians should record federal troop if trump sends them to the city da krasner say on cnn philadelphians should record federal troop if trump sends them to the city da krasner say on cnn publisher agrees to change in virginia giuffres memoir after family objection publisher agrees to change in virginia giuffres memoir after family objection publisher agrees to change in virginia giuffres memoir after family objection publisher agrees to change in virginia giuffres memoir after family objection trump to resurrect department of war in new order jax state seek public help in search for missing student take a closer look at trump inferno letter republican launch yet another jan committee republican launch yet another jan committee youre not worthy rfk jr hit by epic putdown a he scrap with senator civil servant exodus how employee wrestle with whether to stay speak up or go the conversation doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless doj call lisa cook claim that trump seek her ouster to control fed baseless way ohio college student face new reality under trump second term calvinball judge give rare public rebuke of supreme court axios doj call lisa cook claim that trump seek her ouster to control fed baseless dept of justice wont defend usda program wisconsin farmer sued over</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>wall street cheer worker fear layoff overshadow earnings verizon speak goldman sachs communacopia sept exclusive ev maker rivian lay worker prep launch cheaper suv wall street journal verizon speak goldman sachs communacopia sept fewer discount spending shopper expecting holiday season trump administration nominates new federal maritime commissioner amid leadership transition google facing million damage nearly decade improper smartphone snooping spirit airline stop flying san diego october google facing million damage nearly decade improper smartphone snooping google face million damage tracking people online activity google facing million damage nearly decade improper smartphone snooping google facing million damage nearly decade improper smartphone snooping google facing million damage nearly decade improper smartphone snooping google facing million damage nearly decade improper smartphone snooping google facing million damage nearly decade improper smartphone snooping google facing million damage nearly decade improper smartphone snooping google facing million damage nearly decade improper smartphone snooping google facing million damage nearly decade improper smartphone snooping google facing million damage nearly decade improper smartphone snooping google facing million damage nearly decade improper smartphone snooping northwestern university president step following federal funding freeze popular backtoschool product according shopify data popular backtoschool product according shopify data popular backtoschool product according shopify data zappos taking shoe brand crocs birkenstock doc marten google facing million damage nearly decade improper smartphone snooping proposed minnesota power sale blackrock rous concern proposed minnesota power sale blackrock rous concern proposed minnesota power sale blackrock rous concern proposed minnesota power sale blackrock rous concern proposed minnesota power sale blackrock rous concern netflix expands moment feature custom clip option mobile user proposed minnesota power sale blackrock rous concern proposed minnesota power sale blackrock rous concern orsted skyborn sue halt mw revolution wind google facing million damage nearly decade improper smartphone snooping news invent inventor develops automatic flat tire protection mbq polkadot cardano price face pressure viral ethereum l token gain popularity proposed minnesota power sale blackrock rous concern court tariff ruling business due refund analyst saying kratos defense security solution ktos presque isle look hide new solar project public view trump tariff thrown company refunded billion surprised stock market moving higher raymond james larry adam crypto company scary attack north korean hacker investing astronics corporation atro ny coffee price climb conab cut brazil coffee production forecast china dark horse ai startup domestic chip nvidias latest model doe nvda stock stock etf sale month g fuel unveils groundbreaking formula next innovation energy rocket lab corporation rklb announces opening launch complex tariff pressure loom american eagle outlook recent gain tech company bet aifueled auto repair east bay expansion tech company bet aifueled auto repair east bay expansion lake area writer alliance host annual fall conference oct maddens court tariff ruling business due refund bofa security lift elbit system eslts price target maintains buy rating brilliant nextgen secures million funding accelerate product innovation market growth transgender federal employee face fear discrimination trump b powerball jackpot withheld tax karman holding krmn nearly since nyse debut february jennings contract sweetener next er list business dealing jennings contract sweetener next er list business dealing jennings contract sweetener next er list business dealing jennings contract sweetener next er list business dealing lawsuit roblox emote charli xcx apple dance amicably resolved rapafusyn pharmaceutical close oversubscribed million series financing advance rapafusyn pharmaceutical close oversubscribed million series financing advance mastercontrol reach arr milestone driven aipowered quality manufacturing solution paramount mandate dayaweek office ahead major cost cut major israeli defense contractor selects mobilicom limited mob support rcws prime healthcare hospital across earn national recognition american heart association maryland rake million cannabis tax revenue allocates fund social equity public health b powerball jackpot withheld tax paramount staffer expected office day rapafusyn pharmaceutical close oversubscribed million series financing advance nondegrading molecular glue drug discovery platform trump concerned month socialist mamdani surge putting nyc mayor race upheaval b powerball jackpot withheld tax b powerball jackpot withheld tax sifco industry sif surged month avondale councilmember max white ascends vice chair valley metro board spearheading transit improvement maricopa county xrp news today xrp price recovery stall tokenization forecast reach trillion doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless agent detain illinois domestic violence courthouse advocate warn chilling effect victim agent detain illinois domestic violence courthouse advocate warn chilling effect victim equality utah ally gala announces theme guest star tig notoro influential behind aocs victory seek oust la democratic congressman influential behind aocs victory seek oust la democratic congressman paris yield ukraine support plan threat russia sanction paris yield ukraine support plan threat russia sanction paris yield ukraine support plan threat russia sanction paris yield ukraine support plan threat russia sanction paris yield ukraine support plan threat russia sanction paris yield ukraine support plan threat russia sanction paris yield ukraine support plan threat russia sanction paris yield ukraine support plan threat russia sanction senator tear rfk jr vaccine restriction explosive hearing report wake minneapolis school shooting doj deliberating trans gun ban eagle county democrat sponsor september food drive senate face reality blue slip lawton resident vote charter amendment council representative upcoming election something thats worth fighting jim bank stress preserve american dream sad reality california county restriction spectator car sideshow violates amendment applied reporter bay area resident protest billionaire labor day jeffries democrat fight gop effort whitewash jan attack capitol navy revers demotion rep ronny jackson trump white house doctor jeffries democrat fight gop effort whitewash jan attack capitol jeffries democrat fight gop effort whitewash jan attack capitol hhs chief cant imagine parent florida donald trump great britain doubt bigger threat free speech jeffries democrat fight gop effort whitewash jan attack capitol jeffries democrat fight gop effort whitewash jan attack capitol keith ellison son figure minneapolis councilmember salary fellowship harvard jeffries democrat fight gop effort whitewash jan attack capitol jeffries democrat fight gop effort whitewash jan attack capitol robert f kennedy jr vaccine policy endangers america child madison county court denies terry sedlaceks request transfer alton mental health center jeffries democrat fight gop effort whitewash jan attack capitol heidi stevens forgetting erasing past sure path repeating ever board correction attorney cant represent panel attorney general lawsuit pritzker urged avoid playing politics crime issue obama advisor doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless clark county extends deadline nurse join public health advisory council federal judge criticize supreme court overturning ruling siding trump allentown investigation find isolated discriminatory conduct dysfunctional hr department systemic discrimination philadelphians record federal troop trump sends da krasner cnn philadelphians record federal troop trump sends da krasner cnn philadelphians record federal troop trump sends da krasner cnn philadelphians record federal troop trump sends da krasner cnn publisher agrees change virginia giuffres memoir family objection publisher agrees change virginia giuffres memoir family objection publisher agrees change virginia giuffres memoir family objection publisher agrees change virginia giuffres memoir family objection trump resurrect department war new order jax seek public help search missing student take closer look trump inferno letter republican launch yet another jan committee republican launch yet another jan committee youre worthy rfk jr hit epic putdown scrap senator civil servant exodus employee wrestle stay speak conversation doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless doj call lisa cook claim trump seek ouster control fed baseless ohio college student face new reality trump term calvinball judge give rare public rebuke supreme court axios doj call lisa cook claim trump seek ouster control fed baseless dept justice wont defend usda program wisconsin farmer sued</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2306,6 +2306,42 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45908</v>
+      </c>
+      <c r="B53" t="n">
+        <v>6495.14990234375</v>
+      </c>
+      <c r="C53" t="n">
+        <v>6508.669921875</v>
+      </c>
+      <c r="D53" t="n">
+        <v>6483.2900390625</v>
+      </c>
+      <c r="E53" t="n">
+        <v>6498.08984375</v>
+      </c>
+      <c r="F53" t="n">
+        <v>5211500000</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.0021059789159529</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year august worst month for job growth this year hbcu tradition without commitment is just noise indiana national guard member to assist state ice operation kenvue stock drop on report rfk jr will link autism to tylenol use during pregnancy we asked grok chatgpt and gemini about elon musk chance of unlocking the full trillion in his pay proposal the u added only job last month showing crack in the labor market rosen leading investor counsel encourages altimmune inc investor to secure counsel before tesla trillion pay package for elon musk boil down to one thing keeping the attention of the world richest man justin sun urge trumplinked wlfi to unlock unreasonably frozen token pg terminates fedex a operator of ohio distribution center ppmd kick off world duchenne awareness day with bad shirt friday special united nation documentary premiere google hit with billion fine from european union in adtech antitrust case google hit with billion fine from european union in adtech antitrust case google hit with billion fine from european union in adtech antitrust case google hit with billion fine from european union in adtech antitrust case google hit with billion fine from european union in adtech antitrust case google hit with billion fine from european union in adtech antitrust case alphabet to rally more than here are top analyst forecast for friday judge immediately toss newsmaxs lawsuit against fox news but thats not end of story milwaukee set sail on m south shore cruise dock project aim to boost great lake tourism by how could an openai partnership with broadcom shake up silicon valley chip hierarchy stock slip a wall street question whether the u job market ha slowed by enough or too much byd bev sale up while phev sale down chart tesla proposes trillion compensation package for musk over year ap business summarybrief at pm edt why september typical stock slump shouldnt scare you the relationship architect genine fallon turn brand capital and investor trust into one strategy a year after opening illinois casino look to add hotel a it anticipates competition from wisconsin school district approves further scrutiny of fiscal mismanagement missoula county approves tax increase the surprising way a medium mogul discovered he ha highfunctioning autism gardening turn your garden harvest into a peck of pickled pepper powerball jackpot rise to b nd largest in game history ap business summarybrief at pm edt lupo caffe now offering dinner service expanded menu in generation park leica store gallery boston present greeting from niagara a new photographic exhibition by natalia neuhaus giorgio armani leaf a legacy a the master of luxury readytowear spirit airline to leave portland international airport other location learning to manage chronic ache amy wilkinson join protiviti advisory board nyc mayor eric adam say he willing to hear about other job mirae asset global etf holding ltd purchase share of meta platform inc meta stock slip a wall street question whether the u job market ha slowed by enough or too much stock slip a wall street question whether the u job market ha slowed by enough or too much stock slip a wall street question whether the u job market ha slowed by enough or too much stock slip a wall street question whether the u job market ha slowed by enough or too much stock slip a wall street question whether the u job market ha slowed by enough or too much stock slip a wall street question whether the u job market ha slowed by enough or too much of american worried about moneyheres why a cd could help upgraded betmgm bonus code silive unlocks betting bonus for nfl week all talentz showcase outsourcing excellence at gitex nigeria indiana slashing rate for child care provider santa monica city attorney file discrimination suit against landlord for denying veteran housing adaptation unpacking the latest option trading trend in rivian automotive unpacking the latest option trading trend in zeta global holding kenvue crater on report rfk jr to link autism to tylenol use in pregnancy liberty insurance agency receives award for partnership with area ronald mcdonald house charity best camera mobile phone in for photography enthusiast contourglobal launch operation at black hollow sun solar plant contourglobal launch operation at black hollow sun solar plant u unemployment rate near year high a labor market hit stall speed reuters nutex health nutx face investor lawsuit over alleged revenue inflation scheme hagens berman job weakened again increasing the odds of an interest rate cut gold stock closing in on record after year wait signal sector revaluation is the fed ready to go big analyst debate jumbo rate cut after soft job data bond yield tumble a jobmarket frailty put halfpoint fed rate cut on table sweetgreen swipe chipotle cao for cfo jab insurance completes acquisition of prosperity life group jab insurance completes acquisition of prosperity life group hhs reset clock on longawaited hair testing guideline afterearningsissnowflakestockbuysellorfairlyvalued newsmaxs lawsuit against fox hit a snag a judge dismisses it a shotgun pleading newsmaxs lawsuit against fox hit a snag a judge dismisses it a shotgun pleading american express cardholder how you can watch dancing with the star season free of charge court is right trump is not a tariff king schumer blame trump chaotic tariff for poor job report and economic uncertainty schumer blame trump chaotic tariff for poor job report and economic uncertainty schumer blame trump chaotic tariff for poor job report and economic uncertainty newsmaxs lawsuit against fox hit a snag a judge dismisses it a shotgun pleading cnn the wealthiest zip code in massachusetts trump promised no tax on social security in his one big beautiful bill act this democratic bill could actually do it mortgage rate forecast when will rate go down ap technology summarybrief at pm edt ap business summarybrief at pm edt st amendment shutting down permanently both sf taproom and east bay brewery will close local player win k on table game at la vega valley casino photo mass scheduled at st mary in florence operation warp speed wa one of trump biggest achievement then came rfk jr and vaccine skeptic oregon secretary of state form advisory committee to strengthen voter registration system state ag urged to investigate how popular detroit democrat avoided mandatory jail time for third duo two dc teen arrested in congressional intern fatal shooting two dc teen arrested in congressional intern fatal shooting kandiyohi county marriage license issued aug through sept dangerous myth of juvenile crime national conservatism asserts it dominance in trump washington jeanine pirros clown show prosecution buried by msnbc legal panel after judge blow up national conservatism asserts it dominance in trump washington national conservatism asserts it dominance in trump washington national conservatism is reshaping the republican party national conservatism asserts it dominance in trump washington national conservatism asserts it dominance in trump washington national conservatism asserts it dominance in trump washington national conservatism asserts it dominance in trump washington national conservatism asserts it dominance in trump washington national conservatism asserts it dominance in trump washington national conservatism asserts it dominance in trump washington quebec minister asks walmart amazon to stop selling prohells angel merchandise ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt violent attack on usbp agent in naco result in prison term texas legislature long summer end with democrat marginalized republican triumphant and unified michelle wu chance of losing boston mayor race a trump admin suespoll ap news summary at pm edt dearborn call for community input on west warren ave roadway project at upcoming public meeting malnourished kid arrive daily at a gaza hospital a netanyahu denies hunger malnourished kid arrive daily at a gaza hospital a netanyahu denies hunger malnourished kid arrive daily at a gaza hospital a netanyahu denies hunger malnourished kid arrive daily at a gaza hospital a netanyahu denies hunger your right when it come to ice how to protect yourself your neighbor a federal agent arrive block club chicago your right when it come to ice how to protect yourself your neighbor a federal agent arrive ice is incarcerating immigrant at angola louisiana max security prison markey former cdc chief denounce rfk in codman square south korean k tank to get israel trophy protection system a palestinian and an israeli working together on a new vision for peace the surprising way a medium mogul discovered he ha highfunctioning autism rfk jr to link tylenol use in pregnancy to autism say wall street journal trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job trump defends handling of epstein controversy say gop doing legendary job arkansas state official to address contraband cellphone in prison first nation call on ottawa to crack down on drug trafficker in their community lawrence odonnell dub rfk jr the most dangerous nepo baby in american history inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response hoosier voice concern over potential election law change at indianapolis hearing inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response inhome care rule change proposal generates more than response gold the s champion poised for even greater triumph average san diego gas price hit highest mark since june america escalates trade war with china over child safety exclusive betmgm bonus code silive unlocks betting bonus for cfb week city of keene approves change to downtown infrastructure project rfk jr family member say he is a threat to american health and call for his resignation child launch lemonade stand craft and more at nashville entrepreneur market pelham and mi pueblo supermarket resolve compliance dispute hundred get together for third annual patriot day k run ethereum eth little pepe lilpepe see strong growth top cryptos for carney most of economic weakness due to inappropriate federal reserve policy saratoga job showcase planned for friday sep crown coin casino promo code get k cc sc september lucid land million from uber to launch autonomous ev fleet ford ev sale surge a buyer race to beat expiring tax credit offduty pilot pleads guilty to trying to crash alaska airline jet bbc nfl longshot pick week odds best prop this parlay brings a massive return on a bet anthropic agrees to pay author billion in landmark ai settlement thrift treasure or new trend shopper find style without breaking the bank opec likely to agree to another production increase on sunday report this is a longterm investment why more white collar worker are hiring executive function coach bank warn of risk a critical cyber law nears expiration this nj town just approved the remodeling of an old strip mall at a busy traffic circle from glass pyramid to solar candlelight two leap of eastern wisdom in paris yeah this isnt going to end well for u uber is testing cash ridesdrivers react opinion want to fix the economy fund child care judge order trump admin to release billion in frozen foreign aid funding conflict is good for family business if you manage it properly greene mayor adam still ha chance to walk away a winner republican move to lift drilling and mining restriction in western state caledonianrecord partner with clear view advantage to elevate local business online spark season on the line sunday against the wing september mortgage outlook rate may stay put until the fed meet ice is said to have begun operation in the boston area the new york time state and federal data should be above politics state and federal data should be above politics lewisville city council invite public input on proposed m budget and property tax cut cardano eye in q but magax presale could deliver much bigger gain homearama coming to westfield judge halt koi casino project near windsor faulting fed approval horrifyingly irresponsible paul krugman point with alarm at trump online antic mayor message capitola mall st avenue are entering a new phase walmarts bestselling drawer dresser is on sale for only postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un postal operator suspend service to u over tariff un saturday morning point reyes station minimart mystery perplexes local postal traffic to u sank after trump ended lowvalue parcel exemption the fed got it wrong and is late again top economist say a job gain collapse innout officially expands into yet another state flame extend f connor zary with year deal flame extend f connor zary with year deal postal traffic to u fell after exemption ended on lowvalue parcel postal traffic to u fell after exemption ended on lowvalue parcel acadia monthly visit reach year high in august major food company ceo allegedly fired after having romantic relationship with two different employee report acadia monthly visit reach year high in august little rock airport executive director placed on administrative leave alan dershowitz there is no genocide in gaza why the claim equal holocaust denial walmart weekend steal smart tv laptop audio gear robinhood and applovin to join the sp sending share soaring he lost k in a day panicked mom see gambling hook young men under trump the federal trade commission is abandoning it ban on noncompetes magnet manufacturer to build m plant in columbus cortland county real estate most expensive home sold aug sept gm president say pause on ev mandate is welcome call for consumerfocused policy trump warns any venezuelan plane threatening u ship will be shot down postal traffic to u sank after trump administration ended exemption on lowvalue parcel opec will likely agree to further oil output hike on sunday source say aldi want to dominate u and it tier strategy is already winning over shopper ulta beauty make major store change amid breakup with target trumpbacked world liberty sink a billionaire justin sun protest then reinvests lyon township bid farewell to beloved draught horse brewery spirit after year kingston common council approves zoning change for schwenk drive why cai plunged in august sandy spring score legal victory court issue injunction against failsafe data llc over unpermitted shortterm rental briggs the million question will kentucky buy out of game at glass bowl cory morgan a austerity loom the cra becomes a test case for reform iconic lake worth drivein theatre and swap shop set to close in palm spring amid regulatory challenge why i am considering drip for my iv income etf strategy here what im learning popular casino sue former universal studio exec over million in debt salesforce inc nysecrm declares quarterly dividend salesforce inc crm to go exdividend on september th kingston common council ok sewer project on foxhall and flatbush avenue postal traffic to the u sank after trump administration ended exemption on lowvalue parcel podcasters and influencers the unexpected job covered under trump no tax on tip plan real estate expert jim and mike savas explain accurate home pricing in hellonation september mortgage outlook rate may stay put until the fed meet in for a fight idahoan rally at statehouse to support transgender right rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation rfk jr family member say he is a threat to american health and call for his resignation biden chooses delaware for his presidential library a his team turn to raising money for it rfk jr family member say he is a threat to american health and call for his resignation ap news maduro vow to defend venezuela sovereignty a tension with u escalate pb west point yank tom hank award bash with no explanation leaving hollywood nonsoldier in the dust ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt trump administration blocked from ending protection for venezuelan haitian report ap news summary at pm edt ap news summary at pm edt pritzker hit trump over deportation meme this is not a joke this is not normal apple resists uk push to weaken icloud encryption amid security clash thousand march in dc against trump law enforcement takeover rep smith blast trump department of war rebrand phillies karen roasted online after miami baseball game confrontation wouldnt want to be her right now video how donald trump is weaponizing the government to settle personal score and pursue his agenda how donald trump is weaponizing the government to settle personal score and pursue his agenda how donald trump is weaponizing the government to settle personal score and pursue his agenda how donald trump is weaponizing the government to settle personal score and pursue his agenda how donald trump is weaponizing the government to settle personal score and pursue his agenda how donald trump is weaponizing the government to settle personal score and pursue his agenda how donald trump is weaponizing the government to settle personal score and pursue his agenda how donald trump is weaponizing the government to settle personal score and pursue his agenda how donald trump is weaponizing the government to settle personal score and pursue his agenda how donald trump is weaponizing the government to settle personal score and pursue his agenda scared man trump blasted for impeachmentworthy threat aimed at chicago if you think redistricting is crazy now check out the history book if you think redistricting is crazy now check out the history book what to know about the trial of the man accused of trying to assassinate trump in florida tribune poll question watch pedotrump lie collapse completely a resurfaced interview confirms trump wa only one offering help to epstein victim yikes kamala harris radical protege rep lateefah simon may be the future of the democratic party california city to repeal homeless housing ban after state sue greene mayor adam still ha chance to walk away a winner ronald l hirsch what doe all men are created equal really mean extrajudicial military killing is not a legitimate answer to drug trafficking second amendment group slam floated gun ban for transgender people twice told tale new rule for homelessness behavior enforcement how justice seeking another term on pa supreme court ruled in pivotal election case greene mayor adam still ha chance to walk away a winner brett varoz nominated by governor cox for utah board of pardon and parole seat u say it will deport kilmar abrego garcia to eswatini because he fear deportation to uganda south sudan repatriate mexican man deported from u in july south sudan repatriate mexican man deported from u in july south sudan repatriate mexican man deported from u in july legal aid group sue to preemptively block u from deporting a dozen honduran child legal aid group sue to preemptively block u from deporting a dozen honduran child legal aid group sue to preemptively block u from deporting a dozen honduran child legal aid group sue to preemptively block u from deporting a dozen honduran child trump downplays possible regime change in venezuela u deploys stealth fighter jet ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt chicago brace for trump national guard plan hyundai ice raid put spotlight on visa waiver program korean travel hyundai ice raid put spotlight on visa waiver program korean travel hyundai ice raid put spotlight on visa waiver program korean travel hyundai ice raid put spotlight on visa waiver program korean travel hyundai ice raid put spotlight on visa waiver program korean travel what is eswatini meet the african country where kilmar abrego garcia could go next celebration of sukkot to be held oct in clearbrook minnesota elgin news digest former u board member cody holt running for senate ecc announces student leader for school year biden chooses delaware for presidential library pick board to raise fund aclu argues border patrol broke court order with highprofile sacramento raid adam zyglis bill opener lawmaker tell utah supreme court theyre harmed by judge ruling in gerrymandering case democrat blast ice raid on koreanrun hyundai worksite in georgia chicago mexican independence day celebration shadowed by trump threat for the city chicago mexican independence day celebration shadowed by trump threat for the city chicago mexican independence day celebration shadowed by trump threat for the city ice is said to have begun operation in the boston area ice is said to have begun operation in the boston area the new york time hyundai ice raid put spotlight on visa waiver program korean travel budget airline to launch new flight to popular destination greece italy the caribbean thousand celebrate culture during schenectady festival weekend atlanta investor acquires m industrial facility jobhopping ha long been the path to higher pay for the first time since staying put is doing better delorenzos pizza renovation underway for pizza and marijuana dispensary amazon cut seller fee boost ai tool ahead of festive shopping season gm ceo mary barra sell of personal stock in company mass timber a lego flyvbjergs modularity meet lowcarbon construction first nation development corporation open new transcanada highway gas station gst reform taxation cant be an emotional decision say fm sitharaman el paso celebrates groundbreaking for million sean haggerty dr extension project i thought of moderna inc mrna after florida vaccine rule say jim cramer ciena corporation cien is a terrific company say jim cramer it kind of like a cultural nostalgia gen z drive boom in grannycore activity including mahjong baking and needlework is buying a home still the best way to build wealth is buying a home still the best way to build wealth is buying a home still the best way to build wealth is buying a home still the best way to build wealth jim cramer reveals why texas instrument incorporated txns share dipped lower is buying a home still the best way to build wealth mississippi hunter snag foot alligator that look straight out of jurassic park movie kohl corporation ks had a decent last quarter said jim cramer best walmart deal score massive discount on tech appliance and essential rosen a highly ranked law firm encourages lineage inc investor to secure counsel before rosen a highly ranked law firm encourages lineage inc investor to secure counsel before rosen a highly ranked law firm encourages lineage inc investor to secure counsel before rosen a highly ranked law firm encourages lineage inc investor to secure counsel before europe slap billion fine on google donald trump say money could instead go to american investment and job woman drive her jeep in for an oil change drive out in a chevy equinox ev arctic pablo coin presale cross m raising stake in top new meme coin to join now while shiba inu and brett hold ground shes long had sweet success with bittersweet candy now heather lent reflects on that success w podcast rosen a highly ranked law firm encourages lineage inc investor to secure counsel before important deadline in security class action line horror box office blow past billion for a the conjuring last rite take in thirdlargest domestic opening ever a new era in smart living ecovacs unveils deebot x with powerboost technology at ifa taste test woodford reserve first single malt show craft distillery still have a leg up on the big boy zuckerberg shredded over awkward hot mic with trump powerball lottery winner in missouri and texas to split nearly billion jackpot shiba inus shibarium debut embarrassing marketing plan a community anger grows u postal import plunge after tariff exemption end tennis number one aryna sabalenka becomes first woman to win straight u open since serena williams over a decade ago david blackmon trump is most consequential energy president in u history powerball ticket sold in colorado won between and million powerball ticket sold in colorado won between and million kennedy must go say critic of all stripe maha is a sham trump approval milestone signal strong support for policy victory centre step up effort for rollout of ambitious national deepwater mission face the nation king named board chairwoman of get your money right inc u in very deep negotiation with hamas to end gaza conflict trump say stand up sunday national interfaith coalition call for an end to antisemitism and all faithbased hate from home kitchen to commercial processor margarita and elote nacho redbird is now open in old rincon market powerball player win million in ohio a billion jackpot hit in u powerball player win million in ohio a billion jackpot hit in u massachusetts lag in housing production despite unit added in healeys term acacajunmantriathlonjpg acacajunmantriathlonjpg postal traffic to u drop more than after trade exemption rule end un agency say postal traffic to u drop more than after trade exemption rule end un agency say npr postal traffic to u drop more than after trade exemption rule end un agency say revenue loss state govts build pressure on centre after gst reform week after hitting switzerland with tariff trump to watch u open men final from the rolex suite source say federal coal lease fasttracked in north dakota environmental group object david blackmon trump is most consequential energy president in u history gst cut a partial cushion against trade headwind say mahesh nandurkar alphabet inc googl share acquired by sepio capital lp select equity group lp decrease stake in visa inc v undersea cable cut in the red sea disrupting internet access in asia and the mideast global edtech company xed set the syllabus for gift city listing why the smartest money isnt on thing but on becoming more fully yourself draftkings promo code bet get off nfl sunday ticket in bonus for lion v packer a longstanding tax on wealth is a central issue a prosperous norway vote in a close election fanduel promo code bet get if it win for lion v packer social debt of around m to kent county council written off ohio donor ditch tim ryan pour nearly k into vivek ramaswamys governor bid rare and soughtafter bourbon set for annual auction at kentucky museum missouri and texas player claim recordbreaking billion powerball jackpot powerball winning ticket sold in texas missouri for nearly billion jackpot cayuga county real estate see all home sold aug sept push to ban stock trading by congress follows il rep reported violation issuer and one mega deal qip issuance tell a split story watsonville city council to vote on expanding license plate reader program sept sec scott bessent gov wes moore and sen cory booker lancaster county lake health alert get update floyd county to consider op</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year august worst month job growth year hbcu tradition without commitment noise indiana national guard assist operation kenvue stock drop report rfk jr link autism tylenol pregnancy grok chatgpt gemini elon musk chance unlocking full trillion pay proposal added job month showing crack labor market rosen leading investor counsel encourages altimmune investor secure counsel tesla trillion pay package elon musk boil keeping attention world richest man justin sun urge trumplinked wlfi unlock unreasonably frozen token pg terminates fedex operator ohio distribution center ppmd kick world duchenne awareness day bad shirt friday special united nation documentary premiere google hit billion fine european union adtech antitrust case google hit billion fine european union adtech antitrust case google hit billion fine european union adtech antitrust case google hit billion fine european union adtech antitrust case google hit billion fine european union adtech antitrust case google hit billion fine european union adtech antitrust case alphabet rally analyst forecast friday judge immediately toss newsmaxs lawsuit fox news thats end story milwaukee set sail south shore cruise dock project aim boost great lake tourism openai partnership broadcom shake silicon valley chip hierarchy stock slip wall street job market slowed enough byd bev sale phev sale chart tesla proposes trillion compensation package musk year business summarybrief pm september typical stock slump shouldnt scare relationship architect genine fallon turn brand capital investor trust strategy year opening illinois casino look add hotel anticipates competition wisconsin school district approves scrutiny fiscal mismanagement missoula county approves tax increase surprising medium mogul discovered highfunctioning autism gardening turn garden harvest peck pickled pepper powerball jackpot rise b nd largest game history business summarybrief pm lupo caffe offering dinner service expanded menu generation park leica store gallery boston present greeting niagara new photographic exhibition natalia neuhaus giorgio armani leaf legacy master luxury readytowear spirit airline portland international airport location learning manage chronic ache amy wilkinson join protiviti advisory board nyc mayor eric adam willing hear job mirae asset global etf holding purchase share meta platform meta stock slip wall street job market slowed enough stock slip wall street job market slowed enough stock slip wall street job market slowed enough stock slip wall street job market slowed enough stock slip wall street job market slowed enough stock slip wall street job market slowed enough american worried moneyheres cd help upgraded betmgm bonus code silive unlocks betting bonus nfl talentz showcase outsourcing excellence gitex nigeria indiana slashing rate child care provider santa monica attorney file discrimination suit landlord denying veteran housing adaptation unpacking latest option trading trend rivian automotive unpacking latest option trading trend zeta global holding kenvue crater report rfk jr link autism tylenol pregnancy liberty insurance agency receives award partnership area ronald mcdonald house charity best camera mobile phone photography enthusiast contourglobal launch operation black hollow sun solar plant contourglobal launch operation black hollow sun solar plant unemployment rate year high labor market hit stall speed reuters nutex health nutx face investor lawsuit alleged revenue inflation scheme hagens berman job weakened increasing odds interest rate cut gold stock closing record year wait signal sector revaluation fed ready big analyst debate jumbo rate cut soft job data bond yield tumble jobmarket frailty put halfpoint fed rate cut table sweetgreen swipe chipotle cao cfo jab insurance completes acquisition prosperity life jab insurance completes acquisition prosperity life hhs reset clock longawaited hair testing guideline afterearningsissnowflakestockbuysellorfairlyvalued newsmaxs lawsuit fox hit snag judge dismisses shotgun pleading newsmaxs lawsuit fox hit snag judge dismisses shotgun pleading american express cardholder watch dancing star season free charge court trump tariff king schumer blame trump chaotic tariff poor job report economic uncertainty schumer blame trump chaotic tariff poor job report economic uncertainty schumer blame trump chaotic tariff poor job report economic uncertainty newsmaxs lawsuit fox hit snag judge dismisses shotgun pleading cnn wealthiest zip code massachusetts trump promised tax social security big bill act democratic bill mortgage rate forecast rate technology summarybrief pm business summarybrief pm st amendment shutting permanently sf taproom east bay brewery close local player k table game la vega valley casino photo mass scheduled st mary florence operation warp speed trump biggest achievement came rfk jr vaccine skeptic oregon secretary form advisory committee strengthen voter registration system ag urged investigate popular detroit democrat avoided mandatory jail third duo dc teen arrested congressional intern fatal shooting dc teen arrested congressional intern fatal shooting kandiyohi county marriage license issued aug sept dangerous myth juvenile crime national conservatism asserts dominance trump washington jeanine pirros clown prosecution buried msnbc legal panel judge blow national conservatism asserts dominance trump washington national conservatism asserts dominance trump washington national conservatism reshaping republican party national conservatism asserts dominance trump washington national conservatism asserts dominance trump washington national conservatism asserts dominance trump washington national conservatism asserts dominance trump washington national conservatism asserts dominance trump washington national conservatism asserts dominance trump washington national conservatism asserts dominance trump washington quebec minister asks walmart amazon stop selling prohells angel merchandise news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm violent attack usbp agent naco prison term texas legislature summer end democrat marginalized republican triumphant unified michelle wu chance losing boston mayor race trump admin suespoll news summary pm dearborn call community input west warren ave roadway project upcoming public meeting malnourished kid arrive gaza hospital netanyahu denies hunger malnourished kid arrive gaza hospital netanyahu denies hunger malnourished kid arrive gaza hospital netanyahu denies hunger malnourished kid arrive gaza hospital netanyahu denies hunger come protect neighbor federal agent arrive block club chicago come protect neighbor federal agent arrive incarcerating immigrant angola louisiana max security prison markey cdc chief denounce rfk codman square south korean k tank israel trophy protection system palestinian israeli working together new vision peace surprising medium mogul discovered highfunctioning autism rfk jr link tylenol pregnancy autism wall street journal trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job trump defends handling epstein controversy gop legendary job arkansas address contraband cellphone prison nation call ottawa crack drug trafficker community lawrence odonnell dub rfk jr dangerous nepo baby american history inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response hoosier voice concern potential election law change indianapolis hearing inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response inhome care rule change proposal generates response gold champion poised greater triumph average san diego gas price hit highest mark since june america escalates trade war china child safety exclusive betmgm bonus code silive unlocks betting bonus cfb keene approves change downtown infrastructure project rfk jr family threat american health call resignation child launch lemonade stand craft nashville entrepreneur market pelham mi pueblo supermarket resolve compliance dispute together third annual patriot day k run ethereum eth little pepe lilpepe strong growth cryptos carney economic weakness due inappropriate federal reserve policy saratoga job showcase planned friday sep crown coin casino promo code k cc sc september lucid land million uber launch autonomous ev fleet ford ev sale surge buyer race beat expiring tax credit offduty pilot pleads guilty crash alaska airline jet bbc nfl longshot pick odds best prop parlay brings massive bet anthropic agrees pay author billion landmark ai settlement thrift treasure new trend shopper find style without breaking bank opec likely agree another production increase sunday report longterm investment white collar worker hiring executive function coach bank warn risk critical cyber law nears expiration nj town approved remodeling old strip mall busy traffic circle glass pyramid solar candlelight leap eastern wisdom paris yeah isnt end uber testing cash ridesdrivers react opinion fix economy fund child care judge order trump admin release billion frozen foreign aid funding conflict good family business manage properly greene mayor adam chance walk away winner republican move lift drilling mining restriction western caledonianrecord partner view advantage elevate local business online spark season line sunday wing september mortgage outlook rate stay put fed meet begun operation boston area new york federal data politics federal data politics lewisville council invite public input proposed budget property tax cut cardano eye q magax presale deliver bigger gain homearama coming westfield judge halt koi casino project windsor faulting fed approval horrifyingly irresponsible paul krugman alarm trump online antic mayor message capitola mall st avenue entering new phase walmarts bestselling drawer dresser sale postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un postal operator suspend service tariff un saturday morning reyes station minimart mystery perplexes local postal traffic sank trump ended lowvalue parcel exemption fed got late economist job gain collapse innout officially expands yet another flame extend f connor zary year deal flame extend f connor zary year deal postal traffic fell exemption ended lowvalue parcel postal traffic fell exemption ended lowvalue parcel acadia monthly visit reach year high august major food company ceo allegedly fired romantic relationship different employee report acadia monthly visit reach year high august little rock airport executive director placed administrative alan dershowitz genocide gaza claim equal holocaust denial walmart weekend steal smart tv laptop audio gear robinhood applovin join sp sending share soaring k day panicked mom gambling hook young men trump federal trade commission abandoning ban noncompetes magnet manufacturer build plant columbus cortland county real estate expensive sold aug sept gm president pause ev mandate welcome call consumerfocused policy trump warns venezuelan plane threatening ship shot postal traffic sank trump administration ended exemption lowvalue parcel opec likely agree oil output hike sunday source aldi dominate tier strategy winning shopper ulta beauty major store change amid breakup target trumpbacked world liberty sink billionaire justin sun protest reinvests lyon township bid farewell beloved draught horse brewery spirit year kingston common council approves zoning change schwenk drive cai plunged august sandy spring score legal victory court issue injunction failsafe data llc unpermitted shortterm rental briggs million kentucky buy game glass bowl cory morgan austerity loom cra becomes test case reform iconic lake worth drivein theatre swap shop set close palm spring amid regulatory challenge considering drip iv income etf strategy im learning popular casino sue universal studio exec million debt salesforce nysecrm declares quarterly dividend salesforce crm exdividend september kingston common council ok sewer project foxhall flatbush avenue postal traffic sank trump administration ended exemption lowvalue parcel podcasters influencers unexpected job covered trump tax tip plan real estate expert jim mike savas explain accurate pricing hellonation september mortgage outlook rate stay put fed meet fight idahoan rally statehouse support transgender rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation rfk jr family threat american health call resignation biden chooses delaware presidential library team turn raising money rfk jr family threat american health call resignation news maduro vow defend venezuela sovereignty tension escalate pb west yank tom hank award bash explanation leaving hollywood nonsoldier dust news summary pm news summary pm news summary pm news summary pm trump administration blocked ending protection venezuelan haitian report news summary pm news summary pm pritzker hit trump deportation meme joke normal apple resists uk push weaken icloud encryption amid security clash thousand march dc trump law enforcement takeover rep smith blast trump department war rebrand phillies karen roasted online miami baseball game confrontation wouldnt video donald trump weaponizing government settle personal score pursue agenda donald trump weaponizing government settle personal score pursue agenda donald trump weaponizing government settle personal score pursue agenda donald trump weaponizing government settle personal score pursue agenda donald trump weaponizing government settle personal score pursue agenda donald trump weaponizing government settle personal score pursue agenda donald trump weaponizing government settle personal score pursue agenda donald trump weaponizing government settle personal score pursue agenda donald trump weaponizing government settle personal score pursue agenda donald trump weaponizing government settle personal score pursue agenda scared man trump blasted impeachmentworthy threat aimed chicago redistricting crazy history book redistricting crazy history book trial man accused assassinate trump florida tribune poll watch pedotrump lie collapse completely resurfaced interview confirms trump offering help epstein victim yikes kamala harris radical protege rep lateefah simon future democratic party california repeal homeless housing ban sue greene mayor adam chance walk away winner ronald l hirsch doe men created equal extrajudicial military killing legitimate answer drug trafficking amendment slam floated gun ban transgender people twice tale new rule homelessness behavior enforcement justice seeking another term pa supreme court ruled pivotal election case greene mayor adam chance walk away winner brett varoz nominated governor cox utah board pardon parole seat deport kilmar abrego garcia eswatini fear deportation uganda south sudan repatriate mexican man deported july south sudan repatriate mexican man deported july south sudan repatriate mexican man deported july legal aid sue preemptively block deporting dozen honduran child legal aid sue preemptively block deporting dozen honduran child legal aid sue preemptively block deporting dozen honduran child legal aid sue preemptively block deporting dozen honduran child trump downplays possible regime change venezuela deploys stealth fighter jet news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm chicago brace trump national guard plan hyundai raid put spotlight visa waiver program korean travel hyundai raid put spotlight visa waiver program korean travel hyundai raid put spotlight visa waiver program korean travel hyundai raid put spotlight visa waiver program korean travel hyundai raid put spotlight visa waiver program korean travel eswatini meet african country kilmar abrego garcia next celebration sukkot oct clearbrook minnesota elgin news digest board cody holt running senate ecc announces student school year biden chooses delaware presidential library pick board raise fund aclu argues border patrol broke court order highprofile sacramento raid adam zyglis bill opener lawmaker utah supreme court theyre harmed judge ruling gerrymandering case democrat blast raid koreanrun hyundai worksite georgia chicago mexican independence day celebration shadowed trump threat chicago mexican independence day celebration shadowed trump threat chicago mexican independence day celebration shadowed trump threat begun operation boston area begun operation boston area new york hyundai raid put spotlight visa waiver program korean travel budget airline launch new flight popular destination greece italy caribbean thousand celebrate culture schenectady festival weekend atlanta investor acquires industrial facility jobhopping path higher pay since staying put better delorenzos pizza renovation underway pizza marijuana dispensary amazon cut seller fee boost ai tool ahead festive shopping season gm ceo mary barra sell personal stock company mass timber lego flyvbjergs modularity meet lowcarbon construction nation development corporation open new transcanada highway gas station gst reform taxation cant emotional decision fm sitharaman el paso celebrates groundbreaking million sean haggerty dr extension project thought moderna mrna florida vaccine rule jim cramer ciena corporation cien terrific company jim cramer cultural nostalgia gen z drive boom grannycore activity mahjong baking needlework buying best build wealth buying best build wealth buying best build wealth buying best build wealth jim cramer reveals texas instrument incorporated txns share dipped lower buying best build wealth mississippi hunter snag foot alligator look straight jurassic park movie kohl corporation k decent quarter jim cramer best walmart deal score massive discount tech appliance essential rosen highly ranked law firm encourages lineage investor secure counsel rosen highly ranked law firm encourages lineage investor secure counsel rosen highly ranked law firm encourages lineage investor secure counsel rosen highly ranked law firm encourages lineage investor secure counsel europe slap billion fine google donald trump money instead american investment job woman drive jeep oil change drive chevy equinox ev arctic pablo coin presale cross raising stake new meme coin join shiba inu brett ground shes sweet success bittersweet candy heather lent reflects success w podcast rosen highly ranked law firm encourages lineage investor secure counsel important deadline security class action line horror box office blow past billion conjuring rite take thirdlargest domestic opening ever new era smart living ecovacs unveils deebot x powerboost technology ifa taste test woodford reserve single malt craft distillery leg big boy zuckerberg shredded awkward hot mic trump powerball lottery winner missouri texas split nearly billion jackpot shiba inus shibarium debut embarrassing marketing plan community anger grows postal import plunge tariff exemption end tennis aryna sabalenka becomes woman straight open since serena williams decade ago david blackmon trump consequential energy president history powerball ticket sold colorado million powerball ticket sold colorado million kennedy must critic stripe maha sham trump approval milestone signal strong support policy victory centre step effort rollout ambitious national deepwater mission face nation king named board chairwoman money deep negotiation hamas end gaza conflict trump stand sunday national interfaith coalition call end antisemitism faithbased hate kitchen commercial processor margarita elote nacho redbird open old rincon market powerball player million ohio billion jackpot hit powerball player million ohio billion jackpot hit massachusetts lag housing production unit added healeys term acacajunmantriathlonjpg acacajunmantriathlonjpg postal traffic drop trade exemption rule end un agency postal traffic drop trade exemption rule end un agency npr postal traffic drop trade exemption rule end un agency revenue loss govts build pressure centre gst reform hitting switzerland tariff trump watch open men final rolex suite source federal coal lease fasttracked north dakota environmental object david blackmon trump consequential energy president history gst cut partial cushion trade headwind mahesh nandurkar alphabet googl share acquired sepio capital lp select equity lp decrease stake visa v undersea cable cut red sea disrupting internet access asia mideast global edtech company xed set syllabus gift listing smartest money isnt becoming fully draftkings promo code bet nfl sunday ticket bonus lion v packer longstanding tax wealth central issue prosperous norway vote close election fanduel promo code bet lion v packer social debt around kent county council written ohio donor ditch tim ryan pour nearly k vivek ramaswamys governor bid rare soughtafter bourbon set annual auction kentucky museum missouri texas player claim recordbreaking billion powerball jackpot powerball winning ticket sold texas missouri nearly billion jackpot cayuga county real estate sold aug sept push ban stock trading congress follows il rep reported violation issuer mega deal qip issuance split story watsonville council vote expanding license plate reader program sept sec scott bessent gov wes moore sen cory booker lancaster county lake health alert update floyd county consider op</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:J54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2342,6 +2342,42 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="B54" t="n">
+        <v>6512.60986328125</v>
+      </c>
+      <c r="C54" t="n">
+        <v>6518.22998046875</v>
+      </c>
+      <c r="D54" t="n">
+        <v>6483.080078125</v>
+      </c>
+      <c r="E54" t="n">
+        <v>6503.330078125</v>
+      </c>
+      <c r="F54" t="n">
+        <v>4798350000</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.0026881536531127</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>average wyoming gasoline price up cent per gallon in past week skechers are comfortable reliable and up to off right now michigan want b from worker it say were overpaid covid unemployment benefit celebrating people choice prairie fire glass fincen warns of surge in financially motivated sextortion hazard alert ai enabled bot undermining safety training putting organization and worker at risk inception growth acquisition limited nasdaqigta see large growth in short interest elis sa otcmktselssf short interest update click group limited otcmktsclcgy short interest update meiji yasuda life insurance co ha million position in alphabet inc googl short interest in givaudan sa otcmktsgvdbf decline by maruichi steel tube ltd otcmchif see large increase in short interest short interest in strive dividend growth etf nysearcastxd increase by meiji yasuda life insurance co decrease stock position in alphabet inc googl celsius nasdaqcelh trading down after insider selling global x sp covered call etf nysearcaxyld see large increase in short interest alphabet inc googl stake raised by coppell advisory solution llc brp nasdaqdooo reach new year high after analyst upgrade inception growth acquisition limited nasdaqigtar short interest up in august maruichi steel tube ltd otcmchif see significant increase in short interest market have real tailwind and focus will return to fundamental laffer tenglers nancy tengler investor alert pomerantz law firm reminds investor with loss on their investment in replimune group inc of class action lawsuit and upcoming deadline repl investor alert pomerantz law firm investigates claim on behalf of investor of neogen corporation neog fermi ipo ride ai power boom a data center lock in renewables nuclear pomerantz law firm announces the filing of a class action against tesla inc and certain officer tsla latest global sewage pump market sizeshare worth usd billion by at a cagr custom market insight analysis outlook leader report trend forecast segmentation growth rate value swot analysis pomerantz law firm announces the filing of a class action against nutex health inc and certain officer nutx investor alert pomerantz law firm reminds investor with loss on their investment in centene corporation of class action lawsuit and upcoming deadline cnc pomerantz law firm announces the filing of a class action against dow inc and certain officer dow amazon is selling a kitchen pantry cabinet for thats functional and attractive pomerantz law firm announces the filing of a class action against cto realty growth inc and certain officer cto investor alert pomerantz law firm reminds investor in easterly rocmuni high income municipal bond fund fka principal street high income municipal fund of class action lawsuit and upcoming deadline rmhix rmhvx rmjax investor alert pomerantz law firm reminds investor with loss on their investment in fiserv inc of class action lawsuit and upcoming deadline fi why is bitcoin price down today what doe the future hold for btc latest global sewage pump market sizeshare worth usd billion by at a cagr custom market insight analysis outlook leader report trend forecast segmentation growth rate value swot analysis solventum announces pricing of it upsized billion note tender offer investor alert pomerantz law firm reminds investor with loss on their investment in rxsight inc of class action lawsuit and upcoming deadline rxst bitcoin news today bitcoin mining difficulty hit new high a industry face growing challenge jf lehman company announces team addition and promotion pomerantz law firm announces the filing of a class action against biohaven ltd and certain officer bhvn pomerantz law firm announces the filing of a class action against unicycive therapeutic inc and certain officer uncy lifeway food announces muscle matestm a breakthrough functional beverage with creatine protein and probiotic disrupting the fitness nutrition category pomerantz law firm announces the filing of a class action against alto neuroscience inc and certain officer anro amid deep funding cut montanapbs plan to expand in eastern montana pomerantz law firm announces the filing of a class action against flywire corporation and certain officer flyw investor alert pomerantz law firm reminds investor with loss on their investment in xplr infrastructure lp fka nextera energy partner lp of class action lawsuit and upcoming deadline xifr investor alert pomerantz law firm investigates claim on behalf of investor of capricor therapeutic inc capr solventum announces pricing of it upsized billion note tender offer trump quietly give jd vance a tiny sliver of his fundraising ahead of election nasdaq hit record high a trader focus on rate cut reuters the world of han zimmer a new dimension delivers electrifying start to north american tour the world of han zimmer a new dimension delivers electrifying start to north american tour septum get ok from shapiro to spend project money to avoid service cut septum get ok from shapiro to spend project money to avoid service cut septum get ok from shapiro to spend project money to avoid service cut septum get ok from shapiro to spend project money to avoid service cut septum get ok from shapiro to spend project money to avoid service cut septum get ok from shapiro to spend project money to avoid service cut septum get ok from shapiro to spend project money to avoid service cut septum get ok from shapiro to spend project money to avoid service cut dogecoin and shiba inu holder diversify into viral altcoins like remittix a meme season fade financial page summary taxation change of the one big beautiful bill bitcoin at k ethereum k solana ozak ai price prediction still dominates robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home robinhood join new band of company calling the sp their home trumpworld wooing candidate to run against desantis handpicked attorney general ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt why is france on the brink of collapse again pm loses key confidence vote a economic turmoil deepens johnson say he didnt use right terminology in calling trump an epstein informant calhoun cleburne commissioner elected to statewide committee inception growth acquisition limited nasdaqigtar short interest up in august jpmorgan u tech leader etf nasdaqjtek see significant drop in short interest brp nasdaqdooo reach new year high after analyst upgrade vancity investment management ltd take position in alphabet inc googl chicago democrat warns history will prove party wrong on crime a official reject trump help free speech university in austin make freshman read palantir ceo deep thought truck driver charged with murder at i san simon rest area detail on trump initial supreme court win over immigration stop ftc member removal ua board of trustee chair say university will take sander annual rivalry suggestion under consideration mayoral forum run into headwind thousand rally in serbia and accuse police of brutality at antigovernment demonstration thousand rally in serbia and accuse police of brutality at antigovernment demonstration thousand rally in serbia and accuse police of brutality at antigovernment demonstration thousand rally in serbia and accuse police of brutality at antigovernment demonstration thousand rally in serbia and accuse police of brutality at antigovernment demonstration thousand rally in serbia and accuse police of brutality at antigovernment demonstration doj panel make clear illegal alien are subject to mandatory detention exmicrosoft ai strategist run for illinois congress on balanced oversight platform beckwiths haitian asylum post spark conservative backlash state department adjudicating nonimmigrant visa applicant in their country of nationality or residence short interest in vanguard largecap etf nysearcavv increase by first trust morningstar dividend leader index fund nysearcafdl see large decline in short interest cbs news tap former ceo of conservative think tank a ombudsman to monitor bias u supreme court allows trump controversial immigration raid to continue ap sport summarybrief at pm edt hegseth caine visit puerto rico a u step up military ops in caribbean trump want to cut program used for rural housing need ap news summary at pm edt appeal court upholds e jean carroll m defamation judgment against trump race crime and medium bias collide on a charlotte light rail train epstein survivor who invited trump to meet with her say shes heard cricket in response republican senator investigate palisade fire response letter to the editor white culture crockett trump administration protects pedophile criminal promising blockchain stock to watch today september th tech giant race for trump aidriven golden dome missile shield visiting lawmaker look to tweak great american outdoors act which give billion to park nbc exclusive mesquite father who say he wa shot by kid at park sunday night speaks out scotus allows trump firing of exschumer aide from ftc for now dave yost just detonated year of cuyahoga county government with a single opinion macomb county judge toss marijuana charge ruling legalization law trump schoolzone statute broadcom nasdaqavgo trading higher on analyst upgrade gofundme yank down fundraiser for suspect in murder of woman on charlotte light rail french government collapse a prime minister is ousted new mexico to be first state to launch universal child care system governor announces man accused of trying to assassinate trump blocked from asking potential juror about gaza and greenland french premier francois bayrou to resign after losing confidence vote french premier francois bayrou to resign after losing confidence vote republican block epstein file discharge petition im nobody justice amy coney barrett insists shes not in trump pocket durango police chief review enforcement philosophy five year of ticketing sabrina carpenter dragged for trans right themed vmas performance new york ag will defend her state abortion shield law from texas challenge concerned chicago resident hand out flyer warning public of right ahead of ice raid geneva firefighter get new union contract david marcus this is our last shared experience and it shaping the culture war ap news summary at pm edt ap news summary at pm edt israeli force bomb loot vandalize our home in gaza we long for normal life french premier francois bayrou to resign after losing confidence vote mon sep pst dhs launch new immigration enforcement operation in chicago owner of penn hill care home pleads guilty to m health care fraud i am proud to serve supreme court justice amy coney barrett open up about being on the bench im just trying to find out if shes ok with immigration detainee location still unknown protester gather outside of oswego border patrol station johnson say he didnt use right terminology in calling trump an epstein informant politico commentary trump is old and ailing but democrat shouldnt count on time to solve their problem sam bregman get jicarilla apache endorsement in governor race supreme court lift restriction on la immigration stop set after agent swept up u citizen letter trump turning u into a police state letter trump turning u into a police state letter trump turning u into a police state the capitulation of the u medium is not an aberration what lorains proposed ban on public sleeping would do and why critic are worried appeal court reject state challenge to probationary worker firing appeal court reject state challenge to probationary worker firing charlotte mayor despicable response to monster who murdered innocent young woman is who the dems are pritzker sign behavioral health data law amid privacy concern dnr to hold meeting on proposed sunfish bag limit for rabideau lake ap sport summarybrief at pm edt ap sport summarybrief at pm edt french prime minister francois bayrou ousted after losing confidence vote horrifying supreme court insane new ruling spark immediate outrage ap news summary at pm edt elderly couple turn table on con artist trying to steal rolex watch ukraine war increasingly likely to go into military analyst say michigan capital plan new approach to homelessness a pod city michigan capital plan new approach to homelessness a pod city</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>average wyoming gasoline price cent per gallon past skechers comfortable reliable michigan b worker overpaid covid unemployment benefit celebrating people choice prairie fire glass fincen warns surge financially motivated sextortion hazard alert ai enabled bot undermining safety training putting organization worker risk inception growth acquisition limited nasdaqigta large growth short interest elis sa otcmktselssf short interest update click limited otcmktsclcgy short interest update meiji yasuda life insurance co million alphabet googl short interest givaudan sa otcmktsgvdbf decline maruichi steel tube otcmchif large increase short interest short interest strive dividend growth etf nysearcastxd increase meiji yasuda life insurance co decrease stock alphabet googl celsius nasdaqcelh trading insider selling global x sp covered call etf nysearcaxyld large increase short interest alphabet googl stake raised coppell advisory solution llc brp nasdaqdooo reach new year high analyst upgrade inception growth acquisition limited nasdaqigtar short interest august maruichi steel tube otcmchif significant increase short interest market real tailwind focus fundamental laffer tenglers nancy tengler investor alert pomerantz law firm reminds investor loss investment replimune class action lawsuit upcoming deadline repl investor alert pomerantz law firm investigates claim behalf investor neogen corporation neog fermi ipo ride ai power boom data center lock renewables nuclear pomerantz law firm announces filing class action tesla certain officer tsla latest global sewage pump market sizeshare worth usd billion cagr custom market insight analysis outlook report trend forecast segmentation growth rate value swot analysis pomerantz law firm announces filing class action nutex health certain officer nutx investor alert pomerantz law firm reminds investor loss investment centene corporation class action lawsuit upcoming deadline cnc pomerantz law firm announces filing class action dow certain officer dow amazon selling kitchen pantry cabinet thats functional attractive pomerantz law firm announces filing class action cto realty growth certain officer cto investor alert pomerantz law firm reminds investor easterly rocmuni high income municipal bond fund fka principal street high income municipal fund class action lawsuit upcoming deadline rmhix rmhvx rmjax investor alert pomerantz law firm reminds investor loss investment fiserv class action lawsuit upcoming deadline fi bitcoin price today doe future btc latest global sewage pump market sizeshare worth usd billion cagr custom market insight analysis outlook report trend forecast segmentation growth rate value swot analysis solventum announces pricing upsized billion note tender offer investor alert pomerantz law firm reminds investor loss investment rxsight class action lawsuit upcoming deadline rxst bitcoin news today bitcoin mining difficulty hit new high industry face growing challenge jf lehman company announces team addition promotion pomerantz law firm announces filing class action biohaven certain officer bhvn pomerantz law firm announces filing class action unicycive therapeutic certain officer uncy lifeway food announces muscle matestm breakthrough functional beverage creatine protein probiotic disrupting fitness nutrition category pomerantz law firm announces filing class action alto neuroscience certain officer anro amid deep funding cut montanapbs plan expand eastern montana pomerantz law firm announces filing class action flywire corporation certain officer flyw investor alert pomerantz law firm reminds investor loss investment xplr infrastructure lp fka nextera energy partner lp class action lawsuit upcoming deadline xifr investor alert pomerantz law firm investigates claim behalf investor capricor therapeutic capr solventum announces pricing upsized billion note tender offer trump quietly give jd vance tiny sliver fundraising ahead election nasdaq hit record high trader focus rate cut reuters world han zimmer new dimension delivers electrifying start north american tour world han zimmer new dimension delivers electrifying start north american tour septum ok shapiro spend project money avoid service cut septum ok shapiro spend project money avoid service cut septum ok shapiro spend project money avoid service cut septum ok shapiro spend project money avoid service cut septum ok shapiro spend project money avoid service cut septum ok shapiro spend project money avoid service cut septum ok shapiro spend project money avoid service cut septum ok shapiro spend project money avoid service cut dogecoin shiba inu holder diversify viral altcoins remittix meme season fade financial page summary taxation change big bill bitcoin k ethereum k solana ozak ai price prediction dominates robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp robinhood join new band company calling sp trumpworld wooing candidate run desantis handpicked attorney general news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm news summary pm france brink collapse pm loses confidence vote economic turmoil deepens johnson didnt terminology calling trump epstein informant calhoun cleburne commissioner elected statewide committee inception growth acquisition limited nasdaqigtar short interest august jpmorgan tech etf nasdaqjtek significant drop short interest brp nasdaqdooo reach new year high analyst upgrade vancity investment management take alphabet googl chicago democrat warns history prove party crime reject trump help free speech university austin freshman palantir ceo deep thought truck driver charged murder san simon rest area detail trump initial supreme court immigration stop ftc removal ua board trustee chair university take sander annual rivalry suggestion consideration mayoral forum run headwind thousand rally serbia accuse police brutality antigovernment demonstration thousand rally serbia accuse police brutality antigovernment demonstration thousand rally serbia accuse police brutality antigovernment demonstration thousand rally serbia accuse police brutality antigovernment demonstration thousand rally serbia accuse police brutality antigovernment demonstration thousand rally serbia accuse police brutality antigovernment demonstration doj panel illegal alien subject mandatory detention exmicrosoft ai strategist run illinois congress balanced oversight platform beckwiths haitian asylum post spark conservative backlash department adjudicating nonimmigrant visa applicant country nationality residence short interest vanguard largecap etf nysearcavv increase trust morningstar dividend index fund nysearcafdl large decline short interest cbs news tap ceo conservative tank ombudsman monitor bias supreme court allows trump controversial immigration raid continue sport summarybrief pm hegseth caine visit puerto rico step military ops caribbean trump cut program used rural housing news summary pm appeal court upholds e jean carroll defamation judgment trump race crime medium bias collide charlotte light rail train epstein survivor invited trump meet shes heard cricket response republican senator investigate palisade fire response letter editor white culture crockett trump administration protects pedophile criminal promising blockchain stock watch today september tech giant race trump aidriven golden dome missile shield visiting lawmaker look tweak great american outdoors act give billion park nbc exclusive mesquite father shot kid park sunday night speaks scotus allows trump firing exschumer aide ftc dave yost detonated year cuyahoga county government single opinion macomb county judge toss marijuana charge ruling legalization law trump schoolzone statute broadcom nasdaqavgo trading higher analyst upgrade gofundme yank fundraiser suspect murder woman charlotte light rail french government collapse prime minister ousted new mexico launch universal child care system governor announces man accused assassinate trump blocked asking potential juror gaza greenland french premier francois bayrou resign losing confidence vote french premier francois bayrou resign losing confidence vote republican block epstein file discharge petition im nobody justice amy coney barrett insists shes trump pocket durango police chief review enforcement philosophy year ticketing sabrina carpenter dragged trans themed vmas performance new york ag defend abortion shield law texas challenge concerned chicago resident flyer warning public ahead raid geneva firefighter new union contract david marcus shared experience shaping culture war news summary pm news summary pm israeli force bomb loot vandalize gaza normal life french premier francois bayrou resign losing confidence vote mon sep pst dhs launch new immigration enforcement operation chicago owner penn hill care pleads guilty health care fraud proud supreme court justice amy coney barrett open bench im find shes ok immigration detainee location unknown protester gather outside oswego border patrol station johnson didnt terminology calling trump epstein informant politico commentary trump old ailing democrat shouldnt count solve problem sam bregman jicarilla apache endorsement governor race supreme court lift restriction la immigration stop set agent swept citizen letter trump turning police letter trump turning police letter trump turning police capitulation medium aberration lorains proposed ban public sleeping critic worried appeal court reject challenge probationary worker firing appeal court reject challenge probationary worker firing charlotte mayor despicable response monster murdered innocent young woman dems pritzker sign behavioral health data law amid privacy concern dnr meeting proposed sunfish bag limit rabideau lake sport summarybrief pm sport summarybrief pm french prime minister francois bayrou ousted losing confidence vote horrifying supreme court insane new ruling spark immediate outrage news summary pm elderly couple turn table con artist steal rolex watch ukraine war increasingly likely military analyst michigan capital plan new approach homelessness pod michigan capital plan new approach homelessness pod</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2378,6 +2378,42 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45910</v>
+      </c>
+      <c r="B55" t="n">
+        <v>6532.0400390625</v>
+      </c>
+      <c r="C55" t="n">
+        <v>6555.97021484375</v>
+      </c>
+      <c r="D55" t="n">
+        <v>6516.33984375</v>
+      </c>
+      <c r="E55" t="n">
+        <v>6550.2900390625</v>
+      </c>
+      <c r="F55" t="n">
+        <v>5253010000</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0029834699435626</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>doing thing differently city first standing committee meeting today san jose home sell for million san jose home sell for million how to achieve a perfect credit score and why you dont really need it how to achieve a perfect credit score and why you dont really need it how to achieve a perfect credit score and why you dont really need it how to achieve a perfect credit score and why you dont really need it how to achieve a perfect credit score and why you dont really need it how to achieve a perfect credit score and why you dont really need it large social and economic inequality persist among uk doctor study reveals softwaredefined memory sdm pioneer kove announces benchmark showing x larger ai inference workload on redis valkey with lower latency than local memory business journal reveals washington fastestgrowing private company rmcad reaffirms commitment to excellence with reaccreditation from the higher learning commission the pge corporation foundation and california fire foundation announce wildfire safety grant for eighth consecutive year ose immunotherapeutics board urge support for valuedriving strategy and openminded governance publication of circular for combined annual general meeting of september saudi arabia trillion wealth fund to unveil new investment strategy shiba inu shib and pepe coin pepe set to crash but new competitor below offer a better investment for striper set to paint the town budgetfriendly paved lot maintenance come to corpus christi striper set to paint the town budgetfriendly paved lot maintenance come to corpus christi philadelphia eagle receive modest grade for latest roster upgrade ap technology summarybrief at pm edt whats going on with jetblue airway stock tuesday medline unite to launch achilles repair system at aofas annual meeting st charles parish roll back tax to year low a economy strengthens whats going on with trump medium technology stock today trump fed choice wont pledge to resign if term extends past january microsoft tell worker to prepare to return to the office investor action notice moore law pllc encourages investor in charter communication inc to contact law firm investor action notice moore law pllc encourages investor in charter communication inc to contact law firm google cloud leaning on artificial intelligence to gain market share ceo say johnson fistel investigates fairness of proposed sale of staar surgical johnson fistel investigates fairness of proposed sale of staar surgical crude oil strength spark short covering in sugar future government accidentally reveals someone inside twitter fabricated gotcha account to frame conservative firebrand eric trump director plan scrapped shifted to observer role on alt sigma board after nasdaq review socialist embraced by democrat make his criminalfriendly case at worst time possible x ha been ceoless for month oddsmakers dont think thats changing maine republican urge trump admin to revoke gulf of maine wind lease federal clean air vehicle cav decal program to end nationwide on october digital sportsman launch innovative business software for guided outdoor adventure company life dental group announces it th consecutive recognition on the inc list ab verifies multipurpose cbm lng carrier and bunker vessel design from hd hyundai mipo adverse weather in west africa and tighter inventory boost cocoa price cracker barrel scrap controversial move and come clean on why all location keep the old look alabamabased energy company announces million acquisition hoc acquires middel consulting american trust ha stake in exxon mobil corporation xom how big is the gender wage gap now what new census data show coffee price undercut by a stronger dollar armor health data driven approach to patient care help secure another agreement in pennsylvania to provide inmate healthcare service for patient in lackawanna county georgia dca accepting public comment on data center through friday ford hint that something big is coming after wiping it entire instagram mauldin vaught partner with crete professional alliance expanding resource and strengthening client offering mauldin vaught partner with crete professional alliance expanding resource and strengthening client offering mauldin vaught partner with crete professional alliance expanding resource and strengthening client offering mauldin vaught partner with crete professional alliance expanding resource and strengthening client offering billiondownload npm package hijacked in cryptostealing attack smokey bone barbecue chain closing more restaurant how will michigan location be impacted hfm investment advisor llc take position in alphabet inc goog democratic ag back quick supreme court review of tariff suit should you buy brcb stock after the black rock coffee bar ipo murdoch succession drama end with eldest son taking control of medium empire what you need to know twenty one pilot sue temu over knockoff merchandise blatant copy nyc grocery delivery worker rally at city hall for more wage and flexible hour the price of building a home keep climbing and uncertainty isnt helping lurie unveils heart of the city plan to revitalize downtown sf the harbor freight product user say it probably best to avoid buying google pixel review best pixel phone till now the ferrari testarossa is back motorcom billionaire gop megadonor ken griffin warns trump federal reserve strategy carry steep cost snag some powerbeats pro at their best price ahead of your next workout wto fishery subsidy agreement to enter into force sept starbucks is closing these store is your favorite location on this list atmos capital gestao de recursos ltda sell share of alphabet inc googl trinity financial advisor llc buy share of alphabet inc googl semmax financial advisor inc buy share of alphabet inc googl sc capital management llc decrease stock holding in alphabet inc googl alphabet inc googl share bought by alaethes wealth llc familyowned john deere dealership expands into nepa median income barely rose during the biden administration median income barely rose during the biden administration lab of crypto announces acquisition and rebrand under portuguese medium firm expands educationfirst blockchain program whats happening to ky bourbon industry join our livestream whats happening to ky bourbon industry join our livestream all entertainment medium group welcome legal titan paul d bekman a newest partner first we got bad job news is inflation also going to get worse now israeli strike target hamas leader in qatar a they weigh gaza ceasefire proposal israeli strike target hamas leader in qatar a they weigh gaza ceasefire proposal israeli strike target hamas leader in qatar a they weigh gaza ceasefire proposal what you should ask about rehab just in time for national recovery month podcasts episode a week cost per episode behind an ai start ups plan wall street hold near it record following the latest report showing the u job market is slowing wall street hold near it record following the latest report showing the u job market is slowing wall street hold near it record following the latest report showing the u job market is slowing wall street hold near it record following the latest report showing the u job market is slowing wall street hold near it record following the latest report showing the u job market is slowing wall street hold near it record following the latest report showing the u job market is slowing apple unveils iphone pro and iphone pro max the most powerful and advanced pro model ever apple debut iphone apple debut apple watch series featuring groundbreaking health insight french president emmanuel macron appoints outgoing defense minister sebastien lecornu a prime minister religious leader oppose construction of mega resort at sacred holy site israel doha strike sent a decisive message that terror will find no safe haven new mexico will be the first state to make child care free the th news trump directed envoy to warn qatar ahead of unfortunate israeli strike white house say the liberal jacinta nampijinpa price problem podcast california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california governor criticizes trump and tout achievement in address california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state california gov newsom say trump ha a relentless unhinged obsession with the state rfk jr latest make america healthy again report call for more scrutiny of vaccine and autism ap news summary at pm edt ap news summary at pm edt macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister macron appoints defense minister lecornu a france latest prime minister other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book something can be done about this new plan aim to stop sex abuse in california school other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book dhs say it can build border wall regardless of jaguar other notable name appear in the jeffrey epstein th birthday book ready to do the work shannon stewart sworn in a penticton city councillor penticton macron appoints defense minister lecornu a france latest prime minister other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book the pge corporation foundation and california fire foundation announce wildfire safety grant for eighth consecutive year other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book macron appoints defense minister lecornu a france latest prime minister other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book naomi osaka misplay on race other notable name appear in the jeffrey epstein th birthday book other notable name appear in the jeffrey epstein th birthday book donald trump begs democratic leader to ask him for help in crime crackdown trump plot to derail hillary in set the stage for his epstein nightmare analyst husband is perfect in some way but refuse intimacy husband is perfect in some way but refuse intimacy ny ag intervenes in tx shield lawsuit a gopled legislature clear pathway for civil suit ap business summarybrief at pm edt ap news summary at pm edt get out of there israel warns gaza city to evacuate white house trump wa not an fbi informant on epstein baltimore councilman izzy patoka launch bid for county executive with former governor omalleys endorsement supreme court for now allows u to hold fund it want to rescind housing project move forward in big bear despite pushback from bald eagle advocate macron appoints another loyalist a prime minister after string of failed government rfk jr latest make america healthy again report call for more scrutiny of vaccine and autism iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt iran and the iaea are expected to resume cooperation under an agreement backed by egypt</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>differently standing committee meeting today san jose sell million san jose sell million achieve perfect credit score dont achieve perfect credit score dont achieve perfect credit score dont achieve perfect credit score dont achieve perfect credit score dont achieve perfect credit score dont large social economic inequality persist among uk doctor study reveals softwaredefined memory sdm pioneer kove announces benchmark showing x larger ai inference workload redis valkey lower latency local memory business journal reveals washington fastestgrowing private company rmcad reaffirms commitment excellence reaccreditation higher learning commission pge corporation foundation california fire foundation announce wildfire safety grant eighth consecutive year ose immunotherapeutics board urge support valuedriving strategy openminded governance publication circular combined annual general meeting september saudi arabia trillion wealth fund unveil new investment strategy shiba inu shib pepe coin pepe set crash new competitor offer better investment striper set paint town budgetfriendly paved lot maintenance come corpus christi striper set paint town budgetfriendly paved lot maintenance come corpus christi philadelphia eagle receive modest grade latest roster upgrade technology summarybrief pm whats jetblue airway stock tuesday medline unite launch achilles repair system aofas annual meeting st charles parish roll tax year low economy strengthens whats trump medium technology stock today trump fed choice wont pledge resign term extends past january microsoft worker prepare office investor action notice moore law pllc encourages investor charter communication contact law firm investor action notice moore law pllc encourages investor charter communication contact law firm google cloud leaning artificial intelligence gain market share ceo johnson fistel investigates fairness proposed sale staar surgical johnson fistel investigates fairness proposed sale staar surgical crude oil strength spark short covering sugar future government accidentally reveals someone inside twitter fabricated gotcha account frame conservative firebrand eric trump director plan scrapped shifted observer role alt sigma board nasdaq review socialist embraced democrat criminalfriendly case worst possible x ceoless month oddsmakers dont thats changing maine republican urge trump admin revoke gulf maine wind lease federal clean air vehicle cav decal program end nationwide october digital sportsman launch innovative business software guided outdoor adventure company life dental announces consecutive recognition list ab verifies multipurpose cbm lng carrier bunker vessel design hd hyundai mipo adverse weather west africa tighter inventory boost cocoa price cracker barrel scrap controversial move come clean location old look alabamabased energy company announces million acquisition hoc acquires middel consulting american trust stake exxon mobil corporation xom big gender wage gap new census data coffee price undercut stronger dollar armor health data driven approach patient care help secure another agreement pennsylvania provide inmate healthcare service patient lackawanna county georgia dca accepting public data center friday ford hint something big coming wiping instagram mauldin vaught partner crete professional alliance expanding resource strengthening client offering mauldin vaught partner crete professional alliance expanding resource strengthening client offering mauldin vaught partner crete professional alliance expanding resource strengthening client offering mauldin vaught partner crete professional alliance expanding resource strengthening client offering billiondownload npm package hijacked cryptostealing attack smokey bone barbecue chain closing restaurant michigan location impacted hfm investment advisor llc take alphabet goog democratic ag quick supreme court review tariff suit buy brcb stock black rock coffee bar ipo murdoch succession drama end eldest son taking control medium empire pilot sue temu knockoff merchandise blatant copy nyc grocery delivery worker rally hall wage flexible hour price building climbing uncertainty isnt helping lurie unveils heart plan revitalize downtown sf harbor freight product user probably best avoid buying google pixel review best pixel phone till ferrari testarossa motorcom billionaire gop megadonor ken griffin warns trump federal reserve strategy carry steep cost snag powerbeats pro best price ahead next workout wto fishery subsidy agreement enter force sept starbucks closing store favorite location list atmos capital gestao de recursos ltda sell share alphabet googl trinity financial advisor llc buy share alphabet googl semmax financial advisor buy share alphabet googl sc capital management llc decrease stock holding alphabet googl alphabet googl share bought alaethes wealth llc familyowned john deere dealership expands nepa median income barely rose biden administration median income barely rose biden administration lab crypto announces acquisition rebrand portuguese medium firm expands educationfirst blockchain program whats happening ky bourbon industry join livestream whats happening ky bourbon industry join livestream entertainment medium welcome legal titan paul bekman newest partner got bad job news inflation worse israeli strike target hamas qatar weigh gaza ceasefire proposal israeli strike target hamas qatar weigh gaza ceasefire proposal israeli strike target hamas qatar weigh gaza ceasefire proposal rehab national recovery month podcasts episode cost per episode behind ai start ups plan wall street record following latest report showing job market slowing wall street record following latest report showing job market slowing wall street record following latest report showing job market slowing wall street record following latest report showing job market slowing wall street record following latest report showing job market slowing wall street record following latest report showing job market slowing apple unveils iphone pro iphone pro max powerful advanced pro model ever apple debut iphone apple debut apple watch series featuring groundbreaking health insight french president emmanuel macron appoints outgoing defense minister sebastien lecornu prime minister religious oppose construction mega resort sacred holy site israel doha strike decisive message terror find safe new mexico child care free news trump directed envoy warn qatar ahead unfortunate israeli strike white house liberal jacinta nampijinpa price problem podcast california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california governor criticizes trump tout achievement address california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession california gov newsom trump relentless unhinged obsession rfk jr latest america healthy report call scrutiny vaccine autism news summary pm news summary pm macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister macron appoints defense minister lecornu france latest prime minister notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book something new plan aim stop sex abuse california school notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book dhs build border wall regardless jaguar notable name appear jeffrey epstein birthday book ready work shannon stewart sworn penticton councillor penticton macron appoints defense minister lecornu france latest prime minister notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book pge corporation foundation california fire foundation announce wildfire safety grant eighth consecutive year notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book macron appoints defense minister lecornu france latest prime minister notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book naomi osaka misplay race notable name appear jeffrey epstein birthday book notable name appear jeffrey epstein birthday book donald trump begs democratic help crime crackdown trump plot derail hillary set stage epstein nightmare analyst husband perfect refuse intimacy husband perfect refuse intimacy ny ag intervenes tx shield lawsuit gopled legislature pathway civil suit business summarybrief pm news summary pm israel warns gaza evacuate white house trump fbi informant epstein baltimore councilman izzy patoka launch bid county executive governor omalleys endorsement supreme court allows fund rescind housing project move forward big bear pushback bald eagle advocate macron appoints another loyalist prime minister string failed government rfk jr latest america healthy report call scrutiny vaccine autism iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt iran iaea expected resume cooperation agreement backed egypt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2414,6 +2414,42 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>45911</v>
+      </c>
+      <c r="B56" t="n">
+        <v>6587.47021484375</v>
+      </c>
+      <c r="C56" t="n">
+        <v>6592.89013671875</v>
+      </c>
+      <c r="D56" t="n">
+        <v>6545.7998046875</v>
+      </c>
+      <c r="E56" t="n">
+        <v>6554.41015625</v>
+      </c>
+      <c r="F56" t="n">
+        <v>5426460000</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.008485890387959801</v>
+      </c>
+      <c r="H56" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>were raising our nvidia price target plus report on oracle big new customer the nrp group break ground on churchill gateway ii a unit affordable housing community in cleveland glenville neighborhood the nrp group break ground on churchill gateway ii a unit affordable housing community in cleveland glenville neighborhood the nrp group break ground on churchill gateway ii a unit affordable housing community in cleveland glenville neighborhood network commences patent litigation against optiver network commences patent litigation against optiver network commences patent litigation against optiver network commences patent litigation against optiver network commences patent litigation against optiver israeli airstrikes on yemen kill at least people houthi official say klarna stock surge on wall street debut a ipo wave kick off newsweek and statista announce the world best smart hospital should you ever pay for help with your credit card debt san diego public service whats happening in mission bay park potbelly to be bought for million by convenience store operator racetrac saratoga property sale singlefamily residence sell for million saratoga property sale singlefamily residence sell for million klc investor deadline robbins geller rudman dowd llp announces that kindercare learning company inc investor with substantial loss have opportunity to lead investor class action lawsuit novo nordisk layoff job cut a weightloss drug competition with eli lilly heat up neurosenses drug candidate show early signal of benefit in alzheimers patientderived neuron tvm capital healthcare announces first closing of it usd million southeast asia fund latest global artificial womb facility market sizeshare worth usd million by at a cagr custom market insight analysis outlook leader report trend forecast segmentation growth rate value swot analysis latest global artificial womb facility market sizeshare worth usd million by at a cagr custom market insight analysis outlook leader report trend forecast segmentation growth rate value swot analysis walmarts bestselling outdoor chaise lounger set is on sale for just invent inventor develops allnatural multipurpose solution rkh aehl stock climb with intraday surge and bitcoin treasury hope milk once again the cream of the crop in san joaquin county mailbag all of the above energy menu is nonsense altcoin news lyno ai presale join top mover with massive roi potential shiba inu and dogecoin are good just not enough here the meme coin to buy and flip into in effectual partner with solv energy to implement generative ai solution for enhanced field technician support effectual partner with solv energy to implement generative ai solution for enhanced field technician support general mill recognized on time world best company list this ruling is not the final word trump appeal order blocking him from firing fed governor cook gallery savannah downtown business association host taste of the luncheon kash patel acknowledged firing fbi official for trump wa unlawfulbut did it anyway lawsuit claim acadian asset management llc sell share of alphabet inc googl fortis capital advisor llc acquires share of broadcom inc avgo fortis capital advisor llc sell share of alphabet inc googl geneos wealth management inc acquires share of broadcom inc avgo fran drescher is ready to do other thing after four year a sag president say union is in fantastic shape far better than when i showed up sugar price gain a crude oil rally fit fashion design mfa show act a moment of transformation dialogue and revelation cocoa price climb on adverse west african weather carrollton city council cut property tax for th year approves fiscal year budget coffee price settle higher on brazil crop concern atm fee hit record high again see the worst city pinstripe to file for bankruptcy abruptly close multiple location san diego public service whats happening in mission beach sarasota launch million water main upgrade on n tamiami trail moderate impact on traffic expected tucker carlson expose mark cuban hypocrisy on ukraine aid robinhood is building a social network for following market mover trade eleven bring your own cup day will return with two new slurpee flavor eleven bring your own cup day will return with two new slurpee flavor eleven bring your own cup day will return with two new slurpee flavor eleven bring your own cup day will return with two new slurpee flavor eleven bring your own cup day will return with two new slurpee flavor eleven bring your own cup day will return with two new slurpee flavor eleven bring your own cup day will return with two new slurpee flavor eleven bring your own cup day will return with two new slurpee flavor eleven bring your own cup day will return with two new slurpee flavor eleven bring your own cup day will return with two new slurpee flavor coreweaves stock ha surged in day why investor might be getting ahead of themselves ntsb warns landbased firefighter unprepared for vessel fire call for urgent training reform amd stock is surging wednesday whats going on ticket on sale for simmons bank championship caddie shootout presented by saracen casino resort paper mill pumping million into expansion of alabama plant healthverity marketplace celebrates peerreviewed publication gamestop share are trading higher wednesday whats going on uber and pipe team to offer restaurant working capital access rosen a highly ranked law firm encourage dow inc investor to secure counsel before important deadline in security class action dow shortage of homebuyers force many seller to lower price or walk away a sale slump drag on openai oracle sign billion computing deal wsj report yahoo finance cracker barrel returning to handmade biscuit latest in series of change after customer speak out tongji sem na miste v celosvetovem zebricku ft master in management investor alert pomerantz law firm investigates claim on behalf of investor of cybin inc cybn why is the u labor market weakening tesla cfo unloads more stock a ceo pay battle brew michigan senate appropriation leader talk budget negotiation with house a shutdown clock tick michigan senate appropriation leader talk budget negotiation with house a shutdown clock tick sheetz alert customer of higher candy price due to hershey cost increase u stock market today sp climb nasdaq rise dow jones drop investor alert pomerantz law firm investigates claim on behalf of investor of agio pharmaceutical inc agio sheetz alert customer of higher candy price due to hershey cost increase sheetz alert customer of higher candy price due to hershey cost increase houthirun health ministry say israeli strike in yemen have killed at least people and wounded more than houthirun health ministry say israeli strike in yemen have killed at least people and wounded more than uipath path stock update rbc weighs in after strong q metric forget black friday walmart ha off the airwrap right now trump administration appeal ruling blocking him from firing federal reserve gov cook trump administration appeal ruling blocking him from firing federal reserve gov cook trump administration appeal ruling blocking him from firing federal reserve gov cook see home sold in union city area sept to sept south korean plane in atlanta for worker detained in immigration raid departure timeline uncertain here how much stock could tumble if consumer inflation come in hot focus partner wealth purchase share of visa inc v trump demand action from jerome powell a wholesale inflation report stuns economist top technology keywords of september lnth financial loss robbins llp informs investor of the lantheus holding inc class action lawsuit nutx investor have opportunity to lead nutex health inc security fraud lawsuit watch rfk jr knock it out of the park on school shooting we had lot of gun when we were kid ap news summary at pm edt ap news summary at pm edt ap news summary at pm edt crossjurisdiction region of modesto create barrier to ada compliant sidewalk michigan battery maker tell korean worker to stay home after ice raid teamster california california labor federation call on governor newsom to sign ab thinkcarebelieve call initiative for the missing child and to end child trafficking and exploitation from slavery to pollution national park employee flagged material deemed disparaging to u from slavery to pollution national park employee flagged material deemed disparaging to u from slavery to pollution national park employee flagged material deemed disparaging to u from slavery to pollution national park employee flagged material deemed disparaging to u from slavery to pollution national park employee flagged material deemed disparaging to u from slavery to pollution national park employee flagged material deemed disparaging to u from slavery to pollution national park employee flagged material deemed disparaging to u from slavery to pollution national park employee flagged material deemed disparaging to u from slavery to pollution national park employee flagged material deemed disparaging to u how will israeli attack in qatar affect effort to end gaza war new mexico will be the first state to make child care free push to shutter homeless camp ongoing could spread to other part of oklahoma letter the left and free speech dc sandwich guy pleads not guilty to misdemeanor assault trial set for november dc sandwich guy pleads not guilty to misdemeanor assault trial set for november florida is right to end vaccine mandate we should ban them nationally too your turn report tiger employee accused of misconduct dc sandwich guy pleads not guilty to misdemeanor assault trial set for november senate republican throw down with gop governor from his own state texas am fire professor over genderidentity lesson in literature course texas am fire professor over genderidentity lesson in literature course music teacher charged with raping teen worked in syracuse school helped marching band can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast lucids suv could be tesla and rivians worst nightmare can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast harlow school bus service did not violate open record law ag say can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast bill would let wisconsinite bar themselves from buying gun can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast bill would let wisconsinite bar themselves from buying gun can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast can we rebuild trust when we cant agree on fact the ethical life podcast bill would let wisconsinite bar themselves from buying gun dc sandwich guy pleads not guilty to misdemeanor assault trial set for november dc sandwich guy pleads not guilty to misdemeanor assault trial set for november richard m coon iii proposed city ordinance would shorten operating hour for hookah bar dc sandwich guy pleads not guilty to misdemeanor assault trial set for november ice making fewer arrest at san diego immigration court source say kash patel acknowledged firing fbi official for trump wa unlawfulbut did it anyway lawsuit claim man who hurled sandwich at federal agent pleads not guilty to assault charge broadcom inc avgo stock position lifted by geneos wealth management inc appeal court block trump from firing copyright office director vague threat from iranlinked wouldbe attacker spark increased security at critical nyc location ahead of law enforcement prosecutor group voice support for m prison in sioux fall boston mayor michelle wu take victory lap after trouncing josh kraft in preliminary president donald trump seems to pump brake on deploying national guard troop to chicago chicago tribune</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>raising nvidia price target plus report oracle big new customer nrp break ground churchill gateway ii unit affordable housing community cleveland glenville neighborhood nrp break ground churchill gateway ii unit affordable housing community cleveland glenville neighborhood nrp break ground churchill gateway ii unit affordable housing community cleveland glenville neighborhood network commences patent litigation optiver network commences patent litigation optiver network commences patent litigation optiver network commences patent litigation optiver network commences patent litigation optiver israeli airstrikes yemen kill least people houthi klarna stock surge wall street debut ipo wave kick newsweek statista announce world best smart hospital ever pay help credit card debt san diego public service whats happening mission bay park potbelly bought million convenience store operator racetrac saratoga property sale singlefamily residence sell million saratoga property sale singlefamily residence sell million klc investor deadline robbins geller rudman dowd llp announces kindercare learning company investor substantial loss opportunity lead investor class action lawsuit novo nordisk layoff job cut weightloss drug competition eli lilly heat neurosenses drug candidate early signal benefit alzheimers patientderived neuron tvm capital healthcare announces closing usd million southeast asia fund latest global artificial womb facility market sizeshare worth usd million cagr custom market insight analysis outlook report trend forecast segmentation growth rate value swot analysis latest global artificial womb facility market sizeshare worth usd million cagr custom market insight analysis outlook report trend forecast segmentation growth rate value swot analysis walmarts bestselling outdoor chaise lounger set sale invent inventor develops allnatural multipurpose solution rkh aehl stock climb intraday surge bitcoin treasury milk cream crop san joaquin county mailbag energy menu nonsense altcoin news lyno ai presale join mover massive roi potential shiba inu dogecoin good enough meme coin buy flip effectual partner solv energy implement generative ai solution enhanced field technician support effectual partner solv energy implement generative ai solution enhanced field technician support general mill recognized world best company list ruling final word trump appeal order blocking firing fed governor cook gallery savannah downtown business association host taste luncheon kash patel acknowledged firing fbi trump unlawfulbut anyway lawsuit claim acadian asset management llc sell share alphabet googl fortis capital advisor llc acquires share broadcom avgo fortis capital advisor llc sell share alphabet googl geneos wealth management acquires share broadcom avgo fran drescher ready year sag president union fantastic shape far better showed sugar price gain crude oil rally fit fashion design mfa act moment transformation dialogue revelation cocoa price climb adverse west african weather carrollton council cut property tax year approves fiscal year budget coffee price settle higher brazil crop concern atm fee hit record high worst pinstripe file bankruptcy abruptly close multiple location san diego public service whats happening mission beach sarasota launch million water main upgrade n tamiami trail moderate impact traffic expected tucker carlson expose mark cuban hypocrisy ukraine aid robinhood building social network following market mover trade cup day new slurpee flavor cup day new slurpee flavor cup day new slurpee flavor cup day new slurpee flavor cup day new slurpee flavor cup day new slurpee flavor cup day new slurpee flavor cup day new slurpee flavor cup day new slurpee flavor cup day new slurpee flavor coreweaves stock surged day investor getting ahead ntsb warns landbased firefighter unprepared vessel fire call urgent training reform amd stock surging wednesday whats ticket sale simmons bank championship caddie shootout presented saracen casino resort paper mill pumping million expansion alabama plant healthverity marketplace celebrates peerreviewed publication gamestop share trading higher wednesday whats uber pipe team offer restaurant working capital access rosen highly ranked law firm encourage dow investor secure counsel important deadline security class action dow shortage homebuyers force seller lower price walk away sale slump drag openai oracle sign billion computing deal wsj report yahoo finance cracker barrel returning handmade biscuit latest series change customer speak tongji sem na miste v celosvetovem zebricku ft master management investor alert pomerantz law firm investigates claim behalf investor cybin cybn labor market weakening tesla cfo unloads stock ceo pay battle brew michigan senate appropriation budget negotiation house shutdown clock tick michigan senate appropriation budget negotiation house shutdown clock tick sheetz alert customer higher candy price due hershey cost increase stock market today sp climb nasdaq rise dow jones drop investor alert pomerantz law firm investigates claim behalf investor agio pharmaceutical agio sheetz alert customer higher candy price due hershey cost increase sheetz alert customer higher candy price due hershey cost increase houthirun health ministry israeli strike yemen killed least people wounded houthirun health ministry israeli strike yemen killed least people wounded uipath path stock update rbc weighs strong q metric forget black friday walmart airwrap trump administration appeal ruling blocking firing federal reserve gov cook trump administration appeal ruling blocking firing federal reserve gov cook trump administration appeal ruling blocking firing federal reserve gov cook sold union area sept sept south korean plane atlanta worker detained immigration raid departure timeline uncertain stock tumble consumer inflation come hot focus partner wealth purchase share visa v trump demand action jerome powell wholesale inflation report stuns economist technology keywords september lnth financial loss robbins llp informs investor lantheus holding class action lawsuit nutx investor opportunity lead nutex health security fraud lawsuit watch rfk jr knock park school shooting lot gun kid news summary pm news summary pm news summary pm crossjurisdiction region modesto create barrier ada compliant sidewalk michigan battery maker korean worker stay raid teamster california california labor federation call governor newsom sign ab thinkcarebelieve call initiative missing child end child trafficking exploitation slavery pollution national park employee flagged material deemed disparaging slavery pollution national park employee flagged material deemed disparaging slavery pollution national park employee flagged material deemed disparaging slavery pollution national park employee flagged material deemed disparaging slavery pollution national park employee flagged material deemed disparaging slavery pollution national park employee flagged material deemed disparaging slavery pollution national park employee flagged material deemed disparaging slavery pollution national park employee flagged material deemed disparaging slavery pollution national park employee flagged material deemed disparaging israeli attack qatar affect effort end gaza war new mexico child care free push shutter homeless camp ongoing spread part oklahoma letter left free speech dc sandwich guy pleads guilty misdemeanor assault trial set november dc sandwich guy pleads guilty misdemeanor assault trial set november florida end vaccine mandate ban nationally turn report tiger employee accused misconduct dc sandwich guy pleads guilty misdemeanor assault trial set november senate republican throw gop governor texas fire professor genderidentity lesson literature course texas fire professor genderidentity lesson literature course music teacher charged raping teen worked syracuse school helped marching band rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast lucids suv tesla rivians worst nightmare rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast harlow school bus service violate open record law ag rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast bill wisconsinite bar buying gun rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast bill wisconsinite bar buying gun rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast rebuild trust cant agree fact ethical life podcast bill wisconsinite bar buying gun dc sandwich guy pleads guilty misdemeanor assault trial set november dc sandwich guy pleads guilty misdemeanor assault trial set november richard coon iii proposed ordinance shorten operating hour hookah bar dc sandwich guy pleads guilty misdemeanor assault trial set november making fewer arrest san diego immigration court source kash patel acknowledged firing fbi trump unlawfulbut anyway lawsuit claim man hurled sandwich federal agent pleads guilty assault charge broadcom avgo stock lifted geneos wealth management appeal court block trump firing copyright office director vague threat iranlinked wouldbe attacker spark increased security critical nyc location ahead law enforcement prosecutor voice support prison sioux fall boston mayor michelle wu take victory lap trouncing josh kraft preliminary president donald trump seems pump brake deploying national guard troop chicago chicago tribune</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/notebooks/Cleaned_Topic_Headlines.xlsx
+++ b/notebooks/Cleaned_Topic_Headlines.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2450,6 +2450,42 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="B57" t="n">
+        <v>6584.2900390625</v>
+      </c>
+      <c r="C57" t="n">
+        <v>6600.2099609375</v>
+      </c>
+      <c r="D57" t="n">
+        <v>6579.490234375</v>
+      </c>
+      <c r="E57" t="n">
+        <v>6590.66015625</v>
+      </c>
+      <c r="F57" t="n">
+        <v>4641640000</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-0.0004827613146674</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>bill target trucking standard for hauling livestock worker moved yearold home through downtown tempe to make room for new development atlantic ceo elliot grainge on ai implication will future generation connect to an ai bot the same way a taylor swift make the mailman your dog best friend with barkbox warner bros discovery share jump more than on takeover talk fbi release photo of person of interest in the assassination of charlie kirk finovateeurope unveiling the latest innovation in fintech amazon latest grocery expansion pushed supermarket toward instacart it incoming ceo said tpg to acquire ge vernovas proficy software business for m closing by matt rhule back ncaa plan to end spring transfer portal window matt rhule back ncaa plan to end spring transfer portal window token offering strong upside with lower risk than ripple xrp in amazon is selling a versatile ergonomic office chair for amazon is selling a versatile ergonomic office chair for matt rhule back ncaa plan to end spring transfer portal window cardano face pressure while lyno ai surge ahead with x roi potential eu fix deadline for russian energy exit rejecting trump demand extending coal plant lifespan key to west virginia gov morriseys by energy plan jcpenney launch mackie bob mackie collection to bring red carpet glamour to all jcpenney launch mackie bob mackie collection to bring red carpet glamour to all firm inflation soft job data pull fed in opposing direction the wall street journal top altcoins to watch in ozak solana and pepe u air force and norwegian ally test quicksink antiship weapon in norwegian sea prospect of higher indian sugar export weigh on sugar price city of memphis step in to strengthen mata appoints trustee for operation and financial oversight country financial offer advice on life insurance georgetown approves fy budget of b with lower property tax rate and higher utility rate city commission recognized new business brewtanicals wall street index hit record tesla and micron rally reuters trump nominates pilot for ntsb wealth management associate inc buy share of exxon mobil corporation xom addison capital co lower position in exxon mobil corporation xom u government report billion deficit for august larger than expected credit union with the largest portfolio of home equity loan cheetah mobile announces second quarter unaudited consolidated financial result microsoft exec tell employee in internal meeting rto is backed by data that show inoffice worker are thriving microsoft exec make the case for rto in leaked meeting inperson staff are thriving business insider da davidson raised it price target on nvidia gil luria explains why the u economy ha come down with a case of early onset stagflation eli lilly loses appeal of million medicaid fraud award arabica coffee settle lower on rain forecast for brazil project net million each in state workforce housing tax credit ap business summarybrief at pm edt ap business summarybrief at pm edt ap business summarybrief at pm edt ap business summarybrief at pm edt popular cruise line canceling stop at tropical destination wall street recordsetting run keep motoring on expectation for easier interest rate wall street recordsetting run keep motoring on expectation for easier interest rate wall street recordsetting run keep motoring on expectation for easier interest rate wall street recordsetting run keep motoring on expectation for easier interest rate wall street recordsetting run keep motoring on expectation for easier interest rate mille lac band sign cannabis compact look to become statewide supplier mille lac band sign cannabis compact look to become statewide supplier mille lac band sign cannabis compact look to become statewide supplier mille lac band sign cannabis compact look to become statewide supplier mille lac band sign cannabis compact look to become statewide supplier mille lac band sign cannabis compact look to become statewide supplier mille lac band sign cannabis compact look to become statewide supplier a historic university microgrid cut energy cost and benefit local community a historic university microgrid cut energy cost and benefit local community ge vernovas wind business face a rocky future and southwest give boeing share a lift possible lirr strike and service shutdown on september mta this analyst is pounding the table on micron stock should you buy share here bristol is paving these road this fall strs ohio take million position in cisco system inc csco q earnings here what every music company made energy secretary admits stalling b radioactive waste plant in washington state say murray latest global pharmaceutical metal detector market sizeshare worth usd billion by at a cagr custom market insight analysis outlook leader report trend forecast segmentation growth rate value swot analysis latest global pharmaceutical metal detector market sizeshare worth usd billion by at a cagr custom market insight analysis outlook leader report trend forecast segmentation growth rate value swot analysis sun life marketing pro selected to wrikes elite the inner circle acknowledges connie l doyle a a pinnacle professional member inner circle of excellence the inner circle acknowledges dr curtis l johnston do a a pinnacle lifetime member sun life marketing pro selected to wrikes elite catch the next palantir nvidia or ipo gem here how agilent technology stock is a underperforming the healthcare sector pet owner alert the bissell little green is only at walmart anderson financial strategy llc make new investment in visa inc v simple way to save for the holiday now fayetteville seek resident input for plan aimed at shaping a downtown that work for everyone simple way to save for the holiday now simple way to save for the holiday now ap business summarybrief at pm edt hark capital provides million nav facility to pharos capital group rising inflation and a deteriorating job market put the fed and american in a difficult spot best stock to invest in for the next year rising inflation and a deteriorating job market put the fed and american in a difficult spot credit union with the largest portfolio of first mortgage loan rising inflation and a deteriorating job market put the fed and american in a difficult spot nyc loses million in head start funding for lowincome family report say glitter to gloom on the brass lane a export order dry up ahead of diwali step out in style and comfort this fall with off your first order at bombas leidos australia begin local production of autonomous sea archer vessel fidelity national information service launch aipowered neural treasury suite allstate and nacda honor studentathletes for community service diebold nixdorfs vcplite software implemented by eurasian bank in kazakhstan barclays maintains buy rating on rxo cite strong q performance aidriven productivity gain jefferies raise fortrea ftre pt to amid improved biotech funding circle fireblocks partner to accelerate stablecoin adoption for financial institution argus lower cava group cava pt to despite strong q revenue growth u islamic advocacy group urge schumer jeffries to endorse mamdani for new york mayor steven olikara reacts to charlie kirk killing a lawmaker denounce political violence harris county precinct commissioner briones state sen cook share policy update in town hall random act of patriotism remembers those lost to district fired teacher who made pedophile party accusation belarus free political prisoner a u lift some sanction on it national airline newsroom edition is coalition chaos making life easier for albanese podcast pillen approves nebraska updated medical marijuana regulation america l losing it democratic edge gesture of goodwill at time of need will stay with me forever zohran mamdani steer clear of mayoral opponent trump admin official at ceremony hundred of south korean arrested in a u immigration raid are being sent home pillen approves nebraska updated medical marijuana regulation senate mount new russia pressure campaign the assassination of charlie kirk what response to protrump icon killing mary ellen klas the ice raid on the georgia hyundai plant make no sense mary ellen klas the ice raid on the georgia hyundai plant make no sense mary ellen klas the ice raid on the georgia hyundai plant make no sense rockwall county announces new voting location courthouse annex now the goto spot for ballot letter mayor ha worked with union jury trial of ryan routh man accused of trying to kill trump begin in florida npr british ambassador get the sack over epstein link called him my best pal flower in wake of charlie kirk murder you see who ha sickness of soul flower in wake of charlie kirk murder you see who ha sickness of soul wellpreserved amazon rainforest on indigenous land can protect people from disease study find hawaii governor order flag at halfstaff in remembrance of and charlie kirk a a stand against political violence why st paul midway neighborhood still struggle amid sign of promise supreme court allows random ice stop in los angeles what to know secret service under pressure what kirk assassination mean for trump security walking tall sordid allegation against legendary tennessee sheriff are shocking intrua financial llc grows holding in pepsico inc pep text reveal dialogue between mayor johnson controversial frontrunner in nycs mayoral race mike johnson try to keep a lid on partisan tension after kirk slaying american are virtually united on key aspect of charlie kirk slaying new poll show joe concha say u will go right back to same political discourse after charlie kirk death charlie kirk supporter aim to raise m on givesendgo for his family after assassination polish member of european parliament call for moment of silence for charlie kirk refused by leftist chair exclusive mike lee seek bipartisan resolution honoring charlie kirk a champion for free speech and truth san francisco mayor family zoning plan met with strong opposition roughly davidson county voter purged charlie kirk casket to be flown to arizona aboard air force two the latest pentagon ceremony moved inside due to security concern the latest pentagon ceremony moved inside due to security concern the latest pentagon ceremony moved inside due to security concern mille lac band sign cannabis compact look to become statewide supplier mille lac band sign cannabis compact look to become statewide supplier southington honor those killed on will the gop weaponization panel care about the allegation in the new fbi lawsuit texas am professor appeal firing for lesson with content on gender not many voter came out for tuesday boston election how doe it compare to other year major road in florida could be renamed after charlie kirk county commissioner say local leader condemn political violence gov jim pillen approves nebraska medical marijuana regulation that cap number of plant cbc announces ibanera a title sponsor for the rd annual cbc summit usa this september in washington dc tool who monitor threat to democracy say it maga thats escalating violent rhetoric after kirk death charlie kirk died fighting the idea that word are violence opinion charlie kirk died fighting the idea that word are violence opinion charlie kirk died fighting the idea that word are violence opinion charlie kirk died fighting the idea that word are violence opinion charlie kirk died fighting the idea that word are violence opinion charlie kirk died fighting the idea that word are violence opinion charlie kirk died fighting the idea that word are violence opinion charlie kirk died fighting the idea that word are violence opinion charlie kirk died fighting the idea that word are violence opinion charlie kirk died fighting the idea that word are violence opinion naval academy on lockdown shot heard inside hall state official protest flaglowering for racist sexist homophobic charlie kirk absolutely uncalled for and insane family of person interrogated after charlie kirk assassination speaks out cspan make appalling mistake in charlie kirk headline public safety forum highlight community policing absolutely uncalled for and insane family of person interrogated after charlie kirk assassination speaks out absolutely uncalled for and insane family of person interrogated after charlie kirk assassination speaks out bomb threat called into democratic national committee headquarters the latest fbi release photo of a person of interest in kirk assassination the latest fbi release photo of a person of interest in kirk assassination the latest fbi release photo of a person of interest in kirk assassination the latest fbi release photo of a person of interest in kirk assassination eu parliament denies rightwing request for moment of silence for charlie kirk selena gomez tap jimmy kimmel to host third annual rare impact fund benefit featuring the maria the latest trump mark anniversary at the pentagon the latest trump mark anniversary at the pentagon time to push back against a capricious and dangerous president letter to the editor chris roemer democrat unhinged election strategy commentary kirk vigil to be held at texas am on thursday night rip charlie kirk he practiced politics the right way nyc mayor race adam campaign say it future may rest with independent internal poll haiti un relief chief implores we have to do better to support gangravaged nation park maintenance notice for blackfoot tennessee woman convicted for role in human trafficking of pope county teen is a noshow at revocation hearing never forget annual day of remembrance brings memory call for unity and service sticking with maine football team pay for this black bear maine principal group fight doj subpoena for student athlete name maine principal fight doj request for student name in transgender athlete case maine principal fight doj request for student name in transgender athlete case maine principal fight doj request for student name in transgender athlete case former u senator bob menendezs wife sentenced to year in bribery case conservative pundit matt walsh issue defiant statement a he receives flood of death threat senate republican defeat effort by democrat to force release of epstein file gloversville considers extending moratorium on solar battery storage facility msnbc fire matthew dowd for his charlie kirk comment</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>bill target trucking hauling livestock worker moved yearold downtown tempe room new development atlantic ceo elliot grainge ai implication future generation connect ai bot taylor swift mailman dog best friend barkbox warner bros discovery share jump takeover fbi release photo interest assassination charlie kirk finovateeurope unveiling latest innovation fintech amazon latest grocery expansion pushed supermarket instacart incoming ceo tpg acquire ge vernovas proficy software business closing matt rhule ncaa plan end spring transfer portal window matt rhule ncaa plan end spring transfer portal window token offering strong upside lower risk ripple xrp amazon selling versatile ergonomic office chair amazon selling versatile ergonomic office chair matt rhule ncaa plan end spring transfer portal window cardano face pressure lyno ai surge ahead x roi potential eu fix deadline russian energy exit rejecting trump demand extending coal plant lifespan west virginia gov morriseys energy plan jcpenney launch mackie bob mackie collection red carpet glamour jcpenney launch mackie bob mackie collection red carpet glamour firm inflation soft job data pull fed opposing direction wall street journal altcoins watch ozak solana pepe air force norwegian ally test quicksink antiship weapon norwegian sea prospect higher indian sugar export weigh sugar price memphis step strengthen mata appoints trustee operation financial oversight country financial offer advice life insurance georgetown approves fy budget b lower property tax rate higher utility rate commission recognized new business brewtanicals wall street index hit record tesla micron rally reuters trump nominates pilot ntsb wealth management associate buy share exxon mobil corporation xom addison capital co lower exxon mobil corporation xom government report billion deficit august larger expected credit union largest portfolio equity loan cheetah mobile announces quarter unaudited consolidated financial microsoft exec employee internal meeting rto backed data inoffice worker thriving microsoft exec case rto leaked meeting inperson staff thriving business insider da davidson raised price target nvidia gil luria explains economy come case early onset stagflation eli lilly loses appeal million medicaid fraud award arabica coffee settle lower rain forecast brazil project net million workforce housing tax credit business summarybrief pm business summarybrief pm business summarybrief pm business summarybrief pm popular cruise line canceling stop tropical destination wall street recordsetting run motoring expectation easier interest rate wall street recordsetting run motoring expectation easier interest rate wall street recordsetting run motoring expectation easier interest rate wall street recordsetting run motoring expectation easier interest rate wall street recordsetting run motoring expectation easier interest rate mille lac band sign cannabis compact look become statewide supplier mille lac band sign cannabis compact look become statewide supplier mille lac band sign cannabis compact look become statewide supplier mille lac band sign cannabis compact look become statewide supplier mille lac band sign cannabis compact look become statewide supplier mille lac band sign cannabis compact look become statewide supplier mille lac band sign cannabis compact look become statewide supplier historic university microgrid cut energy cost benefit local community historic university microgrid cut energy cost benefit local community ge vernovas wind business face rocky future southwest give boeing share lift possible lirr strike service shutdown september mta analyst pounding table micron stock buy share bristol paving road fall strs ohio take million cisco system csco q earnings music company energy secretary admits stalling b radioactive waste plant washington murray latest global pharmaceutical metal detector market sizeshare worth usd billion cagr custom market insight analysis outlook report trend forecast segmentation growth rate value swot analysis latest global pharmaceutical metal detector market sizeshare worth usd billion cagr custom market insight analysis outlook report trend forecast segmentation growth rate value swot analysis sun life marketing pro selected wrikes elite inner circle acknowledges connie l doyle pinnacle professional inner circle excellence inner circle acknowledges dr curtis l johnston pinnacle lifetime sun life marketing pro selected wrikes elite catch next palantir nvidia ipo gem agilent technology stock underperforming healthcare sector pet owner alert bissell little green walmart anderson financial strategy llc new investment visa v simple save holiday fayetteville seek resident input plan aimed shaping downtown work everyone simple save holiday simple save holiday business summarybrief pm hark capital provides million nav facility pharos capital rising inflation deteriorating job market put fed american difficult spot best stock invest next year rising inflation deteriorating job market put fed american difficult spot credit union largest portfolio mortgage loan rising inflation deteriorating job market put fed american difficult spot nyc loses million head start funding lowincome family report glitter gloom brass lane export order dry ahead diwali step style comfort fall order bombas leidos australia begin local production autonomous sea archer vessel fidelity national information service launch aipowered neural treasury suite allstate nacda honor studentathletes community service diebold nixdorfs vcplite software implemented eurasian bank kazakhstan barclays maintains buy rating rxo cite strong q performance aidriven productivity gain jefferies raise fortrea ftre pt amid improved biotech funding circle fireblocks partner accelerate stablecoin adoption financial institution argus lower cava cava pt strong q revenue growth islamic advocacy urge schumer jeffries endorse mamdani new york mayor steven olikara reacts charlie kirk killing lawmaker denounce political violence harris county precinct commissioner briones sen cook share policy update town hall random act patriotism remembers district fired teacher pedophile party accusation belarus free political prisoner lift sanction national airline newsroom edition coalition chaos making life easier albanese podcast pillen approves nebraska updated medical marijuana regulation america l losing democratic edge gesture goodwill stay forever zohran mamdani steer mayoral opponent trump admin ceremony south korean arrested immigration raid pillen approves nebraska updated medical marijuana regulation senate mount new russia pressure campaign assassination charlie kirk response protrump icon killing mary ellen klas raid georgia hyundai plant sense mary ellen klas raid georgia hyundai plant sense mary ellen klas raid georgia hyundai plant sense rockwall county announces new voting location courthouse annex goto spot ballot letter mayor worked union jury trial ryan routh man accused kill trump begin florida npr british ambassador sack epstein link best pal flower wake charlie kirk murder sickness soul flower wake charlie kirk murder sickness soul wellpreserved amazon rainforest indigenous land protect people disease study find hawaii governor order flag halfstaff remembrance charlie kirk stand political violence st paul midway neighborhood struggle amid sign promise supreme court allows random stop los angeles secret service pressure kirk assassination trump security walking tall sordid allegation legendary tennessee sheriff shocking intrua financial llc grows holding pepsico pep text reveal dialogue mayor johnson controversial frontrunner nycs mayoral race mike johnson try lid partisan tension kirk slaying american virtually united aspect charlie kirk slaying new poll joe concha political discourse charlie kirk death charlie kirk supporter aim raise givesendgo family assassination polish european parliament call moment silence charlie kirk refused leftist chair exclusive mike lee seek bipartisan resolution honoring charlie kirk champion free speech truth san francisco mayor family zoning plan met strong opposition roughly davidson county voter purged charlie kirk casket flown arizona aboard air force latest pentagon ceremony moved inside due security concern latest pentagon ceremony moved inside due security concern latest pentagon ceremony moved inside due security concern mille lac band sign cannabis compact look become statewide supplier mille lac band sign cannabis compact look become statewide supplier southington honor killed gop weaponization panel care allegation new fbi lawsuit texas professor appeal firing lesson content gender voter came tuesday boston election doe compare year major road florida renamed charlie kirk county commissioner local condemn political violence gov jim pillen approves nebraska medical marijuana regulation cap plant cbc announces ibanera title sponsor rd annual cbc summit usa september washington dc tool monitor threat democracy maga thats escalating violent rhetoric kirk death charlie kirk died fighting idea word violence opinion charlie kirk died fighting idea word violence opinion charlie kirk died fighting idea word violence opinion charlie kirk died fighting idea word violence opinion charlie kirk died fighting idea word violence opinion charlie kirk died fighting idea word violence opinion charlie kirk died fighting idea word violence opinion charlie kirk died fighting idea word violence opinion charlie kirk died fighting idea word violence opinion charlie kirk died fighting idea word violence opinion naval academy lockdown shot heard inside hall protest flaglowering racist sexist homophobic charlie kirk absolutely uncalled insane family interrogated charlie kirk assassination speaks cspan appalling mistake charlie kirk headline public safety forum highlight community policing absolutely uncalled insane family interrogated charlie kirk assassination speaks absolutely uncalled insane family interrogated charlie kirk assassination speaks bomb threat democratic national committee latest fbi release photo interest kirk assassination latest fbi release photo interest kirk assassination latest fbi release photo interest kirk assassination latest fbi release photo interest kirk assassination eu parliament denies rightwing request moment silence charlie kirk selena gomez tap jimmy kimmel host third annual rare impact fund benefit featuring maria latest trump mark anniversary pentagon latest trump mark anniversary pentagon push capricious dangerous president letter editor chris roemer democrat unhinged election strategy commentary kirk vigil texas thursday night rip charlie kirk practiced politics nyc mayor race adam campaign future rest independent internal poll haiti un relief chief implores better support gangravaged nation park maintenance notice blackfoot tennessee woman convicted role human trafficking pope county teen noshow revocation hearing never forget annual day remembrance brings memory call unity service sticking maine football team pay black bear maine principal fight doj subpoena student athlete name maine principal fight doj request student name transgender athlete case maine principal fight doj request student name transgender athlete case maine principal fight doj request student name transgender athlete case senator bob menendezs wife sentenced year bribery case conservative pundit matt walsh issue defiant statement receives flood death threat senate republican defeat effort democrat force release epstein file gloversville considers extending moratorium solar battery storage facility msnbc fire matthew dowd charlie kirk</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
